--- a/data/review/audit_T1.xlsx
+++ b/data/review/audit_T1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:S97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,15 +494,20 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>audit</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>audit_note</t>
         </is>
@@ -579,11 +584,12 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:09e3e960-2759-11f1-aa6b-33c42ee76deb:2007-08-08</t>
+          <t>vilextime:T1:provision:087c6ee0-eab8-11f0-ae57-61568758dbb7#k6#c:2014-01-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -593,37 +599,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pháp luật về đăng ký và quản lý hành nghề kế toán quy định việc xóa tên người hành nghề kế toán khi đăng ký hành nghề không đúng thực tế như thế nào?</t>
+          <t>Một đơn vị được cấp phép cung cấp dịch vụ chứng thực chữ ký số công cộng nhưng đặt hệ thống thiết bị ở nước ngoài thì hành vi này thuộc khung phạt tiền nào?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2007-08-08</t>
+          <t>2014-01-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.9. Người hành nghề kế toán bị xóa tên trong danh sách đăng ký hành nghề kế toán trong các trường hợp sau:</t>
+          <t>6. Phạt tiền từ 60.000.000 đồng đến 80.000.000 đồng đối với một trong các hành vi sau đây:</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>c) Thực tế không hành nghề kế toán nhưng vẫn cố tình đăng ký hành nghề kế toán; hoặc đồng thời đăng ký hành nghề kế toán ở hai nơi.</t>
+          <t>c) Không đặt ở Việt Nam hệ thống thiết bị cung cấp dịch vụ chứng thực chữ ký số của tổ chức được Bộ Thông tin và Truyền thông cấp giấy phép cung cấp dịch vụ chứng thực chữ ký số công cộng hoặc giấy chứng nhận đủ điều kiện bảo đảm an toàn cho chữ ký số chuyên dùng;</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2</t>
+          <t>Điểm c Khoản 6 Điều 57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>72/2007/TT-BTC</t>
+          <t>174/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13896</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32615</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -637,25 +643,22 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mục 2.9.c bị ghi thành 'Điểm c Khoản 2'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức được cấp phép cung cấp dịch vụ chứng thực chữ ký số công cộng nhưng không đặt hệ thống thiết bị tại Việt Nam, thì bị phạt tiền ở mức nào?»; nhãn cũ dat: Câu hỏi về 'một tổ chức'; chưa kiểm được mức trong khoản là cho tổ chức hay cá nhân vì thân Điều 2 NĐ 174/2013 (quy định mức phạt đối với cá nhân, tổ chức) mất khi crawl — người audit cần kiểm). Hỏi khung phạt tiền của hành vi: 60–80 triệu theo câu dẫn. Thân Điều 2 NĐ 174/2013 (mức cho cá nhân/tổ chức) mất khi crawl, người audit kiểm nếu cần</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:0f951378-eb7e-11f0-ad7d-19efec5eca1a#k3#d:2014-11-02</t>
+          <t>vilextime:T1:provision:09e3e960-2759-11f1-aa6b-33c42ee76deb:2007-08-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -665,37 +668,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Một người dân phát hiện thủ tục hành chính được giải quyết khác với thủ tục được niêm yết và đăng tải trên cơ sở dữ liệu quốc gia thì có thể phản ánh, kiến nghị với những cơ quan nào?</t>
+          <t>Pháp luật về đăng ký và quản lý hành nghề kế toán quy định việc xóa tên người hành nghề kế toán khi đăng ký hành nghề không đúng thực tế như thế nào?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
+          <t>2007-08-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3. Phản ánh, kiến nghị với Tổ chức Pháp chế các Bộ, cơ quan ngang Bộ, các cơ quan: Bảo hiểm Xã hội Việt Nam, Ngân hàng Chính sách Xã hội, Ngân hàng Phát triển Việt Nam; Sở Tư pháp các tỉnh, thành phố trực thuộc Trung ương hoặc Cục Kiểm soát thủ tục hành chính Bộ Tư pháp về những nội dung sau:</t>
+          <t>2.9. Người hành nghề kế toán bị xóa tên trong danh sách đăng ký hành nghề kế toán trong các trường hợp sau:</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>d) Sự không thống nhất giữa thủ tục hành chính được giải quyết với thủ tục hành chính được niêm yết tại nơi giải quyết thủ tục hành chính và được đăng tải trên Cơ sở dữ liệu quốc gia.</t>
+          <t>c) Thực tế không hành nghề kế toán nhưng vẫn cố tình đăng ký hành nghề kế toán; hoặc đồng thời đăng ký hành nghề kế toán ở hai nơi.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 3 Điều 10</t>
+          <t>Điểm c Khoản 2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>19/2014/TT-BTP</t>
+          <t>72/2007/TT-BTC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37749</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13896</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -709,17 +712,26 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Mục 2.9.c bị ghi thành 'Điểm c Khoản 2'</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:0fdffb50-2d40-11f1-ad9b-6dee35851177:2025-12-19</t>
+          <t>vilextime:T1:provision:0f951378-eb7e-11f0-ad7d-19efec5eca1a#k3#d:2014-11-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -729,37 +741,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực chức danh nghề nghiệp bác sĩ y học dự phòng, nhiệm vụ về truyền thông giáo dục sức khỏe và quản lý sức khỏe cộng đồng gồm những việc gì?</t>
+          <t>Một người dân phát hiện thủ tục hành chính được giải quyết khác với thủ tục được niêm yết và đăng tải trên cơ sở dữ liệu quốc gia thì có thể phản ánh, kiến nghị với những cơ quan nào?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2014-11-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. Nhiệm vụ:</t>
+          <t>3. Phản ánh, kiến nghị với Tổ chức Pháp chế các Bộ, cơ quan ngang Bộ, các cơ quan: Bảo hiểm Xã hội Việt Nam, Ngân hàng Chính sách Xã hội, Ngân hàng Phát triển Việt Nam; Sở Tư pháp các tỉnh, thành phố trực thuộc Trung ương hoặc Cục Kiểm soát thủ tục hành chính Bộ Tư pháp về những nội dung sau:</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>c) Tổ chức biên soạn nội dung và lập kế hoạch hướng dẫn công tác thông tin, giáo dục, truyền thông về bảo vệ, chăm sóc và nâng cao sức khỏe; đưa ra các biện pháp quản lý sức khỏe tại cộng đồng;</t>
+          <t>d) Sự không thống nhất giữa thủ tục hành chính được giải quyết với thủ tục hành chính được niêm yết tại nơi giải quyết thủ tục hành chính và được đăng tải trên Cơ sở dữ liệu quốc gia.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 1 Điều 8</t>
+          <t>Điểm d Khoản 3 Điều 10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>41/2025/TT-BYT</t>
+          <t>19/2014/TT-BTP</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183370</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37749</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -769,33 +781,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Thông tư có ba Điều cho ba hạng bác sĩ y học dự phòng (Điều 7 hạng I, Điều 8 hạng II, Điều 9 hạng III), mỗi Điều có điểm c về truyền thông giáo dục sức khỏe; câu hỏi không nêu hạng</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Điều 7 điểm c: Chủ trì, biên soạn nội dung và lập kế hoạch hướng dẫn công tác thông tin, giáo dục, truyền thông...</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:102bc0a0-4247-11f1-8e2b-43ffd0f6b455:2026-05-19</t>
+          <t>vilextime:T1:provision:0fdffb50-2d40-11f1-ad9b-6dee35851177:2025-12-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -805,37 +806,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hành vi sử dụng biển hiệu sai mẫu hoặc sai nội dung đăng ký hoạt động trong lĩnh vực bổ trợ tư pháp được xác định ra sao về mức xử phạt?</t>
+          <t>Trong lĩnh vực chức danh nghề nghiệp bác sĩ y học dự phòng hạng II, nhiệm vụ về truyền thông giáo dục sức khỏe và quản lý sức khỏe cộng đồng gồm những việc gì?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. Phạt tiền từ 3.000.000 đồng đến 7.000.000 đồng đối với một trong các hành vi sau:</t>
+          <t>1. Nhiệm vụ:</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>e) Sử dụng biển hiệu không đúng mẫu hoặc nội dung biển hiệu không đúng giấy đăng ký hoạt động;</t>
+          <t>c) Tổ chức biên soạn nội dung và lập kế hoạch hướng dẫn công tác thông tin, giáo dục, truyền thông về bảo vệ, chăm sóc và nâng cao sức khỏe; đưa ra các biện pháp quản lý sức khỏe tại cộng đồng;</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Điểm e Khoản 1 Điều 17</t>
+          <t>Điểm c Khoản 1 Điều 8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>109/2026/NĐ-CP</t>
+          <t>41/2025/TT-BYT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0ae72df0-4247-11f1-9aef-8b444472143a</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183370</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -845,33 +846,26 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>'Biển hiệu sai mẫu/sai nội dung trong lĩnh vực bổ trợ tư pháp' có ở Điều 9 (tổ chức hành nghề luật sư), 11 (tư vấn pháp luật), 17 (công chứng), 69 (thừa phát lại) với mức phạt khác nhau; câu hỏi không nêu nghề</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Điều 69 điểm m: Sử dụng biển hiệu không đúng mẫu quy định.</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực chức danh nghề nghiệp bác sĩ y học dự phòng, nhiệm vụ về truyền thông giáo dục sức khỏe và quản lý sức khỏe cộng đồng gồm những việc gì?»; nhãn cũ khong_dat question_ambiguous: Thông tư có ba Điều cho ba hạng bác sĩ y học dự phòng (Điều 7 hạng I, Điều 8 hạng II, Điều 9 hạng III), mỗi Điều có điểm c về truyền thông giáo dục sức khỏe; câu hỏi không nêu hạng). Đã nêu hạng II</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:1b3c3f68-eb87-11f0-a44b-2b764e784ab1:2001-04-02</t>
+          <t>vilextime:T1:provision:102bc0a0-4247-11f1-8e2b-43ffd0f6b455:2026-05-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -881,37 +875,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khi doanh nghiệp bảo hiểm hoặc doanh nghiệp môi giới bảo hiểm tổ chức công tác kế toán, doanh nghiệp phải áp dụng chế độ kế toán nào?</t>
+          <t>Trong lĩnh vực công chứng, hành vi sử dụng biển hiệu không đúng mẫu hoặc có nội dung không khớp với giấy đăng ký hoạt động thuộc khung phạt tiền nào?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2001-04-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VÀ BÁO CÁO TÀI CHÍNH</t>
+          <t>1. Phạt tiền từ 3.000.000 đồng đến 7.000.000 đồng đối với một trong các hành vi sau:</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doanh nghiệp bảo hiểm, doanh nghiệp môi giới bảo hiểm phải thực hiện chế độ kế toán áp dụng đối với kinh doanh bảo hiểm theo quy định của pháp luật về kế toán.</t>
+          <t>e) Sử dụng biển hiệu không đúng mẫu hoặc nội dung biển hiệu không đúng giấy đăng ký hoạt động;</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Điều 101</t>
+          <t>Điểm e Khoản 1 Điều 17</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24/2000/QH10</t>
+          <t>109/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5748</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0ae72df0-4247-11f1-9aef-8b444472143a</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -925,25 +919,22 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>valid_to_wrong,lead_in_wrong</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Luật KDBH 24/2000/QH10 đã bị Luật KDBH 08/2022/QH15 thay thế từ 01/01/2023 (có cạnh 'Văn bản được thay thế'); lead_in chỉ còn mảnh tiêu đề 'VÀ BÁO CÁO TÀI CHÍNH'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Hành vi sử dụng biển hiệu sai mẫu hoặc sai nội dung đăng ký hoạt động trong lĩnh vực bổ trợ tư pháp được xác định ra sao về mức xử phạt?»; nhãn cũ khong_dat question_ambiguous: 'Biển hiệu sai mẫu/sai nội dung trong lĩnh vực bổ trợ tư pháp' có ở Điều 9 (tổ chức hành nghề luật sư), 11 (tư vấn pháp luật), 17 (công chứng), 69 (thừa phát lại) với mức phạt khác nhau; câu hỏi không nêu nghề). Hỏi khung phạt tiền của hành vi trong lĩnh vực công chứng: 3–7 triệu theo câu dẫn; tổ chức gấp 02 lần theo khoản 4 Điều 4 NĐ 109/2026</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:273af4d0-1db4-11f1-8ca4-fb91ecf6f674:2012-11-16</t>
+          <t>vilextime:T1:provision:1b3c3f68-eb87-11f0-a44b-2b764e784ab1:2001-04-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -953,37 +944,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nếu một thương nhân nước ngoài không có hiện diện tại Việt Nam phải thông báo hoạt động trên phương tiện thông tin đại chúng, thì những loại báo nào được coi là phương tiện thông tin đại chúng phổ biến?</t>
+          <t>Khi doanh nghiệp bảo hiểm hoặc doanh nghiệp môi giới bảo hiểm tổ chức công tác kế toán, doanh nghiệp phải áp dụng chế độ kế toán nào?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2012-11-16</t>
+          <t>2001-04-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Điều 11. Thông báo hoạt động</t>
+          <t>VÀ BÁO CÁO TÀI CHÍNH</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2. Các phương tiện thông tin đại chúng phổ biến bao gồm báo hình, báo tiếng, báo mạng, báo in được phát hành toàn quốc tại Việt Nam.</t>
+          <t>Doanh nghiệp bảo hiểm, doanh nghiệp môi giới bảo hiểm phải thực hiện chế độ kế toán áp dụng đối với kinh doanh bảo hiểm theo quy định của pháp luật về kế toán.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 11</t>
+          <t>Điều 101</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28/2012/TT-BCT</t>
+          <t>24/2000/QH10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27815</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5748</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -999,23 +990,24 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>valid_to_wrong</t>
+          <t>valid_to_wrong,lead_in_wrong</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 28/2012/TT-BCT nhưng valid_to rỗng</t>
+          <t>Luật KDBH 24/2000/QH10 đã bị Luật KDBH 08/2022/QH15 thay thế từ 01/01/2023 (có cạnh 'Văn bản được thay thế'); lead_in chỉ còn mảnh tiêu đề 'VÀ BÁO CÁO TÀI CHÍNH'</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:2744c8d4-278c-11f1-93f1-6b9e4c555f4c:1999-05-24</t>
+          <t>vilextime:T1:provision:273af4d0-1db4-11f1-8ca4-fb91ecf6f674:2012-11-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1025,37 +1017,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực tiền lương của Tổng Công ty Điện lực Việt Nam, điều kiện áp dụng hệ số điều chỉnh tăng thêm tiền lương tối thiểu để tính đơn giá tiền lương được quy định ra sao?</t>
+          <t>Nếu một thương nhân nước ngoài không có hiện diện tại Việt Nam phải thông báo hoạt động trên phương tiện thông tin đại chúng, thì những loại báo nào được coi là phương tiện thông tin đại chúng phổ biến?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1999-05-24</t>
+          <t>2012-11-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1. Đơn giá tiền lương.</t>
+          <t>Điều 11. Thông báo hoạt động</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>b. Điều kiện áp dụng hệ số điều chỉnh tăng thêm tiền lương tối thiểu: Việc áp dụng hệ số điều chỉnh tăng thêm tiền lương tối thiểu để tính đơn giá tiền lương của Tổng Công ty theo quy định tại Nghị định số 28/CP ngày 28/3/1997 của Chính phủ khi thực hiện đầy đủ các điều kiện sau: - Sản xuất, kinh doanh có lãi; - Bảo đảm thực hiện các khoản nộp ngân sách nhà nước theo đúng quy định của pháp luật; - Mỗi năm giảm tổn thất điện năng từ 0,2% - 0,3% so với chỉ tiêu kế hoạch được Hội đồng quản trị Tổng Công ty Điện lực Việt Nam phê duyệt (chỉ tiêu tổn thất điện được xây dựng trên cơ sở số thực hiện của năm trước liền kề). - Năng suất lao động bình quân của công nhân, viên chức ngành điện tính theo Kwh điện thương phẩm năm sau phải cao hơn năm trước liền kề.</t>
+          <t>2. Các phương tiện thông tin đại chúng phổ biến bao gồm báo hình, báo tiếng, báo mạng, báo in được phát hành toàn quốc tại Việt Nam.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Điểm b</t>
+          <t>Khoản 2 Điều 11</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20/1999/TT-BLĐTBXH</t>
+          <t>28/2012/TT-BCT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6796</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27815</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1071,23 +1063,24 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>citation_path_wrong</t>
+          <t>valid_to_wrong</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Citation chỉ còn 'Điểm b' (path 'Phần › Mục › Điểm b')</t>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 28/2012/TT-BCT nhưng valid_to rỗng</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:2f5ea3c0-2c85-11f1-b760-79130d885196:2014-01-01</t>
+          <t>vilextime:T1:provision:2744c8d4-278c-11f1-93f1-6b9e4c555f4c:1999-05-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1097,37 +1090,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pháp luật về xử phạt vi phạm hành chính trong lĩnh vực y tế quy định mức phạt như thế nào đối với người sử dụng lao động không đóng bảo hiểm y tế cho từ 500 đến dưới 1.000 người lao động?</t>
+          <t>Trong lĩnh vực tiền lương của Tổng Công ty Điện lực Việt Nam, điều kiện áp dụng hệ số điều chỉnh tăng thêm tiền lương tối thiểu để tính đơn giá tiền lương được quy định ra sao?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>1999-05-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3. Phạt tiền đối với hành vi không đóng bảo hiểm y tế cho toàn bộ số người lao động có trách nhiệm tham gia bảo hiểm y tế của người sử dụng lao động theo một trong các mức sau đây:</t>
+          <t>1. Đơn giá tiền lương.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>đ) Từ 15.000.000 đồng đến 20.000.000 đồng, khi vi phạm từ 500 đến dưới 1.000 người lao động;</t>
+          <t>b. Điều kiện áp dụng hệ số điều chỉnh tăng thêm tiền lương tối thiểu: Việc áp dụng hệ số điều chỉnh tăng thêm tiền lương tối thiểu để tính đơn giá tiền lương của Tổng Công ty theo quy định tại Nghị định số 28/CP ngày 28/3/1997 của Chính phủ khi thực hiện đầy đủ các điều kiện sau: - Sản xuất, kinh doanh có lãi; - Bảo đảm thực hiện các khoản nộp ngân sách nhà nước theo đúng quy định của pháp luật; - Mỗi năm giảm tổn thất điện năng từ 0,2% - 0,3% so với chỉ tiêu kế hoạch được Hội đồng quản trị Tổng Công ty Điện lực Việt Nam phê duyệt (chỉ tiêu tổn thất điện được xây dựng trên cơ sở số thực hiện của năm trước liền kề). - Năng suất lao động bình quân của công nhân, viên chức ngành điện tính theo Kwh điện thương phẩm năm sau phải cao hơn năm trước liền kề.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Điểm đ Khoản 3 Điều 57</t>
+          <t>Điểm b</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>176/2013/NĐ-CP</t>
+          <t>20/1999/TT-BLĐTBXH</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32779</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6796</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1143,23 +1136,24 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>valid_to_wrong</t>
+          <t>citation_path_wrong</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>NĐ 176/2013/NĐ-CP đã bị NĐ 117/2020/NĐ-CP thay thế (hiệu lực 15/11/2020), valid_to vẫn rỗng · Mức trong đáp án là mức cho cá nhân; nếu người sử dụng lao động là tổ chức thì gấp 02 lần (khoản 5 quy định chung NĐ 176/2013)</t>
+          <t>Citation chỉ còn 'Điểm b' (path 'Phần › Mục › Điểm b')</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:312d0ee8-eb81-11f0-be34-83d33c77be02#k3:2006-04-02</t>
+          <t>vilextime:T1:provision:2f5ea3c0-2c85-11f1-b760-79130d885196:2014-01-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1169,37 +1163,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Điều kiện về dự toán trước khi thực hiện chỉ định thầu được xác định ra sao trong quy định về đấu thầu?</t>
+          <t>Pháp luật về xử phạt vi phạm hành chính trong lĩnh vực y tế quy định mức phạt như thế nào đối với người sử dụng lao động không đóng bảo hiểm y tế cho từ 500 đến dưới 1.000 người lao động?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2006-04-02</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Điều 20. Chỉ định thầu</t>
+          <t>3. Phạt tiền đối với hành vi không đóng bảo hiểm y tế cho toàn bộ số người lao động có trách nhiệm tham gia bảo hiểm y tế của người sử dụng lao động theo một trong các mức sau đây:</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3. Trước khi thực hiện chỉ định thầu quy định tại các điểm b, c, d và đ khoản 1 Điều này, dự toán đối với gói thầu đó phải được phê duyệt theo quy định.</t>
+          <t>đ) Từ 15.000.000 đồng đến 20.000.000 đồng, khi vi phạm từ 500 đến dưới 1.000 người lao động;</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 20</t>
+          <t>Điểm đ Khoản 3 Điều 57</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>61/2005/QH11</t>
+          <t>176/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16750</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32779</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1213,17 +1207,26 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NĐ 176/2013/NĐ-CP đã bị NĐ 117/2020/NĐ-CP thay thế (hiệu lực 15/11/2020), valid_to vẫn rỗng · Mức trong đáp án là mức cho cá nhân; nếu người sử dụng lao động là tổ chức thì gấp 02 lần (khoản 5 quy định chung NĐ 176/2013)</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:344e3fb0-2c82-11f1-8054-4716585c218c:2022-09-02</t>
+          <t>vilextime:T1:provision:312d0ee8-eb81-11f0-be34-83d33c77be02#k3:2006-04-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1233,37 +1236,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Một cơ quan áp dụng biện pháp ngăn chặn đối với hành vi cản trở hoạt động tố tụng thì phải tuân theo nguyên tắc được quy định ở văn bản nào?</t>
+          <t>Điều kiện về dự toán trước khi thực hiện chỉ định thầu được xác định ra sao trong quy định về đấu thầu?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2006-04-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Điều 8. Biện pháp ngăn chặn, bảo đảm xử lý vi phạm hành chính đối với hành vi cản trở hoạt động tố tụng và nguyên tắc áp dụng</t>
+          <t>Điều 20. Chỉ định thầu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2. Nguyên tắc áp dụng biện pháp ngăn chặn và bảo đảm xử lý vi phạm hành chính đối với hành vi cản trở hoạt động tố tụng thực hiện theo quy định tại Điều 120 của Luật Xử lý vi phạm hành chính.</t>
+          <t>3. Trước khi thực hiện chỉ định thầu quy định tại các điểm b, c, d và đ khoản 1 Điều này, dự toán đối với gói thầu đó phải được phê duyệt theo quy định.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 8</t>
+          <t>Khoản 3 Điều 20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>02/2022/UBTVQH15</t>
+          <t>61/2005/QH11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155813</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16750</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1283,11 +1286,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:38528280-2c85-11f1-954b-d3e284a740f5:2014-02-02</t>
+          <t>vilextime:T1:provision:344e3fb0-2c82-11f1-8054-4716585c218c:2022-09-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1297,37 +1301,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực quản lý nợ của doanh nghiệp do Nhà nước nắm giữ toàn bộ vốn, Bộ Tài chính có trách nhiệm chủ trì xây dựng và hướng dẫn những nội dung nào?</t>
+          <t>Một cơ quan áp dụng biện pháp ngăn chặn đối với hành vi cản trở hoạt động tố tụng thì phải tuân theo nguyên tắc được quy định ở văn bản nào?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2014-02-02</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Điều 21. Quyền, trách nhiệm của Bộ Tài chính</t>
+          <t>Điều 8. Biện pháp ngăn chặn, bảo đảm xử lý vi phạm hành chính đối với hành vi cản trở hoạt động tố tụng và nguyên tắc áp dụng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1. Chủ trì nghiên cứu, xây dựng để báo cáo Chính phủ cơ chế về quản lý nợ của doanh nghiệp; hướng dẫn về các chỉ tiêu giám sát, đánh giá khả năng thanh toán nợ của doanh nghiệp; hướng dẫn chế độ trích lập và sử dụng các khoản dự phòng nợ phải thu khó đòi. Phối hợp tham gia với Bộ quản lý ngành, Ủy ban nhân dân cấp tỉnh trong việc giám sát, kiểm tra, đánh giá các khoản nợ của tập đoàn kinh tế nhà nước, tổng công ty nhà nước, công ty trách nhiệm hữu hạn một thành viên do Bộ quản lý ngành, Ủy ban nhân dân cấp tỉnh quyết định thành lập hoặc được giao quản lý.</t>
+          <t>2. Nguyên tắc áp dụng biện pháp ngăn chặn và bảo đảm xử lý vi phạm hành chính đối với hành vi cản trở hoạt động tố tụng thực hiện theo quy định tại Điều 120 của Luật Xử lý vi phạm hành chính.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 21</t>
+          <t>Khoản 2 Điều 8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>206/2013/NĐ-CP</t>
+          <t>02/2022/UBTVQH15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32730</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155813</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1347,11 +1351,12 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:3c58dda6-e177-11f0-aad8-510bc3ddb5e6:2007-08-31</t>
+          <t>vilextime:T1:provision:38528280-2c85-11f1-954b-d3e284a740f5:2014-02-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1361,37 +1366,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trách nhiệm tiếp nhận, giải quyết việc thông báo, đăng ký khuyến mại và hội chợ, triển lãm thương mại của cơ quan quản lý nhà nước được xác định ra sao?</t>
+          <t>Trong lĩnh vực quản lý nợ của doanh nghiệp do Nhà nước nắm giữ toàn bộ vốn, Bộ Tài chính có trách nhiệm chủ trì xây dựng và hướng dẫn những nội dung nào?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2007-08-31</t>
+          <t>2014-02-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2. Trách nhiệm của cơ quan quản lý nhà nước</t>
+          <t>Điều 21. Quyền, trách nhiệm của Bộ Tài chính</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>b) Tiếp nhận, giải quyết việc thông báo, đăng ký thực hiện khuyến mại, tổ chức hội chợ, triển lãm thương mại thuộc thẩm quyền theo quy định tại Luật Thương mại, Nghị định số 37/2006/NĐ-CP và hướng dẫn tại Thông tư này;</t>
+          <t>1. Chủ trì nghiên cứu, xây dựng để báo cáo Chính phủ cơ chế về quản lý nợ của doanh nghiệp; hướng dẫn về các chỉ tiêu giám sát, đánh giá khả năng thanh toán nợ của doanh nghiệp; hướng dẫn chế độ trích lập và sử dụng các khoản dự phòng nợ phải thu khó đòi. Phối hợp tham gia với Bộ quản lý ngành, Ủy ban nhân dân cấp tỉnh trong việc giám sát, kiểm tra, đánh giá các khoản nợ của tập đoàn kinh tế nhà nước, tổng công ty nhà nước, công ty trách nhiệm hữu hạn một thành viên do Bộ quản lý ngành, Ủy ban nhân dân cấp tỉnh quyết định thành lập hoặc được giao quản lý.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2</t>
+          <t>Khoản 1 Điều 21</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07/2007/TTLT-BTM-BTC</t>
+          <t>206/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46601</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32730</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1405,25 +1410,18 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Citation 'Điểm b Khoản 2' thiếu phần/mục cha (path 'Chương I › Khoản 2')</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:45d941c0-2c83-11f1-a5f8-7129425f1ab5:2020-01-02</t>
+          <t>vilextime:T1:provision:3c58dda6-e177-11f0-aad8-510bc3ddb5e6:2007-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,37 +1431,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pháp luật về quản lý đầu tư công trình lâm sinh quy định chi phí chung trong chi phí xây dựng được tính theo tỷ lệ nào và gồm những khoản gì?</t>
+          <t>Trách nhiệm tiếp nhận, giải quyết việc thông báo, đăng ký khuyến mại và hội chợ, triển lãm thương mại của cơ quan quản lý nhà nước được xác định ra sao?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2007-08-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1. Chi phí xây dựng:</t>
+          <t>2. Trách nhiệm của cơ quan quản lý nhà nước</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>b) Chi phí chung: được tính bằng 5,0% chi phí trực tiếp, gồm: Chi phí trang bị bảo hộ, an toàn lao động và bảo vệ môi trường cho người lao động và môi trường xung quanh; Chi phí vận chuyển máy móc, thiết bị thi công và lực lượng lao động đến và ra khỏi công trường; Chi phí bảo đảm an toàn giao thông phục vụ thi công (nếu có).</t>
+          <t>b) Tiếp nhận, giải quyết việc thông báo, đăng ký thực hiện khuyến mại, tổ chức hội chợ, triển lãm thương mại thuộc thẩm quyền theo quy định tại Luật Thương mại, Nghị định số 37/2006/NĐ-CP và hướng dẫn tại Thông tư này;</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 5</t>
+          <t>Điểm b Khoản 2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15/2019/TT-BNNPTNT</t>
+          <t>07/2007/TTLT-BTM-BTC</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138874</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46601</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1479,23 +1477,24 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>valid_to_wrong</t>
+          <t>citation_path_wrong</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 15/2019/TT-BNNPTNT nhưng valid_to rỗng</t>
+          <t>Citation 'Điểm b Khoản 2' thiếu phần/mục cha (path 'Chương I › Khoản 2')</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:46db5bf0-31c7-11f1-ac1e-d38b84040a86:2026-02-16</t>
+          <t>vilextime:T1:provision:3f86fc30-ead5-11f0-8294-8d98737f1d2e:2006-01-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1505,37 +1504,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trường hợp một người vận chuyển hàng hóa sao chép lậu và thu lợi bất hợp pháp từ 20.000.000 đồng đến dưới 30.000.000 đồng, người đó bị phạt tiền ở mức nào?</t>
+          <t>Nhóm tài liệu về quá trình đàm phán, ký kết và thực hiện hợp đồng trong giao dịch liên kết được xác định ra sao khi xác định giá thị trường?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2006-01-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1. Phạt tiền đối với hành vi vận chuyển hàng hóa sao chép lậu theo quy định như sau:</t>
+          <t>2.3.2. Thông tin về giao dịch của cơ sở kinh doanh:</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>c) Từ 5.000.000 đồng đến 10.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 20.000.000 đồng đến dưới 30.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 40.000.000 đồng đến dưới 60.000.000 đồng hoặc hàng hóa vi phạm trị giá từ 40.000.000 đồng đến dưới 60.000.000 đồng;</t>
+          <t>c) Các thông tin, tài liệu và chứng từ về quá trình thương lượng, ký kết, thực hiện và thanh lý các hợp đồng/thỏa thuận kinh tế có liên quan đến giao dịch (thường bao gồm: mô tả sản phẩm, địa điểm diễn ra các giao dịch, hình thức giao dịch, giá trị giao dịch, điều kiện thanh toán, các chứng từ thanh toán, thời gian thực hiện, các biên bản làm việc hoặc chỉ thị của ban lãnh đạo về quá trình thương lượng, ký kết và thực hiện giao dịch);</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 1 Điều 36</t>
+          <t>Điểm c Khoản 2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>341/2025/NĐ-CP</t>
+          <t>117/2005/TT-BTC</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185823</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16683</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1549,17 +1548,26 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Đáp án đúng; trích dẫn 'Điểm c Khoản 2' nhưng văn bản đánh số mục 2.3.2 (câu dẫn), đường dẫn trích dẫn lệch</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:4a1d663e-eb7f-11f0-a965-3115c99302b6#k2:2005-04-09</t>
+          <t>vilextime:T1:provision:45d941c0-2c83-11f1-a5f8-7129425f1ab5:2020-01-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1569,37 +1577,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Một người bị xử phạt vi phạm hành chính không tự nguyện nộp tiền phạt thì có thể bị áp dụng biện pháp cưỡng chế nào đối với tài sản của mình?</t>
+          <t>Pháp luật về quản lý đầu tư công trình lâm sinh quy định chi phí chung trong chi phí xây dựng được tính theo tỷ lệ nào và gồm những khoản gì?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2005-04-09</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Điều 2. Các biện pháp cưỡng chế hành chính</t>
+          <t>1. Chi phí xây dựng:</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2. Kê biên phần tài sản có giá trị tương ứng với số tiền phạt để bán đấu giá;</t>
+          <t>b) Chi phí chung: được tính bằng 5,0% chi phí trực tiếp, gồm: Chi phí trang bị bảo hộ, an toàn lao động và bảo vệ môi trường cho người lao động và môi trường xung quanh; Chi phí vận chuyển máy móc, thiết bị thi công và lực lượng lao động đến và ra khỏi công trường; Chi phí bảo đảm an toàn giao thông phục vụ thi công (nếu có).</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 2</t>
+          <t>Điểm b Khoản 1 Điều 5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>37/2005/NĐ-CP</t>
+          <t>15/2019/TT-BNNPTNT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18448</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138874</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1609,33 +1617,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Hỏi biện pháp cưỡng chế 'đối với tài sản'; khoản 1 (khấu trừ tiền từ tài khoản ngân hàng) cũng là biện pháp đối với tài sản</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1. Khấu trừ một phần tiền lương hoặc một phần thu nhập; khấu trừ tiền từ tài khoản tại ngân hàng;</t>
-        </is>
-      </c>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 15/2019/TT-BNNPTNT nhưng valid_to rỗng</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:5003ac4e-eb7e-11f0-a0a3-c9aae40c2eb7:2004-07-02</t>
+          <t>vilextime:T1:provision:46db5bf0-31c7-11f1-ac1e-d38b84040a86:2026-02-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1645,33 +1650,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Theo quy định về tố tụng hình sự, vật chứng, ảnh hoặc biên bản xác nhận vật chứng được xem xét như thế nào tại phiên tòa?</t>
+          <t>Trường hợp một người vận chuyển hàng hóa sao chép lậu và thu lợi bất hợp pháp từ 20.000.000 đồng đến dưới 30.000.000 đồng, người đó bị phạt tiền ở mức nào?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2004-07-02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1. Phạt tiền đối với hành vi vận chuyển hàng hóa sao chép lậu theo quy định như sau:</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1. Vật chứng, ảảnh hoặc biên bản xác nhận vật chứng được đưa ra để xem xét tại phiên tòa.</t>
+          <t>c) Từ 5.000.000 đồng đến 10.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 20.000.000 đồng đến dưới 30.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 40.000.000 đồng đến dưới 60.000.000 đồng hoặc hàng hóa vi phạm trị giá từ 40.000.000 đồng đến dưới 60.000.000 đồng;</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 94</t>
+          <t>Điểm c Khoản 1 Điều 36</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19/2003/QH11</t>
+          <t>341/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19411</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185823</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1685,25 +1694,18 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Chấm lại 28/09 trên câu hỏi đã sửa. Câu hỏi nay hỏi đúng việc xem xét vật chứng. Nút không có Điều cha trong cây nên citation "Điều 94" không kiểm được (theo trí nhớ thuộc Điều 212 BLTTHS 2003 — cần kiểm)</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:514503be-eb6f-11f0-8d3d-79ec914317f6:2004-02-21</t>
+          <t>vilextime:T1:provision:4a1d663e-eb7f-11f0-a965-3115c99302b6#k2:2005-04-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1713,37 +1715,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực đấu thầu, nhà thầu là tổ chức trong nước phải đáp ứng điều kiện gì về đăng ký kinh doanh?</t>
+          <t>Một người bị xử phạt không tự nguyện nộp tiền phạt thì biện pháp cưỡng chế nào cho phép cơ quan có thẩm quyền bán đấu giá tài sản của người đó để thu tiền phạt?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2004-02-21</t>
+          <t>2005-04-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1. Đối với nhà thầu là tổ chức trong nước</t>
+          <t>Điều 2. Các biện pháp cưỡng chế hành chính</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>a. Có giấy chứng nhận đăng ký kinh doanh hoặc giấy phép kinh doanh và thực hiện đúng theo đăng ký kinh doanh hoặc giấy phép kinh doanh do cơ quan có thẩm quyền cấp;</t>
+          <t>2. Kê biên phần tài sản có giá trị tương ứng với số tiền phạt để bán đấu giá;</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Điểm a</t>
+          <t>Khoản 2 Điều 2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01/2004/TT-BKH</t>
+          <t>37/2005/NĐ-CP</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19605</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18448</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1757,25 +1759,22 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Citation chỉ còn 'Điểm a', path 'Phần 1 › Chương › Mục › Điểm a' mất số hiệu</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người bị xử phạt vi phạm hành chính không tự nguyện nộp tiền phạt thì có thể bị áp dụng biện pháp cưỡng chế nào đối với tài sản của mình?»; nhãn cũ khong_dat question_ambiguous: Hỏi biện pháp cưỡng chế 'đối với tài sản'; khoản 1 (khấu trừ tiền từ tài khoản ngân hàng) cũng là biện pháp đối với tài sản). Câu hỏi chốt biện pháp dẫn tới bán đấu giá, chỉ khớp khoản 2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:529ab5be-eb7f-11f0-b0ae-9bfe0f000569:2017-07-02</t>
+          <t>vilextime:T1:provision:5003ac4e-eb7e-11f0-a0a3-c9aae40c2eb7:2004-07-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1785,37 +1784,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Việc xử lý vướng mắc trong quá trình áp dụng khung giá tính thuế tài nguyên được xác định ra sao trong quy định về khung giá tính thuế tài nguyên?</t>
+          <t>Theo quy định về tố tụng hình sự, vật chứng, ảnh hoặc biên bản xác nhận vật chứng được xem xét như thế nào tại phiên tòa?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2017-07-02</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Điều 10. Hiệu lực thi hành</t>
-        </is>
-      </c>
+          <t>2004-07-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3. Trong quá trình thực hiện, nếu có vướng mắc, đề nghị Ủy ban nhân dân các tỉnh, tổ chức, cá nhân phản ánh về Bộ Tài chính để được nghiên cứu giải quyết./. KT. BỘ TRƯỞNG THỨ TRƯỞNG (Đã ký) Đỗ Hoàng Anh Tuấn</t>
+          <t>1. Vật chứng, ảảnh hoặc biên bản xác nhận vật chứng được đưa ra để xem xét tại phiên tòa.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 10</t>
+          <t>Khoản 1 Điều 94</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44/2017/TT-BTC</t>
+          <t>19/2003/QH11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122447</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19411</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1825,33 +1820,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Câu 'nếu có vướng mắc đề nghị phản ánh về Bộ Tài chính' trong Điều hiệu lực thi hành, không phải quy phạm; đáp án dính khối chữ ký</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>./. KT. BỘ TRƯỞNG THỨ TRƯỞNG (Đã ký) Đỗ Hoàng Anh Tuấn</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi đã sửa. Câu hỏi nay hỏi đúng việc xem xét vật chứng. Nút không có Điều cha trong cây nên citation "Điều 94" không kiểm được (theo trí nhớ thuộc Điều 212 BLTTHS 2003 — cần kiểm)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:578ff710-29b8-11f1-b193-61b18a6e6e8f:2025-04-02</t>
+          <t>vilextime:T1:provision:514503be-eb6f-11f0-8d3d-79ec914317f6:2004-02-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1861,37 +1853,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trường hợp một dự án đất đai tại thành phố Đà Nẵng được rà soát điều kiện tiếp tục sử dụng đất, Ủy ban nhân dân thành phố phải ban hành quyết định đánh giá trong thời hạn bao lâu sau khi nhận hồ sơ?</t>
+          <t>Trong lĩnh vực đấu thầu, nhà thầu là tổ chức trong nước phải đáp ứng điều kiện gì về đăng ký kinh doanh?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2004-02-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2. Trình tự rà soát điều kiện được tiếp tục sử dụng đất để thực hiện dự án được thực hiện như sau:</t>
+          <t>1. Đối với nhà thầu là tổ chức trong nước</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>c) Trong thời hạn không quá 05 ngày làm việc kể từ ngày nhận được hồ sơ do Sở Nông nghiệp và Môi trường trình, Ủy ban nhân dân thành phố Đà Nẵng xem xét về các điều kiện và ban hành quyết định đánh giá dự án đủ điều kiện được tiếp tục sử dụng đất gửi Sở Nông nghiệp và Môi trường;</t>
+          <t>a. Có giấy chứng nhận đăng ký kinh doanh hoặc giấy phép kinh doanh và thực hiện đúng theo đăng ký kinh doanh hoặc giấy phép kinh doanh do cơ quan có thẩm quyền cấp;</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2 Điều 5</t>
+          <t>Điểm a</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>76/2025/NĐ-CP</t>
+          <t>01/2004/TT-BKH</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=176677</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19605</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1905,17 +1897,26 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Citation chỉ còn 'Điểm a', path 'Phần 1 › Chương › Mục › Điểm a' mất số hiệu</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:58822430-eacb-11f0-9a05-4d109da0051b#k3:2016-02-02</t>
+          <t>vilextime:T1:provision:529ab5be-eb7f-11f0-b0ae-9bfe0f000569:2017-07-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1925,37 +1926,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trường hợp cần quan trắc công trình đường sắt phục vụ bảo trì, nội dung quan trắc phải bao gồm những thông tin gì?</t>
+          <t>Việc xử lý vướng mắc trong quá trình áp dụng khung giá tính thuế tài nguyên được xác định ra sao trong quy định về khung giá tính thuế tài nguyên?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2016-02-02</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Điều 11. Quan trắc công trình đường sắt phục vụ công tác bảo trì</t>
+          <t>Điều 10. Hiệu lực thi hành</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3. Nội dung quan trắc công trình đường sắt bao gồm: vị trí quan trắc, thông số quan trắc (biến dạng, nghiêng, lún, nứt, võng, ...), thời gian quan trắc, số lượng chu kỳ đo và các nội dung cần thiết khác. Phương án quan trắc phải quy định về phương pháp đo, các thiết bị đo, sơ đồ bố trí và cấu tạo các dấu mốc; tổ chức thực hiện quan trắc; phương pháp xử lý số liệu đo và các nội dung cần thiết khác.</t>
+          <t>3. Trong quá trình thực hiện, nếu có vướng mắc, đề nghị Ủy ban nhân dân các tỉnh, tổ chức, cá nhân phản ánh về Bộ Tài chính để được nghiên cứu giải quyết./. KT. BỘ TRƯỞNG THỨ TRƯỞNG (Đã ký) Đỗ Hoàng Anh Tuấn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 11</t>
+          <t>Khoản 3 Điều 10</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>81/2015/TT-BGTVT</t>
+          <t>44/2017/TT-BTC</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=95563</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122447</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1965,21 +1966,38 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Câu 'nếu có vướng mắc đề nghị phản ánh về Bộ Tài chính' trong Điều hiệu lực thi hành, không phải quy phạm; đáp án dính khối chữ ký</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>./. KT. BỘ TRƯỞNG THỨ TRƯỞNG (Đã ký) Đỗ Hoàng Anh Tuấn</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>loại lineage (other): Câu 'nếu có vướng mắc đề nghị phản ánh về Bộ Tài chính' trong Điều hiệu lực thi hành, không phải quy phạm; đáp án dính khối chữ ký</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:596e6fe0-2c7d-11f1-b48b-4383f69de024:2025-01-02</t>
+          <t>vilextime:T1:provision:578ff710-29b8-11f1-b193-61b18a6e6e8f:2025-04-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1989,37 +2007,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nếu một đơn vị muốn được coi là cơ sở đào tạo lái xe quân sự, thì đơn vị đó phải thuộc phạm vi quản lý của cơ quan nào và có chức năng gì?</t>
+          <t>Trường hợp một dự án đất đai tại thành phố Đà Nẵng được rà soát điều kiện tiếp tục sử dụng đất, Ủy ban nhân dân thành phố phải ban hành quyết định đánh giá trong thời hạn bao lâu sau khi nhận hồ sơ?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Điều 3. Giải thích từ ngữ Trong Thông tư này, các từ ngữ dưới đây được hiểu như sau:</t>
+          <t>2. Trình tự rà soát điều kiện được tiếp tục sử dụng đất để thực hiện dự án được thực hiện như sau:</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5. Cơ sở đào tạo lái xe quân sự là các cơ sở đào tạo thuộc phạm vi quản lý của Bộ Quốc phòng có chức năng đào tạo lái xe quân sự.</t>
+          <t>c) Trong thời hạn không quá 05 ngày làm việc kể từ ngày nhận được hồ sơ do Sở Nông nghiệp và Môi trường trình, Ủy ban nhân dân thành phố Đà Nẵng xem xét về các điều kiện và ban hành quyết định đánh giá dự án đủ điều kiện được tiếp tục sử dụng đất gửi Sở Nông nghiệp và Môi trường;</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Khoản 5 Điều 3</t>
+          <t>Điểm c Khoản 2 Điều 5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>68/2024/TT-BQP</t>
+          <t>76/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172311</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=176677</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2039,11 +2057,12 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:5ad876ec-eb72-11f0-9841-0f234bceec4b:2023-09-16</t>
+          <t>vilextime:T1:provision:58822430-eacb-11f0-9a05-4d109da0051b#k3:2016-02-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2053,37 +2072,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trách nhiệm của cán bộ Cảnh sát giao thông sau khi lập xong biên bản vi phạm hành chính được xác định ra sao trong quy định về tuần tra, kiểm soát giao thông đường bộ?</t>
+          <t>Trường hợp cần quan trắc công trình đường sắt phục vụ bảo trì, nội dung quan trắc phải bao gồm những thông tin gì?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2016-02-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2. Xử phạt vi phạm hành chính có lập biên bản</t>
+          <t>Điều 11. Quan trắc công trình đường sắt phục vụ công tác bảo trì</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>b) Khi lập xong biên bản vi phạm hành chính, cán bộ lập biên bản đọc lại cho những người có tên trong biên bản cùng nghe; hướng dẫn quyền, thời hạn giải trình về vi phạm hành chính đối với hành vi vi phạm hành chính mà cá nhân, tổ chức có quyền giải trình theo quy định tại Điều 61 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020); đề nghị người vi phạm cung cấp số điện thoại liên hệ (nếu có) để nhận thông tin xử phạt thông qua Cổng dịch vụ công Quốc gia, Cổng dịch vụ công Bộ Công an; ký vào biên bản (trường hợp người vi phạm không ký được thì điểm chỉ), trừ trường hợp biên bản được lập theo quy định tại khoản 7 Điều 58 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020). Trường hợp có người chứng kiến, người phiên dịch, người bị thiệt hại hoặc đại diện tổ chức bị thiệt hại thì những người này cùng phải ký vào biên bản; biên bản vi phạm hành chính gồm nhiều trang, thì phải ký vào từng trang biên bản;</t>
+          <t>3. Nội dung quan trắc công trình đường sắt bao gồm: vị trí quan trắc, thông số quan trắc (biến dạng, nghiêng, lún, nứt, võng, ...), thời gian quan trắc, số lượng chu kỳ đo và các nội dung cần thiết khác. Phương án quan trắc phải quy định về phương pháp đo, các thiết bị đo, sơ đồ bố trí và cấu tạo các dấu mốc; tổ chức thực hiện quan trắc; phương pháp xử lý số liệu đo và các nội dung cần thiết khác.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 20</t>
+          <t>Khoản 3 Điều 11</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>32/2023/TT-BCA</t>
+          <t>81/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163057</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=95563</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2103,11 +2122,12 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:5cddfc6a-df46-11f0-9c9d-c1dd56fad116#k5#b:2007-05-19</t>
+          <t>vilextime:T1:provision:596e6fe0-2c7d-11f1-b48b-4383f69de024:2025-01-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2117,37 +2137,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Người nước ngoài thực hiện hành vi phát tán virus, phần mềm hoặc mã độc, hoặc thực hiện hành vi đánh bạc, tổ chức đánh bạc, môi giới mại dâm, lừa đảo, khủng bố trên môi trường mạng thì có thể bị áp dụng hình thức xử phạt bổ sung nào?</t>
+          <t>Nếu một đơn vị muốn được coi là cơ sở đào tạo lái xe quân sự, thì đơn vị đó phải thuộc phạm vi quản lý của cơ quan nào và có chức năng gì?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2007-05-19</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5. Hình thức xử phạt bổ sung:</t>
+          <t>Điều 3. Giải thích từ ngữ Trong Thông tư này, các từ ngữ dưới đây được hiểu như sau:</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>b) Trục xuất người nước ngoài có hành vi vi phạm quy định tại điểm a, d khoản 3 Điều này.</t>
+          <t>5. Cơ sở đào tạo lái xe quân sự là các cơ sở đào tạo thuộc phạm vi quản lý của Bộ Quốc phòng có chức năng đào tạo lái xe quân sự.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 5 Điều 18</t>
+          <t>Khoản 5 Điều 3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>63/2007/NĐ-CP</t>
+          <t>68/2024/TT-BQP</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14477</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172311</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2157,33 +2177,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Chấm lại 28/09 trên câu hỏi đã sửa. Vẫn mơ hồ sau khi sửa: điểm a (tịch thu tang vật) cũng áp dụng cho hành vi tại điểm a, d khoản 3, nên đáp án đủ là cả tịch thu tang vật và trục xuất</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>a) Tịch thu tang vật, phương tiện được sử dụng để vi phạm hành chính đối với hành vi quy định tại điểm a, c, d khoản 3...</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:5e8c584c-543d-11f1-ae49-0120c8b0e422:2026-02-02</t>
+          <t>vilextime:T1:provision:5ad876ec-eb72-11f0-9841-0f234bceec4b:2023-09-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2193,37 +2202,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nếu một doanh nghiệp gia công hàng xuất khẩu loại ra những bán thành phẩm sai quy cách và không dùng được như ban đầu, thì chúng được xác định là loại hàng gì theo quy định về thủ tục hải quan?</t>
+          <t>Trách nhiệm của cán bộ Cảnh sát giao thông sau khi lập xong biên bản vi phạm hành chính được xác định ra sao trong quy định về tuần tra, kiểm soát giao thông đường bộ?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2. Phế liệu, phế phẩm, phế thải của hàng hóa gia công, sản xuất xuất khẩu</t>
+          <t>2. Xử phạt vi phạm hành chính có lập biên bản</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>b) Phế phẩm là thành phẩm, bán thành phẩm không đạt tiêu chuẩn kỹ thuật (quy cách, kích thước, phầm chất,...) bị loại bỏ từ quá trình gia công, sản xuất hàng hoá xuất khẩu, không đạt chất lượng đề xuất khẩu và không còn giá trị sử dụng ban đầu;</t>
+          <t>b) Khi lập xong biên bản vi phạm hành chính, cán bộ lập biên bản đọc lại cho những người có tên trong biên bản cùng nghe; hướng dẫn quyền, thời hạn giải trình về vi phạm hành chính đối với hành vi vi phạm hành chính mà cá nhân, tổ chức có quyền giải trình theo quy định tại Điều 61 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020); đề nghị người vi phạm cung cấp số điện thoại liên hệ (nếu có) để nhận thông tin xử phạt thông qua Cổng dịch vụ công Quốc gia, Cổng dịch vụ công Bộ Công an; ký vào biên bản (trường hợp người vi phạm không ký được thì điểm chỉ), trừ trường hợp biên bản được lập theo quy định tại khoản 7 Điều 58 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020). Trường hợp có người chứng kiến, người phiên dịch, người bị thiệt hại hoặc đại diện tổ chức bị thiệt hại thì những người này cùng phải ký vào biên bản; biên bản vi phạm hành chính gồm nhiều trang, thì phải ký vào từng trang biên bản;</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2</t>
+          <t>Điểm b Khoản 2 Điều 20</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>121/2025/TT-BTC</t>
+          <t>32/2023/TT-BCA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6776a0a0-543a-11f1-9456-0b6fbb8f8274</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163057</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2237,25 +2246,18 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>citation_path_wrong,group_wrong</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Đơn vị là lời văn trích trong thông tư sửa đổi 121/2025/TT-BTC; citation thiếu Điều ('Điểm b Khoản 2'); thực chất là phiên bản mới của điều khoản thuộc thông tư bị sửa</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:5ed1beca-2c86-11f1-841a-7d89578d89e1:2013-05-16</t>
+          <t>vilextime:T1:provision:5c05d5b8-5b30-11f1-941d-c91be229dfcc:2026-05-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2265,37 +2267,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Khi công dân Việt Nam đã kết hôn ở nước ngoài muốn ghi vào sổ việc kết hôn, hồ sơ phải có bản sao giấy tờ nào do nước ngoài cấp?</t>
+          <t>Trong lĩnh vực phối hợp giữa Viện kiểm sát và Tòa án về tố tụng dân sự, Tòa án cấp phúc thẩm phải gửi quyết định về kháng cáo quá hạn cho Viện kiểm sát trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2013-05-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2. Hồ sơ ghi vào sổ việc kết hôn được lập thành 01 bộ, gồm các giấy tờ sau:</t>
+          <t>Điều 16. Gửi văn bản thông báo, quyết định về việc xem xét kháng cáo quá hạn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>b) Bản sao giấy tờ chứng nhận việc kết hôn do cơ quan có thẩm quyền của nước ngoài cấp;</t>
+          <t>2. Tòa án cấp phúc thẩm gửi cho Viện kiểm sát cùng cấp quyết định chấp nhận kháng cáo quá hạn, quyết định không chấp nhận kháng cáo quá hạn quy định tại khoản 3 Điều 275 BLTTDS trong thời hạn 05 ngày làm việc kể từ ngày ra quyết định.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 17</t>
+          <t>Khoản 2 Điều 16</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>24/2013/NĐ-CP</t>
+          <t>07/2026/TTLT-VKSNDTC-TANDTC</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30386</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5b03a780-5b30-11f1-be19-439d7a536e10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2309,25 +2311,18 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>NĐ 24/2013/NĐ-CP đã bị NĐ 123/2015/NĐ-CP thay thế (hiệu lực 01/01/2016); valid_to vẫn rỗng</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:624d3820-2dbe-11f1-ad11-45ab3867d967:2016-07-02</t>
+          <t>vilextime:T1:provision:5cddfc6a-df46-11f0-9c9d-c1dd56fad116#k5#b:2007-05-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2337,37 +2332,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Khi cần cập nhật danh mục chế phẩm sinh học dùng trong xử lý chất thải, Tổng cục Môi trường phải rà soát danh mục này với tần suất như thế nào?</t>
+          <t>Người nước ngoài thực hiện hành vi phát tán virus, phần mềm hoặc mã độc, hoặc thực hiện hành vi đánh bạc, tổ chức đánh bạc, môi giới mại dâm, lừa đảo, khủng bố trên môi trường mạng thì ngoài việc bị tịch thu tang vật, phương tiện, còn có thể bị áp dụng hình thức xử phạt bổ sung nào?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2016-07-02</t>
+          <t>2007-05-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Điều 25. Danh mục chế phẩm sinh học trong xử lý chất thải tại Việt Nam</t>
+          <t>5. Hình thức xử phạt bổ sung:</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2. Định kỳ 06 tháng một lần, Tổng cục Môi trường có trách nhiệm rà soát, sửa đổi, bổ sung danh mục chế phẩm sinh học trong xử lý chất thải tại Việt Nam.</t>
+          <t>b) Trục xuất người nước ngoài có hành vi vi phạm quy định tại điểm a, d khoản 3 Điều này.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 25</t>
+          <t>Điểm b Khoản 5 Điều 18</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>60/2016/NĐ-CP</t>
+          <t>63/2007/NĐ-CP</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111050</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14477</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2382,16 +2377,21 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Người nước ngoài thực hiện hành vi phát tán virus, phần mềm hoặc mã độc, hoặc thực hiện hành vi đánh bạc, tổ chức đánh bạc, môi giới mại dâm, lừa đảo, khủng bố trên môi trường mạng thì có thể bị áp dụng hình thức xử phạt bổ sung nào?»; nhãn cũ khong_dat question_ambiguous: Chấm lại 28/09 trên câu hỏi đã sửa. Vẫn mơ hồ sau khi sửa: điểm a (tịch thu tang vật) cũng áp dụng cho hành vi tại điểm a, d khoản 3, nên đáp án đủ là cả tịch thu tang vật và trục xuất). Câu hỏi loại trừ tịch thu tang vật (điểm a), còn lại trục xuất (điểm b). Câu sửa trong Excel được giữ trong nhãn human:excel</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:64f9e0b0-2c41-11f1-af75-3b2621a5f4cb:2017-07-02</t>
+          <t>vilextime:T1:provision:5e8c584c-543d-11f1-ae49-0120c8b0e422:2026-02-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2401,37 +2401,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực trẻ em, tổ chức đại diện tiếng nói, nguyện vọng của trẻ em có trách nhiệm đề xuất với Chính phủ nội dung gì theo định kỳ?</t>
+          <t>Nếu một doanh nghiệp gia công hàng xuất khẩu loại ra những bán thành phẩm sai quy cách và không dùng được như ban đầu, thì chúng được xác định là loại hàng gì theo quy định về thủ tục hải quan?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2017-07-02</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Điều 51. Trách nhiệm của tổ chức đại diện tiếng nói, nguyện vọng của trẻ em</t>
+          <t>2. Phế liệu, phế phẩm, phế thải của hàng hóa gia công, sản xuất xuất khẩu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2. Hằng năm, đề xuất với Chính phủ kế hoạch thực hiện nhiệm vụ đại diện tiếng nói, nguyện vọng của trẻ em và giám sát việc thực hiện ý kiến, nguyện vọng của trẻ em theo quy định tại điểm b khoản 4 Điều 91 Luật trẻ em.</t>
+          <t>b) Phế phẩm là thành phẩm, bán thành phẩm không đạt tiêu chuẩn kỹ thuật (quy cách, kích thước, phầm chất,...) bị loại bỏ từ quá trình gia công, sản xuất hàng hoá xuất khẩu, không đạt chất lượng đề xuất khẩu và không còn giá trị sử dụng ban đầu;</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 51</t>
+          <t>Điểm b Khoản 2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>56/2017/NĐ-CP</t>
+          <t>121/2025/TT-BTC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=121977</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6776a0a0-543a-11f1-9456-0b6fbb8f8274</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2445,17 +2445,26 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>citation_path_wrong,group_wrong</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Đơn vị là lời văn trích trong thông tư sửa đổi 121/2025/TT-BTC; citation thiếu Điều ('Điểm b Khoản 2'); thực chất là phiên bản mới của điều khoản thuộc thông tư bị sửa</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:67b6aac0-eada-11f0-9fe9-9f5f3d9c1c27#k16#b:2015-03-11</t>
+          <t>vilextime:T1:provision:5ed1beca-2c86-11f1-841a-7d89578d89e1:2013-05-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2465,37 +2474,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Theo quy định về cải tạo phương tiện giao thông cơ giới đường bộ, khối lượng toàn bộ cho phép tham gia giao thông của xe tải sau cải tạo bị giới hạn bởi những giá trị nào?</t>
+          <t>Khi công dân Việt Nam đã kết hôn ở nước ngoài muốn ghi vào sổ việc kết hôn, hồ sơ phải có bản sao giấy tờ nào do nước ngoài cấp?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
+          <t>2013-05-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16. Khối lượng toàn bộ cho phép tham gia giao thông của xe cơ giới sau cải tạo phải đảm bảo:</t>
+          <t>2. Hồ sơ ghi vào sổ việc kết hôn được lập thành 01 bộ, gồm các giấy tờ sau:</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>b) Đối với xe tải và xe chuyên dùng: Không lớn hơn giá trị của khối lượng toàn bộ theo thiết kế của nhà sản xuất và khối lượng toàn bộ cho phép tham gia giao thông theo quy định về tải trọng cầu đường.</t>
+          <t>b) Bản sao giấy tờ chứng nhận việc kết hôn do cơ quan có thẩm quyền của nước ngoài cấp;</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 16 Điều 4</t>
+          <t>Điểm b Khoản 2 Điều 17</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>85/2014/TT-BGTVT</t>
+          <t>24/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144776</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30386</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2509,17 +2518,26 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>NĐ 24/2013/NĐ-CP đã bị NĐ 123/2015/NĐ-CP thay thế (hiệu lực 01/01/2016); valid_to vẫn rỗng</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:680053d0-2768-11f1-bfbd-efc08bd225d4:2015-06-02</t>
+          <t>vilextime:T1:provision:624d3820-2dbe-11f1-ad11-45ab3867d967:2016-07-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2529,37 +2547,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Một Thẩm phán cần được điều động sang làm nhiệm vụ tại Tòa án nhân dân ở tỉnh khác thì ai có thẩm quyền quyết định việc điều động này?</t>
+          <t>Khi cần cập nhật danh mục chế phẩm sinh học dùng trong xử lý chất thải, Tổng cục Môi trường phải rà soát danh mục này với tần suất như thế nào?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2015-06-02</t>
+          <t>2016-07-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Điều 78. Điều động Thẩm phán</t>
+          <t>Điều 25. Danh mục chế phẩm sinh học trong xử lý chất thải tại Việt Nam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2. Chánh án Tòa án nhân dân tối cao quyết định điều động Thẩm phán từ Tòa án nhân dân này đến làm nhiệm vụ tại Tòa án nhân dân khác không cùng phạm vi thẩm quyền theo lãnh thổ hoặc không cùng một tỉnh, thành phố trực thuộc trung ương.</t>
+          <t>2. Định kỳ 06 tháng một lần, Tổng cục Môi trường có trách nhiệm rà soát, sửa đổi, bổ sung danh mục chế phẩm sinh học trong xử lý chất thải tại Việt Nam.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 78</t>
+          <t>Khoản 2 Điều 25</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>62/2014/QH13</t>
+          <t>60/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44169</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111050</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2573,25 +2591,18 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Luật Tổ chức TAND 62/2014/QH13 đã bị Luật Tổ chức TAND 34/2024/QH15 thay thế từ 01/01/2025; valid_to vẫn rỗng</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:6836992a-2e86-11f1-b466-61cabd0bcac0:2025-08-16</t>
+          <t>vilextime:T1:provision:64f9e0b0-2c41-11f1-af75-3b2621a5f4cb:2017-07-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2601,37 +2612,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trường hợp cơ sở khám bệnh, chữa bệnh không có đơn giá làm căn cứ thanh toán, quỹ bảo hiểm y tế thanh toán theo đơn giá nào?</t>
+          <t>Trong lĩnh vực trẻ em, tổ chức đại diện tiếng nói, nguyện vọng của trẻ em có trách nhiệm đề xuất với Chính phủ nội dung gì theo định kỳ?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trường hợp cơ sở khám bệnh, chữa bệnh là đơn vị sự nghiệp công lập tự bảo đảm chi thường xuyên và chi đầu tư, đơn vị sự nghiệp công lập tự bảo đảm chi thường xuyên và các cơ sở khám bệnh, chữa bệnh tư nhân không chọn áp dụng quy định của Luật Đấu thầu đối với mua thuốc, hóa chất, vật tư xét nghiệm, thiết bị y tế và thuộc trường hợp thanh toán theo quy định tại khoản 3 Điều 39 Nghị định này, quỹ bảo hiểm y tế thanh toán trong phạm vi được hưởng và mức hưởng của người tham gia bảo hiểm y tế theo đơn giá mua nhưng không cao hơn đơn giá theo kết quả lựa chọn nhà thầu còn hiệu lực tại thời điểm thanh toán của thuốc cùng tên thương mại, hãng sản xuất, xuất xứ, nồng độ, hàm lượng, đường dùng, cùng nhóm tiêu chí kỹ thuật, dạng bào chế, đơn vị tính hoặc của cùng hóa chất, vật tư xét nghiệm, thiết bị y tế có cùng hãng sản xuất, xuất xứ, tiêu chí kỹ thuật theo nguyên tắc và thứ tự ưu tiên như sau:</t>
+          <t>Điều 51. Trách nhiệm của tổ chức đại diện tiếng nói, nguyện vọng của trẻ em</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6. Trường hợp không có đơn giá quy định tại khoản 5 Điều này, quỹ bảo hiểm y tế thanh toán theo đơn giá trúng thầu của cơ sở khám bệnh, chữa bệnh của Nhà nước, kết quả mua sắm tập trung trên địa bàn tỉnh khác trên toàn quốc theo nguyên tắc quy định tại các điểm a, b và c khoản 5 Điều này.</t>
+          <t>2. Hằng năm, đề xuất với Chính phủ kế hoạch thực hiện nhiệm vụ đại diện tiếng nói, nguyện vọng của trẻ em và giám sát việc thực hiện ý kiến, nguyện vọng của trẻ em theo quy định tại điểm b khoản 4 Điều 91 Luật trẻ em.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Khoản 6 Điều 49</t>
+          <t>Khoản 2 Điều 51</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>188/2025/NĐ-CP</t>
+          <t>56/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179711</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=121977</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2641,33 +2652,22 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Khoản 4, 5, 6 cùng là 'trường hợp không có đơn giá ...' theo tầng; câu hỏi không chỉ ra tầng nào</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>5. Trường hợp không có đơn giá quy định tại khoản 4 Điều này, quỹ bảo hiểm y tế thanh toán theo đơn giá trúng thầu...</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:683af2ca-df3c-11f0-b581-0d9a21390744#k4:2005-07-19</t>
+          <t>vilextime:T1:provision:67b6aac0-eada-11f0-9fe9-9f5f3d9c1c27#k16#b:2015-03-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2677,37 +2677,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trường hợp các đơn vị thuộc Sở Tài chính cần thực hiện quy định pháp luật về thanh tra, Chánh Thanh tra Sở có nhiệm vụ gì đối với thủ trưởng các đơn vị đó?</t>
+          <t>Theo quy định về cải tạo phương tiện giao thông cơ giới đường bộ, khối lượng toàn bộ cho phép tham gia giao thông của xe tải sau cải tạo bị giới hạn bởi những giá trị nào?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2005-07-19</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Điều 15. Nhiệm vụ, quyền hạn của Chánh Thanh tra Sở</t>
+          <t>16. Khối lượng toàn bộ cho phép tham gia giao thông của xe cơ giới sau cải tạo phải đảm bảo:</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4. H­ướng dẫn, đôn đốc Thủ tr­ưởng tổ chức, đơn vị thuộc quyền quản lý của Sở Tài chính thực hiện các quy định pháp luật về thanh tra.</t>
+          <t>b) Đối với xe tải và xe chuyên dùng: Không lớn hơn giá trị của khối lượng toàn bộ theo thiết kế của nhà sản xuất và khối lượng toàn bộ cho phép tham gia giao thông theo quy định về tải trọng cầu đường.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 15</t>
+          <t>Điểm b Khoản 16 Điều 4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>81/2005/NĐ-CP</t>
+          <t>85/2014/TT-BGTVT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18116</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144776</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2717,33 +2717,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Khoản 6 cũng là nhiệm vụ của Chánh Thanh tra Sở đối với thủ trưởng đơn vị thuộc Sở về thực hiện pháp luật thanh tra</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>6. Thanh tra, kiểm tra trách nhiệm của Thủ trưởng tổ chức, đơn vị thuộc quyền quản lý của Sở Tài chính thực hiện...</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:69823b0a-df52-11f0-ac04-13973f36b963:2018-12-15</t>
+          <t>vilextime:T1:provision:680053d0-2768-11f1-bfbd-efc08bd225d4:2015-06-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2753,37 +2742,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pháp luật về quản lý an toàn trong hoạt động dầu khí quy định chương trình quản lý an toàn phải được thực hiện vào những thời điểm nào của công trình?</t>
+          <t>Một Thẩm phán cần được điều động sang làm nhiệm vụ tại Tòa án nhân dân ở tỉnh khác thì ai có thẩm quyền quyết định việc điều động này?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2018-12-15</t>
+          <t>2015-06-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1. Chương trình quản lý an toàn được thực hiện:</t>
+          <t>Điều 78. Điều động Thẩm phán</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>a) Trước khi thi công, xây dựng, lắp đặt.</t>
+          <t>2. Chánh án Tòa án nhân dân tối cao quyết định điều động Thẩm phán từ Tòa án nhân dân này đến làm nhiệm vụ tại Tòa án nhân dân khác không cùng phạm vi thẩm quyền theo lãnh thổ hoặc không cùng một tỉnh, thành phố trực thuộc trung ương.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 1 Điều 4</t>
+          <t>Khoản 2 Điều 78</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>40/2018/TT-BCT</t>
+          <t>62/2014/QH13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133210</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44169</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2793,33 +2782,30 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Hỏi 'những thời điểm nào' nhưng đáp án chỉ là điểm a; điểm b, c cũng là thời điểm thực hiện</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>b) Trước khi chạy thử, vận hành. c) Trước khi hoán cải...</t>
-        </is>
-      </c>
+          <t>Luật Tổ chức TAND 62/2014/QH13 đã bị Luật Tổ chức TAND 34/2024/QH15 thay thế từ 01/01/2025; valid_to vẫn rỗng</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:6c729f40-27ae-11f1-946b-a90cf85afed7:2024-12-11</t>
+          <t>vilextime:T1:provision:6836992a-2e86-11f1-b466-61cabd0bcac0:2025-08-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2829,37 +2815,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Theo quy định sửa đổi về tổ chức, hoạt động của quỹ xã hội, quỹ từ thiện, nghị định sửa đổi bắt đầu có hiệu lực từ ngày nào?</t>
+          <t>Nếu trên địa bàn tỉnh và cả các tỉnh giáp ranh đều không có giá trúng thầu hay kết quả mua sắm tập trung để làm căn cứ, quỹ bảo hiểm y tế thanh toán cho cơ sở khám bệnh, chữa bệnh theo đơn giá ở đâu?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Điều 4. Điều khoản thi hành</t>
+          <t>Trường hợp cơ sở khám bệnh, chữa bệnh là đơn vị sự nghiệp công lập tự bảo đảm chi thường xuyên và chi đầu tư, đơn vị sự nghiệp công lập tự bảo đảm chi thường xuyên và các cơ sở khám bệnh, chữa bệnh tư nhân không chọn áp dụng quy định của Luật Đấu thầu đối với mua thuốc, hóa chất, vật tư xét nghiệm, thiết bị y tế và thuộc trường hợp thanh toán theo quy định tại khoản 3 Điều 39 Nghị định này, quỹ bảo hiểm y tế thanh toán trong phạm vi được hưởng và mức hưởng của người tham gia bảo hiểm y tế theo đơn giá mua nhưng không cao hơn đơn giá theo kết quả lựa chọn nhà thầu còn hiệu lực tại thời điểm thanh toán của thuốc cùng tên thương mại, hãng sản xuất, xuất xứ, nồng độ, hàm lượng, đường dùng, cùng nhóm tiêu chí kỹ thuật, dạng bào chế, đơn vị tính hoặc của cùng hóa chất, vật tư xét nghiệm, thiết bị y tế có cùng hãng sản xuất, xuất xứ, tiêu chí kỹ thuật theo nguyên tắc và thứ tự ưu tiên như sau:</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1. Nghị định này có hiệu lực thi hành từ ngày 10 tháng 12 năm 2024.</t>
+          <t>6. Trường hợp không có đơn giá quy định tại khoản 5 Điều này, quỹ bảo hiểm y tế thanh toán theo đơn giá trúng thầu của cơ sở khám bệnh, chữa bệnh của Nhà nước, kết quả mua sắm tập trung trên địa bàn tỉnh khác trên toàn quốc theo nguyên tắc quy định tại các điểm a, b và c khoản 5 Điều này.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 4</t>
+          <t>Khoản 6 Điều 49</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>136/2024/NĐ-CP</t>
+          <t>188/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171283</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179711</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2876,18 +2862,19 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Điều khoản hiệu lực của chính nghị định sửa đổi, không phải quy phạm nội dung — cân nhắc loại khỏi T1</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cơ sở khám bệnh, chữa bệnh không có đơn giá làm căn cứ thanh toán, quỹ bảo hiểm y tế thanh toán theo đơn giá nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 4, 5, 6 cùng là 'trường hợp không có đơn giá ...' theo tầng; câu hỏi không chỉ ra tầng nào). Câu hỏi nêu tầng 'tỉnh và tỉnh giáp ranh đều không có' (khoản 5) nên chỉ khớp khoản 6</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:6f64a95a-2d44-11f1-b0d7-d1b0e48cb3c1:2024-08-16</t>
+          <t>vilextime:T1:provision:683af2ca-df3c-11f0-b581-0d9a21390744#k4:2005-07-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2897,37 +2884,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực chữ ký số chuyên dùng công vụ, cơ quan quản lý trực tiếp có trách nhiệm gì đối với chứng thư và thiết bị lưu khóa bí mật của thuê bao?</t>
+          <t>Chánh Thanh tra Sở Tài chính có nhiệm vụ hướng dẫn, đôn đốc ai thực hiện các quy định pháp luật về thanh tra?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2005-07-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Điều 37. Trách nhiệm của cơ quan, tổ chức quản lý trực tiếp</t>
+          <t>Điều 15. Nhiệm vụ, quyền hạn của Chánh Thanh tra Sở</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2. Tiếp nhận, bàn giao chứng thư chữ ký số chuyên dùng công vụ, thiết bị lưu khóa bí mật cho thuê bao và chịu trách nhiệm quản lý, sử dụng hiệu quả thiết bị lưu khóa bí mật, dịch vụ chứng thực chữ ký số chuyên dùng công vụ trong phạm vi quản lý.</t>
+          <t>4. H­ướng dẫn, đôn đốc Thủ tr­ưởng tổ chức, đơn vị thuộc quyền quản lý của Sở Tài chính thực hiện các quy định pháp luật về thanh tra.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 37</t>
+          <t>Khoản 4 Điều 15</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>68/2024/NĐ-CP</t>
+          <t>81/2005/NĐ-CP</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168208</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18116</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2937,33 +2924,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>'Trách nhiệm gì đối với chứng thư và thiết bị lưu khóa bí mật' cũng khớp khoản 3 (thu hồi thiết bị lưu khóa) và khoản 4 (hồ sơ chứng thư)</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>3. Thu hồi thiết bị lưu khóa bí mật của các cơ quan, tổ chức, cá nhân thuộc quyền...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp các đơn vị thuộc Sở Tài chính cần thực hiện quy định pháp luật về thanh tra, Chánh Thanh tra Sở có nhiệm vụ gì đối với thủ trưởng các đơn vị đó?»; nhãn cũ khong_dat question_ambiguous: Khoản 6 cũng là nhiệm vụ của Chánh Thanh tra Sở đối với thủ trưởng đơn vị thuộc Sở về thực hiện pháp luật thanh tra). Câu hỏi chốt 'hướng dẫn, đôn đốc', khác khoản 6</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:71e44436-df44-11f0-8400-ddc32f4bb673:2007-12-27</t>
+          <t>vilextime:T1:provision:69823b0a-df52-11f0-ac04-13973f36b963:2018-12-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2973,37 +2953,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thu hoạt động nghiệp vụ của Quỹ đầu tư phát triển địa phương bao gồm khoản thu nào liên quan đến việc chuyển nhượng dự án?</t>
+          <t>Trong giai đoạn xây dựng công trình dầu khí, chương trình quản lý an toàn phải được thực hiện vào thời điểm nào?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2007-12-27</t>
+          <t>2018-12-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.1 Thu hoạt động nghiệp vụ:</t>
+          <t>1. Chương trình quản lý an toàn được thực hiện:</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>d) Thu từ hoạt động chuyển nhượng dự án;</t>
+          <t>a) Trước khi thi công, xây dựng, lắp đặt.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 1</t>
+          <t>Điểm a Khoản 1 Điều 4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>139/2007/TT-BTC</t>
+          <t>40/2018/TT-BCT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=35287</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133210</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3017,25 +2997,22 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi đã sửa: giữ nguyên. Mục 1.1.d bị ghi thành 'Điểm d Khoản 1'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về quản lý an toàn trong hoạt động dầu khí quy định chương trình quản lý an toàn phải được thực hiện vào những thời điểm nào của công trình?»; nhãn cũ khong_dat question_ambiguous: Hỏi 'những thời điểm nào' nhưng đáp án chỉ là điểm a; điểm b, c cũng là thời điểm thực hiện). Câu hỏi chốt giai đoạn xây dựng, chỉ khớp điểm a</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:72b1f658-df3d-11f0-a299-9be2e7ae77e4:2008-01-09</t>
+          <t>vilextime:T1:provision:6c729f40-27ae-11f1-946b-a90cf85afed7:2024-12-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3045,33 +3022,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Khi Bộ Nông nghiệp và Phát triển nông thôn ban hành quyết định đính chính một quyết định trước đó, những người đứng đầu đơn vị nào phải chịu trách nhiệm thi hành?</t>
+          <t>Theo quy định sửa đổi về tổ chức, hoạt động của quỹ xã hội, quỹ từ thiện, nghị định sửa đổi bắt đầu có hiệu lực từ ngày nào?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2008-01-09</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Điều 4. Điều khoản thi hành</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Điều 3. Các ông Chánh Văn phòng, Cục trưởng Cục Trồng trọt, Vụ trưởng Vụ Pháp chế, Thủ trưởng các đơn vị thuộc Bộ chịu trách nhiệm thi hành Quyết định này./. TUQ. BỘ TRƯỞNG CHÁNH VĂN PHÒNG Bạch Quốc Khang</t>
+          <t>1. Nghị định này có hiệu lực thi hành từ ngày 10 tháng 12 năm 2024.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Điều 3</t>
+          <t>Khoản 1 Điều 4</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23/QĐ-BNN1</t>
+          <t>136/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=87507</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171283</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3081,37 +3062,26 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>doc_number_wrong</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Điều khoản thi hành của quyết định đính chính, không phải quy phạm; đáp án dính khối chữ ký người ký; số hiệu '23/QĐ-BNN1' lạ</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>TUQ. BỘ TRƯỞNG CHÁNH VĂN PHÒNG Bạch Quốc Khang</t>
-        </is>
-      </c>
+          <t>Điều khoản hiệu lực của chính nghị định sửa đổi, không phải quy phạm nội dung — cân nhắc loại khỏi T1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:735c35a0-2cbd-11f1-bc6a-b9d587c3623c:2022-02-16</t>
+          <t>vilextime:T1:provision:6f64a95a-2d44-11f1-b0d7-d1b0e48cb3c1:2024-08-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3121,37 +3091,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực ưu đãi người có công với cách mạng, việc xác định danh tính hài cốt liệt sĩ còn thiếu thông tin bằng phương pháp giám định được áp dụng như thế nào?</t>
+          <t>Trong lĩnh vực chữ ký số chuyên dùng công vụ, cơ quan quản lý trực tiếp có trách nhiệm gì trong việc nhận, giao chứng thư và thiết bị lưu khóa bí mật cho thuê bao và quản lý việc sử dụng chúng?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3. Xác định danh tính hài cốt liệt sĩ còn thiếu thông tin:</t>
+          <t>Điều 37. Trách nhiệm của cơ quan, tổ chức quản lý trực tiếp</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>b) Bằng phương pháp giám định ADN đối với hài cốt liệt sĩ khi quy tập vào nghĩa trang liệt sĩ và mộ liệt sĩ trong nghĩa trang liệt sĩ đối với trường hợp còn chưa đầy đủ hoặc chưa có thông tin.</t>
+          <t>2. Tiếp nhận, bàn giao chứng thư chữ ký số chuyên dùng công vụ, thiết bị lưu khóa bí mật cho thuê bao và chịu trách nhiệm quản lý, sử dụng hiệu quả thiết bị lưu khóa bí mật, dịch vụ chứng thực chữ ký số chuyên dùng công vụ trong phạm vi quản lý.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 3 Điều 138</t>
+          <t>Khoản 2 Điều 37</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>131/2021/NĐ-CP</t>
+          <t>68/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=153459</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168208</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3165,25 +3135,22 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 131/2021/NĐ-CP nhưng valid_to rỗng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực chữ ký số chuyên dùng công vụ, cơ quan quản lý trực tiếp có trách nhiệm gì đối với chứng thư và thiết bị lưu khóa bí mật của thuê bao?»; nhãn cũ khong_dat question_ambiguous: 'Trách nhiệm gì đối với chứng thư và thiết bị lưu khóa bí mật' cũng khớp khoản 3 (thu hồi thiết bị lưu khóa) và khoản 4 (hồ sơ chứng thư)). Câu hỏi chốt tiếp nhận, bàn giao cho thuê bao, khác khoản 3, 4</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:73af352e-df43-11f0-b0d7-116c6c341a79:2023-03-02</t>
+          <t>vilextime:T1:provision:71e44436-df44-11f0-8400-ddc32f4bb673:2007-12-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3193,37 +3160,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Theo quy định về chức danh nghề nghiệp viên chức quản lý dự án đường thủy, viên chức phải nắm vững những kiến thức gì về chủ trương, chính sách và quản lý ngành?</t>
+          <t>Thu hoạt động nghiệp vụ của Quỹ đầu tư phát triển địa phương bao gồm khoản thu nào liên quan đến việc chuyển nhượng dự án?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2007-12-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3. Tiêu chuẩn về năng lực chuyên môn, nghiệp vụ</t>
+          <t>1.1 Thu hoạt động nghiệp vụ:</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>a) Nắm vững chủ trương, đường lối của Đảng, chính sách, pháp luật của Nhà nước; kiến thức quản lý về ngành, chiến lược, quy hoạch, phát triển ngành đường thủy;</t>
+          <t>d) Thu từ hoạt động chuyển nhượng dự án;</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 3 Điều 5</t>
+          <t>Điểm d Khoản 1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>43/2022/TT-BGTVT</t>
+          <t>139/2007/TT-BTC</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159157</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=35287</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3233,29 +3200,30 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Thông tư có Điều 4–7 cho bốn hạng (I–IV), mỗi hạng có tiêu chuẩn năng lực tương tự; câu hỏi không nêu hạng</t>
+          <t>Chấm lại 28/09 trên câu hỏi đã sửa: giữ nguyên. Mục 1.1.d bị ghi thành 'Điểm d Khoản 1'</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:77166760-eae6-11f0-a6bf-d98cea2d8675#k2#a:2011-01-02</t>
+          <t>vilextime:T1:provision:72b1f658-df3d-11f0-a299-9be2e7ae77e4:2008-01-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3265,37 +3233,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Khi một ngân hàng tham gia Hệ thống thanh toán điện tử liên ngân hàng, tại Hội sở chính ngân hàng đó phải sử dụng những loại tài khoản nào?</t>
+          <t>Khi Bộ Nông nghiệp và Phát triển nông thôn ban hành quyết định đính chính một quyết định trước đó, những người đứng đầu đơn vị nào phải chịu trách nhiệm thi hành?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2011-01-02</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2. Đối với thành viên</t>
-        </is>
-      </c>
+          <t>2008-01-09</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>a) Tại Hội sở chính sử dụng các tài khoản: - Tài khoản thu hộ, chi hộ (mở tài khoản chi tiết cho từng đơn vị thành viên của mình có tham gia Hệ thống TTLNH); - Tài khoản thanh toán bù trừ; - Các tài khoản thích hợp khác liên quan (Tài khoản tiền gửi thanh toán của khách hàng, các tài khoản nội bộ khác); - Đối với các thành viên không có các chi nhánh thì không phải mở Tài khoản thu hộ, chi hộ.</t>
+          <t>Điều 3. Các ông Chánh Văn phòng, Cục trưởng Cục Trồng trọt, Vụ trưởng Vụ Pháp chế, Thủ trưởng các đơn vị thuộc Bộ chịu trách nhiệm thi hành Quyết định này./. TUQ. BỘ TRƯỞNG CHÁNH VĂN PHÒNG Bạch Quốc Khang</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 5</t>
+          <t>Điều 3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23/2010/TT-NHNN</t>
+          <t>23/QĐ-BNN1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25904</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=87507</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3305,21 +3269,42 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>doc_number_wrong</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Điều khoản thi hành của quyết định đính chính, không phải quy phạm; đáp án dính khối chữ ký người ký; số hiệu '23/QĐ-BNN1' lạ</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TUQ. BỘ TRƯỞNG CHÁNH VĂN PHÒNG Bạch Quốc Khang</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>loại lineage (other): Điều khoản thi hành của quyết định đính chính, không phải quy phạm; đáp án dính khối chữ ký người ký; số hiệu '23/QĐ-BNN1' lạ</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:77282ab0-3c74-11f1-b2ff-b7688e5b9a17:2018-01-02</t>
+          <t>vilextime:T1:provision:735c35a0-2cbd-11f1-bc6a-b9d587c3623c:2022-02-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3329,37 +3314,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trường hợp cần khai thác dữ liệu trên Hệ thống thông tin về tài sản công, cơ quan nào chịu trách nhiệm xây dựng và vận hành hệ thống này?</t>
+          <t>Trong lĩnh vực ưu đãi người có công với cách mạng, việc xác định danh tính hài cốt liệt sĩ còn thiếu thông tin bằng phương pháp giám định được áp dụng như thế nào?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Điều 126. Trách nhiệm xây dựng Hệ thống thông tin về tài sản công</t>
+          <t>3. Xác định danh tính hài cốt liệt sĩ còn thiếu thông tin:</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2. Bộ Tài chính có trách nhiệm tổ chức xây dựng, quản lý, vận hành, khai thác Hệ thống thông tin về tài sản công thuộc phạm vi quản lý.</t>
+          <t>b) Bằng phương pháp giám định ADN đối với hài cốt liệt sĩ khi quy tập vào nghĩa trang liệt sĩ và mộ liệt sĩ trong nghĩa trang liệt sĩ đối với trường hợp còn chưa đầy đủ hoặc chưa có thông tin.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 126</t>
+          <t>Điểm b Khoản 3 Điều 138</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>131/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122988</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=153459</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3373,17 +3358,26 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 131/2021/NĐ-CP nhưng valid_to rỗng</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:790c983e-eb89-11f0-bfbc-3b8923ed9a01#k3:2005-07-02</t>
+          <t>vilextime:T1:provision:73af352e-df43-11f0-b0d7-116c6c341a79:2023-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3393,37 +3387,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực cạnh tranh, người giám định phải chịu trách nhiệm pháp lý trong những trường hợp vi phạm nghĩa vụ giám định nào?</t>
+          <t>Theo quy định về chức danh nghề nghiệp viên chức quản lý dự án đường thủy hạng II, viên chức phải nắm vững những kiến thức gì về chủ trương, chính sách và quản lý ngành?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2005-07-02</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Điều 69. Người giám định</t>
+          <t>3. Tiêu chuẩn về năng lực chuyên môn, nghiệp vụ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3. Người giám định từ chối kết luận giám định mà không có lý do chính đáng hoặc kết luận giám định sai sự thật hoặc khi được cơ quan trưng cầu giám định triệu tập mà vắng mặt không có lý do chính đáng thì phải chịu trách nhiệm theo quy định của pháp luật.</t>
+          <t>a) Nắm vững chủ trương, đường lối của Đảng, chính sách, pháp luật của Nhà nước; kiến thức quản lý về ngành, chiến lược, quy hoạch, phát triển ngành đường thủy;</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 69</t>
+          <t>Điểm a Khoản 3 Điều 5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>27/2004/QH11</t>
+          <t>43/2022/TT-BGTVT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18566</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159157</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3438,16 +3432,21 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về chức danh nghề nghiệp viên chức quản lý dự án đường thủy, viên chức phải nắm vững những kiến thức gì về chủ trương, chính sách và quản lý ngành?»; nhãn cũ khong_dat question_ambiguous: Thông tư có Điều 4–7 cho bốn hạng (I–IV), mỗi hạng có tiêu chuẩn năng lực tương tự; câu hỏi không nêu hạng). Đã nêu hạng II</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:7955ccf0-335c-11f1-85de-b1296396b4f2:2004-09-02</t>
+          <t>vilextime:T1:provision:77166760-eae6-11f0-a6bf-d98cea2d8675#k2#a:2011-01-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3457,37 +3456,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Theo quy định về dự trữ quốc gia, pháp lệnh về lĩnh vực này điều chỉnh những hoạt động nào?</t>
+          <t>Khi một ngân hàng tham gia Hệ thống thanh toán điện tử liên ngân hàng, tại Hội sở chính ngân hàng đó phải sử dụng những loại tài khoản nào?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2004-09-02</t>
+          <t>2011-01-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chương I NHỮNG QUY ĐỊNH CHUNG</t>
+          <t>2. Đối với thành viên</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Điều 2. Phạm vi điều chỉnh Pháp lệnh này quy định việc xây dựng, tổ chức quản lý, điều hành và sử dụng dự trữ quốc gia.</t>
+          <t>a) Tại Hội sở chính sử dụng các tài khoản: - Tài khoản thu hộ, chi hộ (mở tài khoản chi tiết cho từng đơn vị thành viên của mình có tham gia Hệ thống TTLNH); - Tài khoản thanh toán bù trừ; - Các tài khoản thích hợp khác liên quan (Tài khoản tiền gửi thanh toán của khách hàng, các tài khoản nội bộ khác); - Đối với các thành viên không có các chi nhánh thì không phải mở Tài khoản thu hộ, chi hộ.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Điều 2</t>
+          <t>Điểm a Khoản 2 Điều 5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17/2004/PL-UBTVQH11</t>
+          <t>23/2010/TT-NHNN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19465</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25904</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3507,11 +3506,12 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:79b8bd90-227e-11f1-8c2a-e9c4dd423d40:2021-02-06</t>
+          <t>vilextime:T1:provision:77282ab0-3c74-11f1-b2ff-b7688e5b9a17:2018-01-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3521,37 +3521,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trường hợp Quỹ đầu tư phát triển địa phương nhận vốn ủy thác, khoản vốn này có được tính vào vốn hoạt động của Quỹ không và phải hạch toán ra sao?</t>
+          <t>Trường hợp cần khai thác dữ liệu trên Hệ thống thông tin về tài sản công, cơ quan nào chịu trách nhiệm xây dựng và vận hành hệ thống này?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2021-02-06</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CHẾ ĐỘ TÀI CHÍNH, KẾ TOÁN, KIỂM TOÁN , BÁO CÁO VÀ GIÁM SÁT, ĐÁNH GIÁ HIỆU QUẢ HOẠT ĐỘNG</t>
+          <t>Điều 126. Trách nhiệm xây dựng Hệ thống thông tin về tài sản công</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Điều 38. Vốn nhận ủy thác Vốn nhận ủy thác theo quy định tại Điều 32 Nghị định này không thuộc vốn hoạt động của Quỹ đầu tư phát triển địa phương và được hạch toán, quản lý tách bạch với vốn hoạt động của Quỹ.</t>
+          <t>2. Bộ Tài chính có trách nhiệm tổ chức xây dựng, quản lý, vận hành, khai thác Hệ thống thông tin về tài sản công thuộc phạm vi quản lý.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Điều 38</t>
+          <t>Khoản 2 Điều 126</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>147/2020/NĐ-CP</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146471</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122988</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3571,11 +3571,12 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:7a3161a2-e168-11f0-9abf-c32ecbcca391#k5:2011-09-16</t>
+          <t>vilextime:T1:provision:790c983e-eb89-11f0-bfbc-3b8923ed9a01#k3:2005-07-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3585,37 +3586,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Một chủ phương tiện chở khách du lịch trên đường thủy nội địa chở vượt số người được phép thì bị phạt tiền được tính như thế nào?</t>
+          <t>Trong lĩnh vực cạnh tranh, người giám định phải chịu trách nhiệm pháp lý trong những trường hợp vi phạm nghĩa vụ giám định nào?</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
+          <t>2005-07-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Điều 26. Vi phạm quy định về vận chuyển người, hành khách</t>
+          <t>Điều 69. Người giám định</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5. Phạt tiền từ 3 đến 5 lần giá vé trên mỗi hành khách chở vượt quá số người được phép chở đối với phương tiện vận tải hành khách theo tuyến cố định, phương tiện vận chuyển khách du lịch.</t>
+          <t>3. Người giám định từ chối kết luận giám định mà không có lý do chính đáng hoặc kết luận giám định sai sự thật hoặc khi được cơ quan trưng cầu giám định triệu tập mà vắng mặt không có lý do chính đáng thì phải chịu trách nhiệm theo quy định của pháp luật.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Khoản 5 Điều 26</t>
+          <t>Khoản 3 Điều 69</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>60/2011/NĐ-CP</t>
+          <t>27/2004/QH11</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26689</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18566</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3635,11 +3636,12 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:886734ba-eae9-11f0-bfb6-1b525bfe6ee3:2014-11-26</t>
+          <t>vilextime:T1:provision:7955ccf0-335c-11f1-85de-b1296396b4f2:2004-09-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3649,37 +3651,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Khoản thu lãi tiền gửi của Quỹ bảo lãnh tín dụng cho doanh nghiệp nhỏ và vừa được xác định ra sao trong các khoản thu về hoạt động tài chính của Quỹ?</t>
+          <t>Theo quy định về dự trữ quốc gia, pháp lệnh về lĩnh vực này điều chỉnh những hoạt động nào?</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
+          <t>2004-09-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2. Thu về hoạt động tài chính:</t>
+          <t>Chương I NHỮNG QUY ĐỊNH CHUNG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>a) Thu lãi tiền gửi tại Kho bạc Nhà nước, ngân hàng thương mại nơi Quỹ bảo lãnh tín dụng mở tài khoản;</t>
+          <t>Điều 2. Phạm vi điều chỉnh Pháp lệnh này quy định việc xây dựng, tổ chức quản lý, điều hành và sử dụng dự trữ quốc gia.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 13</t>
+          <t>Điều 2</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>147/2014/TT-BTC</t>
+          <t>17/2004/PL-UBTVQH11</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37527</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19465</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3693,25 +3695,18 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 147/2014/TT-BTC nhưng valid_to rỗng</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:894d1dfa-2c7e-11f1-bd6a-31308244359b:2017-04-27</t>
+          <t>vilextime:T1:provision:79b8bd90-227e-11f1-8c2a-e9c4dd423d40:2021-02-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3721,37 +3716,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pháp luật về tổ chức đào tạo trình độ trung cấp, cao đẳng quy định các khóa đã tuyển sinh trước khi văn bản mới có hiệu lực được đào tạo theo quy định nào?</t>
+          <t>Trường hợp Quỹ đầu tư phát triển địa phương nhận vốn ủy thác, khoản vốn này có được tính vào vốn hoạt động của Quỹ không và phải hạch toán ra sao?</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2017-04-27</t>
+          <t>2021-02-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Điều 37. Hiệu lực thi hành</t>
+          <t>CHẾ ĐỘ TÀI CHÍNH, KẾ TOÁN, KIỂM TOÁN , BÁO CÁO VÀ GIÁM SÁT, ĐÁNH GIÁ HIỆU QUẢ HOẠT ĐỘNG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2. Đối với các khóa tuyển sinh trước thời điểm Thông tư này có hiệu lực, các trường thực hiện việc tổ chức đào tạo theo các quy định hiện hành tại thời điểm bắt đầu khóa học cho đến khi kết thúc khóa học.</t>
+          <t>Điều 38. Vốn nhận ủy thác Vốn nhận ủy thác theo quy định tại Điều 32 Nghị định này không thuộc vốn hoạt động của Quỹ đầu tư phát triển địa phương và được hạch toán, quản lý tách bạch với vốn hoạt động của Quỹ.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 37</t>
+          <t>Điều 38</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>09/2017/TT-BLĐTBXH</t>
+          <t>147/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=120907</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146471</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3765,25 +3760,18 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Đây là điều khoản chuyển tiếp (khóa tuyển sinh trước ngày hiệu lực); có cạnh 'Văn bản được thay thế' trỏ vào TT 09/2017 nhưng valid_to rỗng</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:89b5eb36-df3b-11f0-be0a-a597416047b7:2007-02-15</t>
+          <t>vilextime:T1:provision:7a3161a2-e168-11f0-9abf-c32ecbcca391#k5:2011-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3793,37 +3781,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pháp luật về giải pháp điều hành kế hoạch kinh tế - xã hội và ngân sách nhà nước quy định Bộ Lao động - Thương binh và Xã hội phải làm gì đối với hệ thống bảo hiểm xã hội và chế độ bảo hiểm thất nghiệp?</t>
+          <t>Một chủ phương tiện chở khách du lịch trên đường thủy nội địa chở vượt số người được phép thì bị phạt tiền được tính như thế nào?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2007-02-15</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2. Bộ Lao động - Thương binh và Xã hội:</t>
+          <t>Điều 26. Vi phạm quy định về vận chuyển người, hành khách</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>d) Phối hợp với Bộ Y tế, Bộ Tài chính và các cơ quan liên quan đổi mới hệ thống bảo hiểm xã hội, đa dạng hóa hình thức bảo hiểm phù hợp với kinh tế thị trường. Trong quý II năm 2007, trình Chính phủ chế độ bảo hiểm thất nghiệp và các chính sách an sinh xã hội;</t>
+          <t>5. Phạt tiền từ 3 đến 5 lần giá vé trên mỗi hành khách chở vượt quá số người được phép chở đối với phương tiện vận tải hành khách theo tuyến cố định, phương tiện vận chuyển khách du lịch.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2</t>
+          <t>Khoản 5 Điều 26</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>03/2007/NQ-CP</t>
+          <t>60/2011/NĐ-CP</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14704</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26689</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3837,25 +3825,18 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Citation 'Điểm d Khoản 2' thiếu Phần/Mục (path 'Phần › Chương › Khoản 2')</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:89f4e824-df4d-11f0-947a-55d04134c924#k2#b:2016-01-02</t>
+          <t>vilextime:T1:provision:886734ba-eae9-11f0-bfb6-1b525bfe6ee3:2014-11-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3865,37 +3846,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Một đơn vị quân đội có xe cơ giới dùng cho mục đích quốc phòng thì có thuộc phạm vi áp dụng của quy định về kiểm định an toàn kỹ thuật phương tiện giao thông cơ giới đường bộ không, và vì sao?</t>
+          <t>Khoản thu lãi tiền gửi của Quỹ bảo lãnh tín dụng cho doanh nghiệp nhỏ và vừa được xác định ra sao trong các khoản thu về hoạt động tài chính của Quỹ?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2016-01-02</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2. Thông tư này không áp dụng đối với:</t>
+          <t>2. Thu về hoạt động tài chính:</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>b) Xe cơ giới của quân đội, công an sử dụng vào mục đích quốc phòng, an ninh.</t>
+          <t>a) Thu lãi tiền gửi tại Kho bạc Nhà nước, ngân hàng thương mại nơi Quỹ bảo lãnh tín dụng mở tài khoản;</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 1</t>
+          <t>Điểm a Khoản 2 Điều 13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>70/2015/TT-BGTVT</t>
+          <t>147/2014/TT-BTC</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111829</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37527</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3909,17 +3890,26 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 147/2014/TT-BTC nhưng valid_to rỗng</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:8b621ba6-df47-11f0-8be7-01dbfc483b14#k4:2015-12-06</t>
+          <t>vilextime:T1:provision:894d1dfa-2c7e-11f1-bd6a-31308244359b:2017-04-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3929,37 +3919,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Khi đánh giá người giữ chức danh quản lý tại công ty do Nhà nước nắm giữ toàn bộ vốn, hành vi vi phạm quy định nội bộ nào của doanh nghiệp là tiêu chí xác định không hoàn thành nhiệm vụ?</t>
+          <t>Pháp luật về tổ chức đào tạo trình độ trung cấp, cao đẳng quy định các khóa đã tuyển sinh trước khi văn bản mới có hiệu lực được đào tạo theo quy định nào?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2015-12-06</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Điều 17. Tiêu chí đánh giá không hoàn thành nhiệm vụ</t>
+          <t>Điều 37. Hiệu lực thi hành</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4. Vi phạm điều lệ, nội quy, quy chế của tập đoàn, tổng công ty, công ty;</t>
+          <t>2. Đối với các khóa tuyển sinh trước thời điểm Thông tư này có hiệu lực, các trường thực hiện việc tổ chức đào tạo theo các quy định hiện hành tại thời điểm bắt đầu khóa học cho đến khi kết thúc khóa học.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 17</t>
+          <t>Khoản 2 Điều 37</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>97/2015/NĐ-CP</t>
+          <t>09/2017/TT-BLĐTBXH</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=113098</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=120907</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3973,17 +3963,26 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Đây là điều khoản chuyển tiếp (khóa tuyển sinh trước ngày hiệu lực); có cạnh 'Văn bản được thay thế' trỏ vào TT 09/2017 nhưng valid_to rỗng</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:8be75e80-2d47-11f1-bbcc-93110808d881:2017-07-02</t>
+          <t>vilextime:T1:provision:89b5eb36-df3b-11f0-be0a-a597416047b7:2007-02-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3993,37 +3992,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pháp luật về chế độ làm việc của nhà giáo giáo dục nghề nghiệp quy định cách tính tiền lương dạy thêm giờ như thế nào?</t>
+          <t>Pháp luật về giải pháp điều hành kế hoạch kinh tế - xã hội và ngân sách nhà nước quy định Bộ Lao động - Thương binh và Xã hội phải làm gì đối với hệ thống bảo hiểm xã hội và chế độ bảo hiểm thất nghiệp?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2017-07-02</t>
+          <t>2007-02-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Điều 9. Chế độ dạy thêm giờ</t>
+          <t>2. Bộ Lao động - Thương binh và Xã hội:</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4. Cách tính trả lương dạy thêm giờ theo quy định hiện hành.</t>
+          <t>d) Phối hợp với Bộ Y tế, Bộ Tài chính và các cơ quan liên quan đổi mới hệ thống bảo hiểm xã hội, đa dạng hóa hình thức bảo hiểm phù hợp với kinh tế thị trường. Trong quý II năm 2007, trình Chính phủ chế độ bảo hiểm thất nghiệp và các chính sách an sinh xã hội;</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 9</t>
+          <t>Điểm d Khoản 2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>07/2017/TT-BLĐTBXH</t>
+          <t>03/2007/NQ-CP</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119515</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14704</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4033,33 +4032,30 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>unanswerable_as_asked</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Đáp án chỉ dẫn chiếu 'theo quy định hiện hành', không nêu cách tính mà câu hỏi hỏi</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>4. Cách tính trả lương dạy thêm giờ theo quy định hiện hành.</t>
-        </is>
-      </c>
+          <t>Citation 'Điểm d Khoản 2' thiếu Phần/Mục (path 'Phần › Chương › Khoản 2')</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:8c011130-ead1-11f0-b663-bff4a71ea78d:2012-11-21</t>
+          <t>vilextime:T1:provision:89f4e824-df4d-11f0-947a-55d04134c924#k2#b:2016-01-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4069,37 +4065,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pháp luật về xuất bản quy định cơ quan quản lý nhà nước được xử lý thế nào khi xuất bản phẩm đề nghị nhập khẩu không kinh doanh có dấu hiệu vi phạm pháp luật?</t>
+          <t>Một đơn vị quân đội có xe cơ giới dùng cho mục đích quốc phòng thì có thuộc phạm vi áp dụng của quy định về kiểm định an toàn kỹ thuật phương tiện giao thông cơ giới đường bộ không, và vì sao?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2012-11-21</t>
+          <t>2016-01-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Điều 41. Cấp giấy phép nhập khẩu xuất bản phẩm không kinh doanh</t>
+          <t>2. Thông tư này không áp dụng đối với:</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5. Trường hợp phát hiện xuất bản phẩm đề nghị nhập khẩu có dấu hiệu vi phạm pháp luật Việt Nam thì cơ quan quản lý nhà nước về hoạt động xuất bản có quyền từ chối cấp giấy phép nhập khẩu hoặc yêu cầu cơ quan, tổ chức, cá nhân đề nghị cấp giấy phép nhập khẩu cung cấp một bản xuất bản phẩm để tổ chức thẩm định nội dung làm cơ sở cho việc quyết định cấp giấy phép nhập khẩu.</t>
+          <t>b) Xe cơ giới của quân đội, công an sử dụng vào mục đích quốc phòng, an ninh.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Khoản 5 Điều 41</t>
+          <t>Điểm b Khoản 2 Điều 1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>19/2012/QhH13</t>
+          <t>70/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=113342</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111829</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4113,25 +4109,18 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>doc_number_wrong</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Số hiệu ghi sai '19/2012/QhH13' (đúng: 19/2012/QH13)</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:8c493910-243d-11f1-beb6-b7db053a95e9:2024-08-02</t>
+          <t>vilextime:T1:provision:8b621ba6-df47-11f0-8be7-01dbfc483b14#k4:2015-12-06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4141,37 +4130,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Trách nhiệm chỉ đạo các cơ quan thực hiện xây dựng bảng giá đất lần đầu được xác định ra sao trong quy định về giá đất?</t>
+          <t>Khi đánh giá người giữ chức danh quản lý tại công ty do Nhà nước nắm giữ toàn bộ vốn, hành vi vi phạm quy định nội bộ nào của doanh nghiệp là tiêu chí xác định không hoàn thành nhiệm vụ?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2015-12-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Điều 13. Chuẩn bị xây dựng bảng giá đất Việc chuẩn bị xây dựng bảng giá đất lần đầu để công bố và áp dụng từ ngày 01 tháng 01 năm 2026 thực hiện như sau:</t>
+          <t>Điều 17. Tiêu chí đánh giá không hoàn thành nhiệm vụ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4. Ủy ban nhân dân cấp tỉnh chỉ đạo các sở, ngành, Ủy ban nhân dân cấp huyện, Ban quản lý khu công nghệ cao, khu kinh tế (nếu có) để thực hiện xây dựng bảng giá đất.</t>
+          <t>4. Vi phạm điều lệ, nội quy, quy chế của tập đoàn, tổng công ty, công ty;</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 13</t>
+          <t>Khoản 4 Điều 17</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>71/2024/NĐ-CP</t>
+          <t>97/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168381</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=113098</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4185,25 +4174,18 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 71/2024/NĐ-CP nhưng valid_to rỗng</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:943871ea-df50-11f0-9561-3d5192b5741d:2006-10-02</t>
+          <t>vilextime:T1:provision:8be75e80-2d47-11f1-bbcc-93110808d881:2017-07-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4213,37 +4195,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Theo quy định về dự án, công trình quan trọng quốc gia, khi thẩm tra các thông số cơ bản của dự án thì cơ quan thẩm tra phải xem xét những yếu tố nào?</t>
+          <t>Pháp luật về chế độ làm việc của nhà giáo giáo dục nghề nghiệp quy định việc trả lương dạy thêm giờ được tính theo căn cứ nào?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2006-10-02</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3. Cơ quan thẩm tra tiến hành thẩm tra những nội dung chủ yếu sau đây:</t>
+          <t>Điều 9. Chế độ dạy thêm giờ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>đ) Những thông số cơ bản của dự án, công trình bao gồm: quy mô; hình thức đầu tư; địa điểm; diện tích đất cần sử dụng; thời gian, tiến độ thực hiện; phương án lựa chọn công nghệ; giải pháp bảo vệ môi trường; nguồn vốn, khả năng thu hồi vốn và trả nợ vốn vay;</t>
+          <t>4. Cách tính trả lương dạy thêm giờ theo quy định hiện hành.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Điểm đ Khoản 3 Điều 4</t>
+          <t>Khoản 4 Điều 9</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>66/2006/QH11</t>
+          <t>07/2017/TT-BLĐTBXH</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=15828</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119515</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4258,16 +4240,21 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về chế độ làm việc của nhà giáo giáo dục nghề nghiệp quy định cách tính tiền lương dạy thêm giờ như thế nào?»; nhãn cũ khong_dat unanswerable_as_asked: Đáp án chỉ dẫn chiếu 'theo quy định hiện hành', không nêu cách tính mà câu hỏi hỏi). Câu hỏi hỏi căn cứ tính; đáp án chỉ dẫn chiếu quy định hiện hành nhưng trả lời đúng điều được hỏi</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:96b599ac-df4b-11f0-bca0-8df03e56d065:2012-08-11</t>
+          <t>vilextime:T1:provision:8c011130-ead1-11f0-b663-bff4a71ea78d:2012-11-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4277,37 +4264,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Một lãnh đạo cấp cao đi công tác ngắn hạn ở nước ngoài bằng ngân sách nhà nước thì những chức danh nào được thanh toán công tác phí theo tiêu chuẩn cao nhất?</t>
+          <t>Pháp luật về xuất bản quy định cơ quan quản lý nhà nước được xử lý thế nào khi xuất bản phẩm đề nghị nhập khẩu không kinh doanh có dấu hiệu vi phạm pháp luật?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2012-08-11</t>
+          <t>2012-11-21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1. Tiêu chuẩn A: Để thanh toán cho các cán bộ, công chức thuộc các chức danh lãnh đạo sau đây:</t>
+          <t>Điều 41. Cấp giấy phép nhập khẩu xuất bản phẩm không kinh doanh</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>a) Tổng bí thư Đảng, Chủ tịch nước, Phó Chủ tịch nước, Chủ tịch Quốc hội, Phó Chủ tịch Quốc hội, Thủ tướng Chính phủ, Phó Thủ tướng Chính phủ, Uỷ viên Bộ Chính trị.</t>
+          <t>5. Trường hợp phát hiện xuất bản phẩm đề nghị nhập khẩu có dấu hiệu vi phạm pháp luật Việt Nam thì cơ quan quản lý nhà nước về hoạt động xuất bản có quyền từ chối cấp giấy phép nhập khẩu hoặc yêu cầu cơ quan, tổ chức, cá nhân đề nghị cấp giấy phép nhập khẩu cung cấp một bản xuất bản phẩm để tổ chức thẩm định nội dung làm cơ sở cho việc quyết định cấp giấy phép nhập khẩu.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 1 Điều 2</t>
+          <t>Khoản 5 Điều 41</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>102/2012/TT-BTC</t>
+          <t>19/2012/QhH13</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27620</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=113342</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4317,33 +4304,30 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>doc_number_wrong</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn A (cao nhất) gồm cả điểm a, b, c; đáp án chỉ là điểm a</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>b) Cán bộ được hưởng Bảng lương chức vụ lãnh đạo của Nhà nước ... c) Cán bộ lãnh đạo hưởng bảng lương theo Nghị quyết số 730/NQ-UBTVQH...</t>
-        </is>
-      </c>
+          <t>Số hiệu ghi sai '19/2012/QhH13' (đúng: 19/2012/QH13)</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:973e053a-df5a-11f0-91c4-b1f697698700#k2#a:2017-05-02</t>
+          <t>vilextime:T1:provision:8c493910-243d-11f1-beb6-b7db053a95e9:2024-08-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4353,37 +4337,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chi phí lập, thẩm tra quy trình bảo trì công trình xây dựng được xác định ra sao trong chi phí thiết kế?</t>
+          <t>Trách nhiệm chỉ đạo các cơ quan thực hiện xây dựng bảng giá đất lần đầu được xác định ra sao trong quy định về giá đất?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2017-05-02</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2. Các loại chi phí bảo trì công trình xây dựng quy định tại Điều 4 Thông tư này được xác định như sau:</t>
+          <t>Điều 13. Chuẩn bị xây dựng bảng giá đất Việc chuẩn bị xây dựng bảng giá đất lần đầu để công bố và áp dụng từ ngày 01 tháng 01 năm 2026 thực hiện như sau:</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>a) Chi phí lập, thẩm tra quy trình bảo trì công trình xây dựng được xác định trong chi phí thiết kế kỹ thuật (đối với công trình yêu cầu thiết kế 3 bước) hoặc chi phí thiết kế bản vẽ thi công (đối với công trình yêu cầu thiết kế 2 bước và 1 bước). Chi phí thẩm tra quy trình bảo trì công trình xây dựng được xác định trong chi phí thẩm tra thiết kế công trình. Trường hợp công trình xây dựng đang được đầu tư xây dựng hoặc đã được đưa vào sử dụng nhưng chưa có quy trình bảo trì thì chủ đầu tư, chủ sở hữu hoặc người quản lý sử dụng công trình phải tổ chức lập quy trình bảo trì cho công trình. Chi phí các công việc này được lập dự toán theo phương pháp khối lượng và đơn giá như hướng dẫn tại điểm b Khoản 1 Điều này.</t>
+          <t>4. Ủy ban nhân dân cấp tỉnh chỉ đạo các sở, ngành, Ủy ban nhân dân cấp huyện, Ban quản lý khu công nghệ cao, khu kinh tế (nếu có) để thực hiện xây dựng bảng giá đất.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 5</t>
+          <t>Khoản 4 Điều 13</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>03/2017/TT-BXD</t>
+          <t>71/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=123072</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168381</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4397,17 +4381,26 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 71/2024/NĐ-CP nhưng valid_to rỗng</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:9e092383-44c5-47d8-94fe-4379606bf0ec:2026-07-02</t>
+          <t>vilextime:T1:provision:943871ea-df50-11f0-9561-3d5192b5741d:2006-10-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4417,37 +4410,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực cảng hàng không, hồ sơ đề nghị phê duyệt sửa đổi tài liệu khai thác công trình phải kèm theo tài liệu gì để chứng minh nội dung sửa đổi?</t>
+          <t>Theo quy định về dự án, công trình quan trọng quốc gia, khi thẩm tra các thông số cơ bản của dự án thì cơ quan thẩm tra phải xem xét những yếu tố nào?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2006-10-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5. Người khai thác công trình gửi 01 bộ hồ sơ đề nghị phê duyệt sửa đổi, bổ sung tài liệu khai thác công trình đến Cục Hàng không Việt Nam. Hồ sơ đề nghị gồm:</t>
+          <t>3. Cơ quan thẩm tra tiến hành thẩm tra những nội dung chủ yếu sau đây:</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>c) Bản sao hoặc bản sao điện tử tài liệu chứng minh nội dung sửa đổi, bổ sung.</t>
+          <t>đ) Những thông số cơ bản của dự án, công trình bao gồm: quy mô; hình thức đầu tư; địa điểm; diện tích đất cần sử dụng; thời gian, tiến độ thực hiện; phương án lựa chọn công nghệ; giải pháp bảo vệ môi trường; nguồn vốn, khả năng thu hồi vốn và trả nợ vốn vay;</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 5</t>
+          <t>Điểm đ Khoản 3 Điều 4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>205/2026/NĐ-CP</t>
+          <t>66/2006/QH11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=49828ac0-6e5a-11f1-b670-d3ec94724b75</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=15828</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4461,25 +4454,18 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Citation 'Điểm c Khoản 5' thiếu Điều (path 'Chương V › Mục 2 › Khoản 5')</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:a138d600-4dd7-11f1-aedf-29a605bed581:2012-12-29</t>
+          <t>vilextime:T1:provision:96b599ac-df4b-11f0-bca0-8df03e56d065:2012-08-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4489,37 +4475,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Khi kết thúc năm tài chính, ngân hàng thương mại nhà nước thực hiện hỗ trợ lãi suất giảm tổn thất sau thu hoạch phải gửi hồ sơ đề nghị quyết toán cho cơ quan nào và trong thời hạn bao lâu?</t>
+          <t>Trong tiêu chuẩn A thanh toán công tác phí ngắn hạn ở nước ngoài, những chức danh lãnh đạo nào được liệt kê đích danh mà không xác định theo bảng lương?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2012-12-29</t>
+          <t>2012-08-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4. Quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất:</t>
+          <t>1. Tiêu chuẩn A: Để thanh toán cho các cán bộ, công chức thuộc các chức danh lãnh đạo sau đây:</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>4.1. Chậm nhất trong vòng 90 ngày kể từ ngày kết thúc năm tài chính, các ngân hàng thương mại nhà nước phải gửi hồ sơ đề nghị quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất cho Bộ Tài chính. Đối với các trường hợp hồ sơ không hợp lệ, Bộ Tài chính có trách nhiệm thông báo bằng văn bản cho các ngân hàng thương mại nhà nước trong thời hạn 10 ngày.</t>
+          <t>a) Tổng bí thư Đảng, Chủ tịch nước, Phó Chủ tịch nước, Chủ tịch Quốc hội, Phó Chủ tịch Quốc hội, Thủ tướng Chính phủ, Phó Thủ tướng Chính phủ, Uỷ viên Bộ Chính trị.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Điểm 4 Khoản 4 Điều 4</t>
+          <t>Điểm a Khoản 1 Điều 2</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>188/2012/TT-BTC</t>
+          <t>102/2012/TT-BTC</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27889</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27620</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4533,25 +4519,22 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Mục 4.1 bị ghi thành 'Điểm 4 Khoản 4 Điều 4'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một lãnh đạo cấp cao đi công tác ngắn hạn ở nước ngoài bằng ngân sách nhà nước thì những chức danh nào được thanh toán công tác phí theo tiêu chuẩn cao nhất?»; nhãn cũ khong_dat question_ambiguous: Tiêu chuẩn A (cao nhất) gồm cả điểm a, b, c; đáp án chỉ là điểm a). Câu hỏi chốt các chức danh liệt kê đích danh, chỉ khớp điểm a</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:a1986eb2-df46-11f0-9b1e-cd51ca7f41d6#k1#b:2010-01-02</t>
+          <t>vilextime:T1:provision:973e053a-df5a-11f0-91c4-b1f697698700#k2#a:2017-05-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4561,37 +4544,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yêu cầu về tiêu chuẩn, định mức và khả năng ngân sách khi mua sắm tài sản chuyên dùng tại đơn vị vũ trang nhân dân được xác định ra sao?</t>
+          <t>Chi phí lập, thẩm tra quy trình bảo trì công trình xây dựng được xác định ra sao trong chi phí thiết kế?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2010-01-02</t>
+          <t>2017-05-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1. Việc mua sắm tài sản chuyên dùng phải phù hợp với nhu cầu sử dụng và đảm bảo các yêu cầu sau đây:</t>
+          <t>2. Các loại chi phí bảo trì công trình xây dựng quy định tại Điều 4 Thông tư này được xác định như sau:</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>b) Phù hợp với tiêu chuẩn, định mức, biên chế tài sản và khả năng của ngân sách nhà nước.</t>
+          <t>a) Chi phí lập, thẩm tra quy trình bảo trì công trình xây dựng được xác định trong chi phí thiết kế kỹ thuật (đối với công trình yêu cầu thiết kế 3 bước) hoặc chi phí thiết kế bản vẽ thi công (đối với công trình yêu cầu thiết kế 2 bước và 1 bước). Chi phí thẩm tra quy trình bảo trì công trình xây dựng được xác định trong chi phí thẩm tra thiết kế công trình. Trường hợp công trình xây dựng đang được đầu tư xây dựng hoặc đã được đưa vào sử dụng nhưng chưa có quy trình bảo trì thì chủ đầu tư, chủ sở hữu hoặc người quản lý sử dụng công trình phải tổ chức lập quy trình bảo trì cho công trình. Chi phí các công việc này được lập dự toán theo phương pháp khối lượng và đơn giá như hướng dẫn tại điểm b Khoản 1 Điều này.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 24</t>
+          <t>Điểm a Khoản 2 Điều 5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>106/2009/NĐ-CP</t>
+          <t>03/2017/TT-BXD</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23816</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=123072</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4601,33 +4584,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>question_leaks</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Câu hỏi nêu sẵn 'tiêu chuẩn, định mức và khả năng ngân sách', đáp án chỉ là 'phù hợp với' chính các yếu tố đó</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>b) Phù hợp với tiêu chuẩn, định mức, biên chế tài sản và khả năng của ngân sách nhà nước.</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:a710acd8-2690-11f1-a009-811809d75813:2006-01-02</t>
+          <t>vilextime:T1:provision:9e092383-44c5-47d8-94fe-4379606bf0ec:2026-07-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4637,37 +4609,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pháp luật về kiểm tra sau thông quan quy định việc kiểm tra đối với doanh nghiệp chuyển phát nhanh thay mặt chủ hàng làm thủ tục hải quan như thế nào?</t>
+          <t>Trong lĩnh vực cảng hàng không, hồ sơ đề nghị phê duyệt sửa đổi tài liệu khai thác công trình phải kèm theo tài liệu gì để chứng minh nội dung sửa đổi?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2006-01-02</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2. Kiểm tra sau thông quan được thực hiện thông qua việc kiểm tra hồ sơ hải quan, các chứng từ kế toán, sổ kế toán, báo cáo tài chính và các chứng từ có liên quan đến hàng hoá xuất khẩu, nhập khẩu; trong trường hợp cần thiết và đủ điều kiện thì kiểm tra hàng hoá nhập khẩu đã được thông quan của các tổ chức, cá nhân (gọi là đơn vị được kiểm tra) sau đây:</t>
+          <t>5. Người khai thác công trình gửi 01 bộ hồ sơ đề nghị phê duyệt sửa đổi, bổ sung tài liệu khai thác công trình đến Cục Hàng không Việt Nam. Hồ sơ đề nghị gồm:</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>đ) Doanh nghiệp cung cấp dịch vụ bưu chính, dịch vụ chuyển phát nhanh quốc tế thay mặt chủ hàng làm thủ tục hải quan đối với hàng hoá xuất khẩu, nhập khẩu theo đường bưu chính, dịch vụ chuyển phát nhanh quốc tế.</t>
+          <t>c) Bản sao hoặc bản sao điện tử tài liệu chứng minh nội dung sửa đổi, bổ sung.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Điểm đ Khoản 2</t>
+          <t>Điểm c Khoản 5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>114/2005/TT-BTC</t>
+          <t>205/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16933</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=49828ac0-6e5a-11f1-b670-d3ec94724b75</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4688,18 +4660,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Citation 'Điểm đ Khoản 2' thiếu Phần A</t>
+          <t>Citation 'Điểm c Khoản 5' thiếu Điều (path 'Chương V › Mục 2 › Khoản 5')</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:a7be8856-df43-11f0-bc93-d9f1eab2568f:2018-07-02</t>
+          <t>vilextime:T1:provision:a0f2ca30-2d47-11f1-82a0-cbd4e794e6b7:2017-01-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4709,37 +4682,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp kinh doanh kết cấu hạ tầng đường sắt cung cấp thông tin cảnh giới tại điểm giao cắt với đường bộ thì hoạt động này được hiểu như thế nào?</t>
+          <t>Trong lĩnh vực bảo đảm an toàn thực phẩm đối với dầu thực vật, cơ sở sản xuất dầu thực vật được hiểu là cơ sở thực hiện những hoạt động nào?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2017-01-21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Điều 3. Giải thích từ ngữ</t>
+          <t>Điều 16. Bảo đảm an toàn thực phẩm đối với cơ sở sản xuất, kinh doanh dầu thực vật</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1. Cung cấp thông tin hỗ trợ cảnh giới tại các điểm giao cắt giữa đường bộ, đường sắt là việc cung cấp thông tin của doanh nghiệp kinh doanh kết cấu hạ tầng đường sắt, chủ sở hữu đường sắt chuyên dùng thuộc phạm vi quản lý cho người cảnh giới để thực hiện nhiệm vụ tại vị trí cần cảnh giới.</t>
+          <t>2. Cơ sở sản xuất dầu thực vật tại mục 5 Chương VI Nghị định số 77/2016/NĐ-CP là cơ sở thực hiện một, một số hoặc toàn bộ các hoạt động sơ chế, chế biến (làm sạch, chưng sấy, ép, trích ly, tinh luyện), bao gói, bảo quản để tạo ra dầu thực vật thành phẩm.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 3</t>
+          <t>Khoản 2 Điều 16</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>28/2018/TT-BGTVT</t>
+          <t>27/2016/TT-BCT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=129226</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=116451</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4759,11 +4732,12 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:a82e7fd0-2f43-11f1-845f-b378206c5594:2010-08-11</t>
+          <t>vilextime:T1:provision:a138d600-4dd7-11f1-aedf-29a605bed581:2012-12-29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4773,37 +4747,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Một tổ chức đăng ký công nhận phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen thì phải nộp tài liệu thuyết minh năng lực theo mẫu của cơ quan nào?</t>
+          <t>Khi kết thúc năm tài chính, ngân hàng thương mại nhà nước thực hiện hỗ trợ lãi suất giảm tổn thất sau thu hoạch phải gửi hồ sơ đề nghị quyết toán cho cơ quan nào và trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2010-08-11</t>
+          <t>2012-12-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2. Tổ chức đăng ký công nhận Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen phải nộp ba (03) bộ hồ sơ cho Bộ Khoa học và Công nghệ. Hồ sơ bao gồm:</t>
+          <t>4. Quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất:</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>c) Thuyết minh về năng lực của Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen theo mẫu của Bộ Khoa học và Công nghệ;</t>
+          <t>4.1. Chậm nhất trong vòng 90 ngày kể từ ngày kết thúc năm tài chính, các ngân hàng thương mại nhà nước phải gửi hồ sơ đề nghị quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất cho Bộ Tài chính. Đối với các trường hợp hồ sơ không hợp lệ, Bộ Tài chính có trách nhiệm thông báo bằng văn bản cho các ngân hàng thương mại nhà nước trong thời hạn 10 ngày.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2 Điều 12</t>
+          <t>Điểm 4 Khoản 4 Điều 4</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>69/2010/NĐ-CP</t>
+          <t>188/2012/TT-BTC</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25420</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27889</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4817,17 +4791,26 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Mục 4.1 bị ghi thành 'Điểm 4 Khoản 4 Điều 4'</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:ac56527c-eb73-11f0-9b3a-07ebd665db64:2014-10-25</t>
+          <t>vilextime:T1:provision:a1986eb2-df46-11f0-9b1e-cd51ca7f41d6#k1#b:2010-01-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4837,37 +4820,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Trường hợp nội dung Chứng nhận tham gia bảo hiểm tiền gửi của một tổ chức tín dụng thay đổi, tổ chức đó phải đề nghị cấp lại trong thời hạn bao lâu?</t>
+          <t>Việc mua sắm tài sản chuyên dùng tại đơn vị vũ trang nhân dân, ngoài việc phù hợp với nhu cầu sử dụng, còn phải phù hợp với những yếu tố nào?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2010-01-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Điều 3. Nội dung Chứng nhận tham gia bảo hiểm tiền gửi</t>
+          <t>1. Việc mua sắm tài sản chuyên dùng phải phù hợp với nhu cầu sử dụng và đảm bảo các yêu cầu sau đây:</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2. Trong thời hạn 15 ngày kể từ ngày có sự thay đổi nội dung Chứng nhận tham gia bảo hiểm tiền gửi quy định tại điểm b khoản 1 Điều này, tổ chức tham gia bảo hiểm tiền gửi thực hiện việc đề nghị cấp lại Chứng nhận tham gia bảo hiểm tiền gửi theo quy định tại khoản 3 Điều 7 Nghị định số 68/2013/NĐ-CP ngày 28 tháng 6 năm 2013 của Chính phủ quy định chi tiết và hướng dẫn thi hành Luật Bảo hiểm tiền gửi.</t>
+          <t>b) Phù hợp với tiêu chuẩn, định mức, biên chế tài sản và khả năng của ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 3</t>
+          <t>Điểm b Khoản 1 Điều 24</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>24/2014/TT-NHNN</t>
+          <t>106/2009/NĐ-CP</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44192</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23816</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4884,18 +4867,19 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi đã sửa: giữ nguyên.</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Yêu cầu về tiêu chuẩn, định mức và khả năng ngân sách khi mua sắm tài sản chuyên dùng tại đơn vị vũ trang nhân dân được xác định ra sao?»; nhãn cũ khong_dat question_leaks: Câu hỏi nêu sẵn 'tiêu chuẩn, định mức và khả năng ngân sách', đáp án chỉ là 'phù hợp với' chính các yếu tố đó). Câu hỏi không còn nêu sẵn đáp án</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:ac625f20-eadf-11f0-bd15-e99c4454aa60#k15:2009-12-23</t>
+          <t>vilextime:T1:provision:a710acd8-2690-11f1-a009-811809d75813:2006-01-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4905,37 +4889,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Một cơ quan chuyên trách về tôn giáo thuộc Bộ Nội vụ thì phải thực hiện công tác cải cách hành chính theo căn cứ nào?</t>
+          <t>Pháp luật về kiểm tra sau thông quan quy định việc kiểm tra đối với doanh nghiệp chuyển phát nhanh thay mặt chủ hàng làm thủ tục hải quan như thế nào?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2009-12-23</t>
+          <t>2006-01-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Điều 2. Nhiệm vụ và quyền hạn</t>
+          <t>2. Kiểm tra sau thông quan được thực hiện thông qua việc kiểm tra hồ sơ hải quan, các chứng từ kế toán, sổ kế toán, báo cáo tài chính và các chứng từ có liên quan đến hàng hoá xuất khẩu, nhập khẩu; trong trường hợp cần thiết và đủ điều kiện thì kiểm tra hàng hoá nhập khẩu đã được thông quan của các tổ chức, cá nhân (gọi là đơn vị được kiểm tra) sau đây:</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>15. Thực hiện công tác cải cách hành chính theo mục tiêu và nội dung chương trình cải cách hành chính nhà nước đã được cấp có thẩm quyền phê duyệt.</t>
+          <t>đ) Doanh nghiệp cung cấp dịch vụ bưu chính, dịch vụ chuyển phát nhanh quốc tế thay mặt chủ hàng làm thủ tục hải quan đối với hàng hoá xuất khẩu, nhập khẩu theo đường bưu chính, dịch vụ chuyển phát nhanh quốc tế.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Khoản 15 Điều 2</t>
+          <t>Điểm đ Khoản 2</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>134/2009/QĐ-TTg</t>
+          <t>114/2005/TT-BTC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23838</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16933</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4949,17 +4933,26 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Citation 'Điểm đ Khoản 2' thiếu Phần A</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:ad505bc0-30b3-11f1-a005-81dac526b4c8:2026-02-17</t>
+          <t>vilextime:T1:provision:a7be8856-df43-11f0-bc93-d9f1eab2568f:2018-07-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4969,37 +4962,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Các đơn vị kế toán phụ thuộc của Ngân hàng Nhà nước được xác định ra sao trong quy định về chế độ báo cáo tài chính của Ngân hàng Nhà nước Việt Nam?</t>
+          <t>Một doanh nghiệp kinh doanh kết cấu hạ tầng đường sắt cung cấp thông tin cảnh giới tại điểm giao cắt với đường bộ thì hoạt động này được hiểu như thế nào?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3. Các đơn vị thuộc NHNN bao gồm: các đơn vị NHNN và các đơn vị sự nghiệp thuộc NHNN (không bao gồm các đơn vị trực tiếp nhận, quyết toán kinh phí với Ngân sách Nhà nước), cụ thể:</t>
+          <t>Điều 3. Giải thích từ ngữ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>a) Các đơn vị NHNN là các đơn vị kế toán phụ thuộc, bao gồm: NHNN Chi nhánh Khu vực; Vụ Tài chính - Kế toán; Sở Giao dịch; Văn phòng; Cục Quản lý ngoại hối; Cục Công nghệ thông tin; Cục Phát hành và Kho quỹ; Chi cục Công nghệ thông tin; Chi cục Phát hành và Kho quỹ; và các đơn vị NHNN có dự án hỗ trợ phát triển chính thức (dự án ODA);</t>
+          <t>1. Cung cấp thông tin hỗ trợ cảnh giới tại các điểm giao cắt giữa đường bộ, đường sắt là việc cung cấp thông tin của doanh nghiệp kinh doanh kết cấu hạ tầng đường sắt, chủ sở hữu đường sắt chuyên dùng thuộc phạm vi quản lý cho người cảnh giới để thực hiện nhiệm vụ tại vị trí cần cảnh giới.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 3 Điều 3</t>
+          <t>Khoản 1 Điều 3</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>84/2025/TT-NHNN</t>
+          <t>28/2018/TT-BGTVT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186231</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=129226</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5019,11 +5012,12 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b063dc28-e181-11f0-99cf-1f4f4f29cdc1#k2:2011-03-16</t>
+          <t>vilextime:T1:provision:a82e7fd0-2f43-11f1-845f-b378206c5594:2010-08-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5033,37 +5027,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Theo quy định về đánh giá môi trường chiến lược trong quy hoạch phân khu, việc đánh giá diễn biến và so sánh tác động môi trường giữa các phương án quy hoạch dựa trên những yếu tố nào?</t>
+          <t>Một tổ chức đăng ký công nhận phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen thì phải nộp tài liệu thuyết minh năng lực theo mẫu của cơ quan nào?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2011-03-16</t>
+          <t>2010-08-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Điều 13. Nội dung ĐMC trong quy hoạch phân khu</t>
+          <t>2. Tổ chức đăng ký công nhận Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen phải nộp ba (03) bộ hồ sơ cho Bộ Khoa học và Công nghệ. Hồ sơ bao gồm:</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2. Đánh giá diễn biến môi trường khu vực, dự báo, so sánh các tác động môi trường của các phương án quy hoạch trên cơ sở mật độ xây dựng, quy hoạch sử dụng đất, bố trí các khu chức năng.</t>
+          <t>c) Thuyết minh về năng lực của Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen theo mẫu của Bộ Khoa học và Công nghệ;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 13</t>
+          <t>Điểm c Khoản 2 Điều 12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01/2011/TT-BXD</t>
+          <t>69/2010/NĐ-CP</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26151</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25420</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5083,11 +5077,12 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b0cb14e0-2c79-11f1-a4df-5bcc3aeb19f1:2016-04-02</t>
+          <t>vilextime:T1:provision:ac56527c-eb73-11f0-9b3a-07ebd665db64:2014-10-25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5097,22 +5092,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Trường hợp một người nước ngoài làm việc tại Việt Nam không hưởng lương để thực hiện điều ước quốc tế, người đó được xác định là loại lao động nước ngoài nào?</t>
+          <t>Trường hợp nội dung Chứng nhận tham gia bảo hiểm tiền gửi của một tổ chức tín dụng thay đổi, tổ chức đó phải đề nghị cấp lại trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2016-04-02</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Điều 3. Người lao động nước ngoài là người di chuyển trong nội bộ doanh nghiệp, tình nguyện viên, chuyên gia, nhà quản lý, giám đốc điều hành và lao động kỹ thuật</t>
+          <t>Điều 3. Nội dung Chứng nhận tham gia bảo hiểm tiền gửi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2. Tình nguyện viên là người lao động nước ngoài làm việc tại Việt Nam theo hình thức tự nguyện và không hưởng lương để thực hiện điều ước quốc tế mà nước Cộng hòa xã hội chủ nghĩa Việt Nam là thành viên.</t>
+          <t>2. Trong thời hạn 15 ngày kể từ ngày có sự thay đổi nội dung Chứng nhận tham gia bảo hiểm tiền gửi quy định tại điểm b khoản 1 Điều này, tổ chức tham gia bảo hiểm tiền gửi thực hiện việc đề nghị cấp lại Chứng nhận tham gia bảo hiểm tiền gửi theo quy định tại khoản 3 Điều 7 Nghị định số 68/2013/NĐ-CP ngày 28 tháng 6 năm 2013 của Chính phủ quy định chi tiết và hướng dẫn thi hành Luật Bảo hiểm tiền gửi.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5122,12 +5117,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>11/2016/NĐ-CP</t>
+          <t>24/2014/TT-NHNN</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=97142</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44192</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5141,25 +5136,22 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>NĐ 11/2016/NĐ-CP đã bị NĐ 152/2020/NĐ-CP thay thế (có cạnh 'Văn bản được thay thế'); valid_to vẫn rỗng</t>
+          <t>Chấm lại 28/09 trên câu hỏi đã sửa: giữ nguyên.</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b179a746-ec3f-11f0-8111-3b42442d06b3#k6#a:2012-12-26</t>
+          <t>vilextime:T1:provision:ac625f20-eadf-11f0-bd15-e99c4454aa60#k15:2009-12-23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5169,37 +5161,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hình thức xử phạt bổ sung đối với giấy chứng nhận cơ sở đủ điều kiện an toàn thực phẩm khi tái phạm được xác định ra sao về thời hạn?</t>
+          <t>Một cơ quan chuyên trách về tôn giáo thuộc Bộ Nội vụ thì phải thực hiện công tác cải cách hành chính theo căn cứ nào?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2012-12-26</t>
+          <t>2009-12-23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6. Hình thức xử phạt bổ sung:</t>
+          <t>Điều 2. Nhiệm vụ và quyền hạn</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>a) Tước quyền sử dụng giấy chứng nhận cơ sở đủ điều kiện an toàn thực phẩm từ 06 tháng đến 09 tháng trong trường hợp tái phạm đối với hành vi quy định tại Khoản 2 và Khoản 3 Điều này;</t>
+          <t>15. Thực hiện công tác cải cách hành chính theo mục tiêu và nội dung chương trình cải cách hành chính nhà nước đã được cấp có thẩm quyền phê duyệt.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 6 Điều 6</t>
+          <t>Khoản 15 Điều 2</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>91/2012/NĐ-CP</t>
+          <t>134/2009/QĐ-TTg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27910</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23838</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5209,33 +5201,22 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Không nêu tái phạm hành vi nào; điểm a (06–09 tháng, hành vi khoản 2, 3) và điểm b (09–12 tháng, hành vi khác) đều là tước GCN khi tái phạm</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>b) Tước quyền sử dụng giấy chứng nhận cơ sở đủ điều kiện an toàn thực phẩm từ 09 tháng đến 12 tháng trong trường hợp tái phạm...</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b3bcbe30-21be-11f1-af12-01dc2ecd3981:2022-01-08</t>
+          <t>vilextime:T1:provision:ad505bc0-30b3-11f1-a005-81dac526b4c8:2026-02-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5245,37 +5226,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực bảo vệ tầng ô-dôn, Bộ Tài nguyên và Môi trường có trách nhiệm gì đối với việc quản lý các chất được kiểm soát và hạn ngạch các chất HCFC, HFC?</t>
+          <t>Các đơn vị kế toán phụ thuộc của Ngân hàng Nhà nước được xác định ra sao trong quy định về chế độ báo cáo tài chính của Ngân hàng Nhà nước Việt Nam?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2022-01-08</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1. Bộ Tài nguyên và Môi trường là cơ quan đầu mối quốc gia thực hiện Công ước Viên và Nghị định thư Montreal, chịu trách nhiệm trước Chính phủ thực hiện quản lý nhà nước về các chất được kiểm soát. Bộ Tài nguyên và Môi trường có trách nhiệm chủ trì, phối hợp với các bộ, ngành liên quan:</t>
+          <t>3. Các đơn vị thuộc NHNN bao gồm: các đơn vị NHNN và các đơn vị sự nghiệp thuộc NHNN (không bao gồm các đơn vị trực tiếp nhận, quyết toán kinh phí với Ngân sách Nhà nước), cụ thể:</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>a) Thực hiện quản lý các chất được kiểm soát theo điều ước quốc tế về bảo vệ tầng ô-dôn mà Việt Nam là thành viên; phân bổ, điều chỉnh, bổ sung hạn ngạch sản xuất, nhập khẩu các chất HCFC, HFC theo giai đoạn và hằng năm;</t>
+          <t>a) Các đơn vị NHNN là các đơn vị kế toán phụ thuộc, bao gồm: NHNN Chi nhánh Khu vực; Vụ Tài chính - Kế toán; Sở Giao dịch; Văn phòng; Cục Quản lý ngoại hối; Cục Công nghệ thông tin; Cục Phát hành và Kho quỹ; Chi cục Công nghệ thông tin; Chi cục Phát hành và Kho quỹ; và các đơn vị NHNN có dự án hỗ trợ phát triển chính thức (dự án ODA);</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 1 Điều 29</t>
+          <t>Điểm a Khoản 3 Điều 3</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>06/2022/NĐ-CP</t>
+          <t>84/2025/TT-NHNN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152647</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186231</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5295,11 +5276,12 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b3f9ad30-2a2f-11f1-b94e-45e747599ed1:1998-07-02</t>
+          <t>vilextime:T1:provision:b0217f44-df52-11f0-b9ee-ef79f453a9d0:2021-06-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5309,33 +5291,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Trường hợp cần tổ chức thực hiện điều lệ kiểm dịch y tế biên giới, những người đứng đầu cơ quan nào chịu trách nhiệm thi hành?</t>
+          <t>Hành vi gian dối trong hồ sơ đề nghị cấp giấy phép sao chép tác phẩm mỹ thuật về danh nhân thuộc khung phạt tiền nào theo quy định xử phạt trong lĩnh vực văn hóa?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1998-07-02</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1. Phạt tiền từ 5.000.000 đồng đến 10.000.000 đồng đối với một trong các hành vi sau đây:</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Điều 4. Bộ trưởng, Thủ trưởng cơ quan ngang Bộ, cơ quan thuộc Chính phủ, Chủ tịch Uỷ ban nhân dân tỉnh, thành phố trực thuộc Trung ương chịu trách nhiệm thi hành Nghị định này./. THỦ TƯỚNG CHÍNH PHỦ (Đã ký) Phan Văn Khải ĐIỀU LỆ KIỂM DỊCH Y TẾ BIÊN GIỚI CỦA NƯỚC CỘNG HOÀ XÃ HỘI CHỦ NGHĨA VIỆT NAM (Ban hành kèm theo Nghị định số 41/1998/NĐ-CP ngày 11 tháng 6 năm 1998 của Chính phủ) Để phòng ngừa những bệnh truyền nhiễm nguy hiểm cho người từ nước ngoài truyền vào Việt Nam và làm lây truyền trên lãnh thổ Việt Nam hoặc từ Việt Nam truyền ra nước ngoài, Điều lệ này qui định về kiểm dịch y tế biên giới.</t>
+          <t>d) Kê khai không trung thực trong hồ sơ đề nghị cấp giấy phép sao chép tác phẩm mỹ thuật về danh nhân văn hóa, anh hùng dân tộc, lãnh tụ hoặc hồ sơ đề nghị cấp giấy phép triển lãm mỹ thuật hoặc hồ sơ đề nghị cấp giấy phép xây dựng tượng đài, tranh hoành tráng hoặc hồ sơ thông báo tổ chức thi sáng tác tác phẩm mỹ thuật.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Điều 4</t>
+          <t>Điểm d Khoản 1 Điều 17</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>41/1998/NĐ-CP</t>
+          <t>38/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7712</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147628</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5345,33 +5331,26 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Điều khoản trách nhiệm thi hành, không phải quy phạm; đáp án dính chữ ký và phần mở đầu Điều lệ ban hành kèm</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>THỦ TƯỚNG CHÍNH PHỦ (Đã ký) Phan Văn Khải ĐIỀU LỆ KIỂM DỊCH Y TẾ BIÊN GIỚI ...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định xử phạt vi phạm hành chính trong lĩnh vực văn hóa, hành vi gian dối trong hồ sơ đề nghị cấp giấy phép sao chép tác phẩm mỹ thuật về danh nhân bị phạt tiền ở mức nào?»; nhãn cũ dat: ). Hỏi khung phạt tiền của hành vi (5–10 triệu theo câu dẫn); tổ chức gấp 02 lần theo khoản 2–3 Điều 5 NĐ 38/2021</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b8841d80-2c83-11f1-a05f-7d1ccf34a165:2018-09-07</t>
+          <t>vilextime:T1:provision:b063dc28-e181-11f0-99cf-1f4f4f29cdc1#k2:2011-03-16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5381,37 +5360,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực gửi, nhận văn bản điện tử giữa các cơ quan hành chính nhà nước, văn bản điện tử phải bảo đảm những yêu cầu gì trong quá trình gửi, nhận và lưu trữ?</t>
+          <t>Theo quy định về đánh giá môi trường chiến lược trong quy hoạch phân khu, việc đánh giá diễn biến và so sánh tác động môi trường giữa các phương án quy hoạch dựa trên những yếu tố nào?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2011-03-16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Điều 6. Yêu cầu gửi, nhận văn bản điện tử</t>
+          <t>Điều 13. Nội dung ĐMC trong quy hoạch phân khu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1. Văn bản điện tử phải được bảo đảm tính xác thực về nguồn gốc, sự toàn vẹn, an toàn thông tin, dữ liệu trong quá trình gửi, nhận, xử lý và lưu trữ.</t>
+          <t>2. Đánh giá diễn biến môi trường khu vực, dự báo, so sánh các tác động môi trường của các phương án quy hoạch trên cơ sở mật độ xây dựng, quy hoạch sử dụng đất, bố trí các khu chức năng.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 6</t>
+          <t>Khoản 2 Điều 13</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>28/2018/QĐ-TTg</t>
+          <t>01/2011/TT-BXD</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149440</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26151</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5421,33 +5400,22 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Điều 6 liệt kê 5 yêu cầu gửi, nhận văn bản điện tử; câu hỏi 'những yêu cầu gì' khớp cả danh sách, đáp án chỉ là khoản 1</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>2. Văn bản điện tử phải được gửi ngay trong ngày văn bản đó ký ban hành...</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:b8918060-2d46-11f1-8ed9-293a0f03a912:2018-09-05</t>
+          <t>vilextime:T1:provision:b0cb14e0-2c79-11f1-a4df-5bcc3aeb19f1:2016-04-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5457,37 +5425,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pháp luật về quản lý an toàn đập, hồ chứa nước quy định việc phê duyệt phương án cắm mốc chỉ giới phù hợp được thực hiện trong thời hạn bao lâu và do ai phê duyệt?</t>
+          <t>Trường hợp một người nước ngoài làm việc tại Việt Nam không hưởng lương để thực hiện điều ước quốc tế, người đó được xác định là loại lao động nước ngoài nào?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2018-09-05</t>
+          <t>2016-04-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>4. Phê duyệt phương án cắm mốc chỉ giới</t>
+          <t>Điều 3. Người lao động nước ngoài là người di chuyển trong nội bộ doanh nghiệp, tình nguyện viên, chuyên gia, nhà quản lý, giám đốc điều hành và lao động kỹ thuật</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>c) Trường hợp nội dung phương án cắm mốc chỉ giới phù hợp với quy định của pháp luật hiện hành và đặc điểm nơi xây dựng đập, trong thời hạn 05 ngày làm việc kể từ ngày tổ chức thẩm định, Ủy ban nhân dân cấp tỉnh có trách nhiệm phê duyệt. Trường hợp nội dung phương án cắm mốc chỉ giới không phù hợp với quy định của pháp luật hiện hành hoặc không phù hợp với đặc điểm nơi xây dựng đập, trong thời hạn 05 ngày làm việc kể từ ngày tổ chức thẩm định, Ủy ban nhân dân cấp tỉnh có trách nhiệm ban hành văn bản yêu cầu chủ sở hữu đập, hồ chứa thủy điện điều chỉnh, bổ sung phương án cắm mốc chỉ giới;</t>
+          <t>2. Tình nguyện viên là người lao động nước ngoài làm việc tại Việt Nam theo hình thức tự nguyện và không hưởng lương để thực hiện điều ước quốc tế mà nước Cộng hòa xã hội chủ nghĩa Việt Nam là thành viên.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 4 Điều 24</t>
+          <t>Khoản 2 Điều 3</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>114/2018/NĐ-CP</t>
+          <t>11/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132219</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=97142</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5508,18 +5476,19 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 114/2018/NĐ-CP nhưng valid_to rỗng</t>
+          <t>NĐ 11/2016/NĐ-CP đã bị NĐ 152/2020/NĐ-CP thay thế (có cạnh 'Văn bản được thay thế'); valid_to vẫn rỗng</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:bcd427a2-df46-11f0-9393-9f1aa228ec14#k1#c:2001-10-21</t>
+          <t>vilextime:T1:provision:b179a746-ec3f-11f0-8111-3b42442d06b3#k6#a:2012-12-26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5529,37 +5498,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực ưu đãi đầu tư xây dựng nhà ở để bán và cho thuê, Quỹ phát triển nhà ở của địa phương được sử dụng vào những mục đích nào?</t>
+          <t>Một cơ sở sử dụng phụ gia thực phẩm đã quá thời hạn sử dụng để sản xuất, chế biến thực phẩm và tái phạm hành vi này thì có thể bị tước quyền sử dụng giấy chứng nhận cơ sở đủ điều kiện an toàn thực phẩm trong bao lâu?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2001-10-21</t>
+          <t>2012-12-26</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1. Căn cứ nhu cầu, điều kiện và chương trình phát triển nhà ở của địa phương, Chủ tịch Uỷ ban nhân dân cấp tỉnh có thể quyết định thành lập Quỹ phát triển nhà ở để huy động các nguồn vốn phục vụ đầu tư phát triển nhà ở trên địa bàn theo quy định như sau:</t>
+          <t>6. Hình thức xử phạt bổ sung:</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>c) Quỹ phát triển nhà ở được sử dụng vào các mục đích sau: Cho các doanh nghiệp trong nước quy định tại khoản 1 Điều 3 Nghị định này vay với lãi suất thấp để đầu tư xây dựng các dự án nhà ở được ưu đãi; Cho các đối tượng hưởng lương từ ngân sách nhà nước vay với lãi suất thấp để mua nhà ở; Cho các doanh nghiệp trong nước vay với điều kiện tín dụng thuận lợi để đầu tư xây dựng các dự án nhà ở.</t>
+          <t>a) Tước quyền sử dụng giấy chứng nhận cơ sở đủ điều kiện an toàn thực phẩm từ 06 tháng đến 09 tháng trong trường hợp tái phạm đối với hành vi quy định tại Khoản 2 và Khoản 3 Điều này;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 1 Điều 12</t>
+          <t>Điểm a Khoản 6 Điều 6</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>71/2001/NĐ-CP</t>
+          <t>91/2012/NĐ-CP</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23099</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27910</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5574,16 +5543,21 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Hình thức xử phạt bổ sung đối với giấy chứng nhận cơ sở đủ điều kiện an toàn thực phẩm khi tái phạm được xác định ra sao về thời hạn?»; nhãn cũ khong_dat question_ambiguous: Không nêu tái phạm hành vi nào; điểm a (06–09 tháng, hành vi khoản 2, 3) và điểm b (09–12 tháng, hành vi khác) đều là tước GCN khi tái phạm). Câu hỏi chốt hành vi dùng phụ gia quá hạn (khoản 2 hoặc 3), chỉ khớp điểm a</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:cc46b990-2e04-11f1-97ec-7f3d95357355:2017-10-22</t>
+          <t>vilextime:T1:provision:b3bcbe30-21be-11f1-af12-01dc2ecd3981:2022-01-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5593,37 +5567,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Trường hợp một công chức được cử đi đào tạo bằng ngân sách nhà nước nhưng tự ý bỏ học hoặc bỏ việc trong thời gian đào tạo, người đó có nghĩa vụ gì đối với chi phí đào tạo?</t>
+          <t>Trong lĩnh vực bảo vệ tầng ô-dôn, Bộ Tài nguyên và Môi trường có trách nhiệm gì đối với việc quản lý các chất được kiểm soát và hạn ngạch các chất HCFC, HFC?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
+          <t>2022-01-08</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Điều 7. Đền bù chi phí đào tạo Cán bộ, công chức, viên chức, được cử đi đào tạo từ trình độ trung cấp trở lên bằng nguồn ngân sách nhà nước hoặc kinh phí của cơ quan quản lý, sử dụng cán bộ, công chức, viên chức phải đền bù chi phí đào tạo khi thuộc một trong các trường hợp sau đây:</t>
+          <t>1. Bộ Tài nguyên và Môi trường là cơ quan đầu mối quốc gia thực hiện Công ước Viên và Nghị định thư Montreal, chịu trách nhiệm trước Chính phủ thực hiện quản lý nhà nước về các chất được kiểm soát. Bộ Tài nguyên và Môi trường có trách nhiệm chủ trì, phối hợp với các bộ, ngành liên quan:</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1. Tự ý bỏ học, bỏ việc hoặc đơn phương chấm dứt hợp đồng làm việc trong thời gian đào tạo.</t>
+          <t>a) Thực hiện quản lý các chất được kiểm soát theo điều ước quốc tế về bảo vệ tầng ô-dôn mà Việt Nam là thành viên; phân bổ, điều chỉnh, bổ sung hạn ngạch sản xuất, nhập khẩu các chất HCFC, HFC theo giai đoạn và hằng năm;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 7</t>
+          <t>Điểm a Khoản 1 Điều 29</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>101/2017/NĐ-CP</t>
+          <t>06/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=124688</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152647</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5643,11 +5617,12 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:d20598e6-df59-11f0-a9f3-71e4d6f8e635#k7:2021-01-02</t>
+          <t>vilextime:T1:provision:b3f9ad30-2a2f-11f1-b94e-45e747599ed1:1998-07-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5657,37 +5632,33 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực điều tra, giải quyết tai nạn giao thông đường bộ, sau khi khám nghiệm hiện trường thì cán bộ Cảnh sát giao thông được phân công phải lập văn bản gì?</t>
+          <t>Trường hợp cần tổ chức thực hiện điều lệ kiểm dịch y tế biên giới, những người đứng đầu cơ quan nào chịu trách nhiệm thi hành?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Điều 9. Khám nghiệm hiện trường</t>
-        </is>
-      </c>
+          <t>1998-07-02</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>7. Sau khi khám nghiệm hiện trường, cán bộ Cảnh sát giao thông được phân công điều tra, xác minh, giải quyết vụ tai nạn giao thông phải có Báo cáo kết quả khám nghiệm hiện trường vụ tai nạn giao thông đường bộ theo mẫu số 07/TNĐB ban hành theo Thông tư này và đề xuất các biện pháp điều tra, xác minh, giải quyết tiếp theo.</t>
+          <t>Điều 4. Bộ trưởng, Thủ trưởng cơ quan ngang Bộ, cơ quan thuộc Chính phủ, Chủ tịch Uỷ ban nhân dân tỉnh, thành phố trực thuộc Trung ương chịu trách nhiệm thi hành Nghị định này./. THỦ TƯỚNG CHÍNH PHỦ (Đã ký) Phan Văn Khải ĐIỀU LỆ KIỂM DỊCH Y TẾ BIÊN GIỚI CỦA NƯỚC CỘNG HOÀ XÃ HỘI CHỦ NGHĨA VIỆT NAM (Ban hành kèm theo Nghị định số 41/1998/NĐ-CP ngày 11 tháng 6 năm 1998 của Chính phủ) Để phòng ngừa những bệnh truyền nhiễm nguy hiểm cho người từ nước ngoài truyền vào Việt Nam và làm lây truyền trên lãnh thổ Việt Nam hoặc từ Việt Nam truyền ra nước ngoài, Điều lệ này qui định về kiểm dịch y tế biên giới.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Khoản 7 Điều 9</t>
+          <t>Điều 4</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>63/2020/TT-BCA</t>
+          <t>41/1998/NĐ-CP</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155496</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7712</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5697,21 +5668,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Điều khoản trách nhiệm thi hành, không phải quy phạm; đáp án dính chữ ký và phần mở đầu Điều lệ ban hành kèm</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>THỦ TƯỚNG CHÍNH PHỦ (Đã ký) Phan Văn Khải ĐIỀU LỆ KIỂM DỊCH Y TẾ BIÊN GIỚI ...</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>loại lineage (other): Điều khoản trách nhiệm thi hành, không phải quy phạm; đáp án dính chữ ký và phần mở đầu Điều lệ ban hành kèm</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:d49e8990-23f7-11f1-8dd9-bb2ca0b668fc:2008-03-19</t>
+          <t>vilextime:T1:provision:b8841d80-2c83-11f1-a05f-7d1ccf34a165:2018-09-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5721,37 +5709,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Khi triển khai chiến lược phát triển ngành đo đạc và bản đồ, ngành phải tiếp tục đầu tư nâng cấp công nghệ gì để phục vụ kinh tế biển và quốc phòng, an ninh trên biển?</t>
+          <t>Trong lĩnh vực gửi, nhận văn bản điện tử giữa các cơ quan hành chính nhà nước, văn bản điện tử phải được bảo đảm những tính chất gì về nguồn gốc, nội dung và an toàn trong suốt quá trình xử lý?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2008-03-19</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1. Ứng dụng và phát triển công nghệ</t>
+          <t>Điều 6. Yêu cầu gửi, nhận văn bản điện tử</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>b) Tiếp tục đầu tư nâng cấp công nghệ đo đạc lập bản đồ địa hình đáy biển và bản đồ chuyên đề, chuyên ngành, chuyên dụng bảo đảm quản lý, phát triển kinh tế biển, quốc phòng, an ninh trên biển;</t>
+          <t>1. Văn bản điện tử phải được bảo đảm tính xác thực về nguồn gốc, sự toàn vẹn, an toàn thông tin, dữ liệu trong quá trình gửi, nhận, xử lý và lưu trữ.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1</t>
+          <t>Khoản 1 Điều 6</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>33/2008/QĐ-TTg</t>
+          <t>28/2018/QĐ-TTg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=12756</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149440</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5765,25 +5753,22 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Citation 'Điểm b Khoản 1' thiếu phần/mục cha (path 'Phần › Chương › Khoản 1')</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực gửi, nhận văn bản điện tử giữa các cơ quan hành chính nhà nước, văn bản điện tử phải bảo đảm những yêu cầu gì trong quá trình gửi, nhận và lưu trữ?»; nhãn cũ khong_dat question_ambiguous: Điều 6 liệt kê 5 yêu cầu gửi, nhận văn bản điện tử; câu hỏi 'những yêu cầu gì' khớp cả danh sách, đáp án chỉ là khoản 1). Câu hỏi chốt tính chất về nguồn gốc, nội dung, an toàn, chỉ khớp khoản 1</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:d93e71d8-df44-11f0-8872-818f0d72bc1d:2015-06-02</t>
+          <t>vilextime:T1:provision:b8918060-2d46-11f1-8ed9-293a0f03a912:2018-09-05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5793,37 +5778,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Theo quy định về tổ chức Tòa án nhân dân, nhiệm kỳ của Thẩm phán lần đầu và khi được bổ nhiệm lại là bao lâu?</t>
+          <t>Pháp luật về quản lý an toàn đập, hồ chứa nước quy định việc phê duyệt phương án cắm mốc chỉ giới phù hợp được thực hiện trong thời hạn bao lâu và do ai phê duyệt?</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2015-06-02</t>
+          <t>2018-09-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>THẨM PHÁN</t>
+          <t>4. Phê duyệt phương án cắm mốc chỉ giới</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nhiệm kỳ đầu của các Thẩm phán là 05 năm; trường hợp được bổ nhiệm lại hoặc được bổ nhiệm vào ngạch Thẩm phán khác thì nhiệm kỳ tiếp theo là 10 năm.</t>
+          <t>c) Trường hợp nội dung phương án cắm mốc chỉ giới phù hợp với quy định của pháp luật hiện hành và đặc điểm nơi xây dựng đập, trong thời hạn 05 ngày làm việc kể từ ngày tổ chức thẩm định, Ủy ban nhân dân cấp tỉnh có trách nhiệm phê duyệt. Trường hợp nội dung phương án cắm mốc chỉ giới không phù hợp với quy định của pháp luật hiện hành hoặc không phù hợp với đặc điểm nơi xây dựng đập, trong thời hạn 05 ngày làm việc kể từ ngày tổ chức thẩm định, Ủy ban nhân dân cấp tỉnh có trách nhiệm ban hành văn bản yêu cầu chủ sở hữu đập, hồ chứa thủy điện điều chỉnh, bổ sung phương án cắm mốc chỉ giới;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Điều 74</t>
+          <t>Điểm c Khoản 4 Điều 24</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>62/2014/QH13</t>
+          <t>114/2018/NĐ-CP</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44169</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132219</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5844,18 +5829,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Luật Tổ chức TAND 62/2014/QH13 đã bị Luật 34/2024/QH15 thay thế từ 01/01/2025; valid_to vẫn rỗng</t>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 114/2018/NĐ-CP nhưng valid_to rỗng</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:da42e420-2c87-11f1-9b3d-cb421e041738:2011-11-26</t>
+          <t>vilextime:T1:provision:bcd427a2-df46-11f0-9393-9f1aa228ec14#k1#c:2001-10-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5865,37 +5851,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực nghĩa vụ quân sự thời chiến, công dân làm nghiên cứu khoa học cần có trình độ và tham gia loại công trình nào thì được miễn gọi nhập ngũ?</t>
+          <t>Trong lĩnh vực ưu đãi đầu tư xây dựng nhà ở để bán và cho thuê, Quỹ phát triển nhà ở của địa phương được sử dụng vào những mục đích nào?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2011-11-26</t>
+          <t>2001-10-21</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Điều 16. Công dân được miễn gọi nhập ngũ trong lĩnh vực nghiên cứu khoa học</t>
+          <t>1. Căn cứ nhu cầu, điều kiện và chương trình phát triển nhà ở của địa phương, Chủ tịch Uỷ ban nhân dân cấp tỉnh có thể quyết định thành lập Quỹ phát triển nhà ở để huy động các nguồn vốn phục vụ đầu tư phát triển nhà ở trên địa bàn theo quy định như sau:</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4. Công dân có trình độ thạc sỹ hoặc nghiên cứu viên chính trở lên đang tham gia nghiên cứu trong các công trình khoa học cấp quốc gia, quốc tế.</t>
+          <t>c) Quỹ phát triển nhà ở được sử dụng vào các mục đích sau: Cho các doanh nghiệp trong nước quy định tại khoản 1 Điều 3 Nghị định này vay với lãi suất thấp để đầu tư xây dựng các dự án nhà ở được ưu đãi; Cho các đối tượng hưởng lương từ ngân sách nhà nước vay với lãi suất thấp để mua nhà ở; Cho các doanh nghiệp trong nước vay với điều kiện tín dụng thuận lợi để đầu tư xây dựng các dự án nhà ở.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 16</t>
+          <t>Điểm c Khoản 1 Điều 12</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>184/2011/TT-BQP</t>
+          <t>71/2001/NĐ-CP</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27025</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23099</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5905,33 +5891,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Hỏi 'cần có trình độ và tham gia loại công trình nào'; khoản 3 (tiến sĩ, đề tài cấp bộ trở lên) và khoản 5 (GS, PGS) cũng là trường hợp được miễn</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>3. Công dân có trình độ tiến sỹ đang tham gia nghiên cứu khoa học đề tài cấp bộ, ngành, quốc gia, quốc tế.</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:dfeea17c-e16c-11f0-ab71-f3424eab00a5:2001-02-03</t>
+          <t>vilextime:T1:provision:cc46b990-2e04-11f1-97ec-7f3d95357355:2017-10-22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5941,33 +5916,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực bảo vệ môi trường đối với bãi chôn lấp chất thải rắn, khi kiểm tra chất lượng môi trường thì cần đặc biệt chú ý đến những hạng mục nào?</t>
+          <t>Trường hợp một công chức được cử đi đào tạo bằng ngân sách nhà nước nhưng tự ý bỏ học hoặc bỏ việc trong thời gian đào tạo, người đó có nghĩa vụ gì đối với chi phí đào tạo?</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2001-02-03</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>2017-10-22</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Điều 7. Đền bù chi phí đào tạo Cán bộ, công chức, viên chức, được cử đi đào tạo từ trình độ trung cấp trở lên bằng nguồn ngân sách nhà nước hoặc kinh phí của cơ quan quản lý, sử dụng cán bộ, công chức, viên chức phải đền bù chi phí đào tạo khi thuộc một trong các trường hợp sau đây:</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4.2. Trong số các hạng mục phải kiểm tra chất lượng về môi trường cần đặc biệt chú ý kiểm tra các hệ thống chống thấm, hệ thống thu gom và xử lý nước rác, hệ thống thu gom, đánh giá và khử biogas cũng như hệ thống giếng quan trắc nước dưới đất, các trạm quan trắc nước mặt. Công tác kiểm tra phải được tiến hành cả ở hiện trường và trong phòng thí nghiệm, đúng hạng mục và phù hợp với từng thời điểm cần thiết nhằm đảm bảo sao cho những vật liệu và thiết bị sử dụng trong BCL đáp ứng các tiêu chuẩn Việt Nam về môi trường (TCVN).</t>
+          <t>1. Tự ý bỏ học, bỏ việc hoặc đơn phương chấm dứt hợp đồng làm việc trong thời gian đào tạo.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Khoản 4</t>
+          <t>Khoản 1 Điều 7</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01/2001/TTLT/BKHCNMT-BXD</t>
+          <t>101/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23306</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=124688</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5981,25 +5960,18 @@
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>citation_path_wrong</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Đáp án là mục 4.2 nhưng citation là 'Khoản 4'</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:e1d96590-df4a-11f0-b9c1-975d55408b6a:2016-06-02</t>
+          <t>vilextime:T1:provision:d20598e6-df59-11f0-a9f3-71e4d6f8e635#k7:2021-01-02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6009,37 +5981,37 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Theo quy định về phối hợp trao đổi thông tin bảo đảm an ninh hàng không dân dụng, thông tin về tình hình nước ngoài nào thuộc nội dung phải trao đổi?</t>
+          <t>Trong lĩnh vực điều tra, giải quyết tai nạn giao thông đường bộ, sau khi khám nghiệm hiện trường thì cán bộ Cảnh sát giao thông được phân công phải lập văn bản gì?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2016-06-02</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Điều 4. Nội dung thông tin trao đổi</t>
+          <t>Điều 9. Khám nghiệm hiện trường</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>4. Tình hình an ninh, chính trị các nước, khu vực có đường bay đi, đến, bay qua Việt Nam.</t>
+          <t>7. Sau khi khám nghiệm hiện trường, cán bộ Cảnh sát giao thông được phân công điều tra, xác minh, giải quyết vụ tai nạn giao thông phải có Báo cáo kết quả khám nghiệm hiện trường vụ tai nạn giao thông đường bộ theo mẫu số 07/TNĐB ban hành theo Thông tư này và đề xuất các biện pháp điều tra, xác minh, giải quyết tiếp theo.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 4</t>
+          <t>Khoản 7 Điều 9</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>07/2016/TTTL-BGTVT-BCA-BQP</t>
+          <t>63/2020/TT-BCA</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=105944</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155496</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6049,33 +6021,22 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>'Thông tin về tình hình nước ngoài' cũng khớp khoản 3 (tội phạm, khủng bố quốc tế) và khoản 6 (xu hướng ngành hàng không các nước)</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>6. Các giải pháp công nghệ mới, xu hướng phát triển của ngành hàng không các nước.</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:e2243f46-df4c-11f0-9861-59e56d9b5b47:2020-02-16</t>
+          <t>vilextime:T1:provision:d49e8990-23f7-11f1-8dd9-bb2ca0b668fc:2008-03-19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6085,37 +6046,37 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pháp luật về xác định giá ca máy và thiết bị thi công xây dựng quy định Ủy ban nhân dân cấp tỉnh giao cơ quan nào xác định giá ca máy tại địa phương và căn cứ vào đâu?</t>
+          <t>Khi triển khai chiến lược phát triển ngành đo đạc và bản đồ, ngành phải tiếp tục đầu tư nâng cấp công nghệ gì để phục vụ kinh tế biển và quốc phòng, an ninh trên biển?</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2020-02-16</t>
+          <t>2008-03-19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Điều 6. Quản lý giá ca máy</t>
+          <t>1. Ứng dụng và phát triển công nghệ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2. Ủy ban nhân dân cấp tỉnh, thành phố trực thuộc trung ương(sau đây gọi tắt là Ủy ban nhân dân cấp tỉnh) giao cho cơ quan chuyên môn về xây dựng căn cứ vào phương pháp xác định giá ca máy theo hướng dẫn tại Thông tư này xác định và trình Ủy ban nhân dân cấp tỉnh công bố trên địa bàn tỉnh, thành phố trực thuộc trung ương theo định kỳ quý/năm hoặc khi có sự thay đổi lớn về giá trên thị trường xây dựng để làm cơ sở xác định chi phí máy thi công để lập và quản lý chi phí đầu tư xây dựng trên địa bàn và gửi về Bộ Xây dựng để theo dõi, quản lý.</t>
+          <t>b) Tiếp tục đầu tư nâng cấp công nghệ đo đạc lập bản đồ địa hình đáy biển và bản đồ chuyên đề, chuyên ngành, chuyên dụng bảo đảm quản lý, phát triển kinh tế biển, quốc phòng, an ninh trên biển;</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 6</t>
+          <t>Điểm b Khoản 1</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>11/2019/TT-BXD</t>
+          <t>33/2008/QĐ-TTg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140320</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=12756</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6129,17 +6090,26 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Citation 'Điểm b Khoản 1' thiếu phần/mục cha (path 'Phần › Chương › Khoản 1')</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:ebf45422-df54-11f0-b907-ef5b243581fd#k1#h:2023-01-02</t>
+          <t>vilextime:T1:provision:d93e71d8-df44-11f0-8872-818f0d72bc1d:2015-06-02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6149,37 +6119,37 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Theo quy định về hồ sơ đồ án quy hoạch xây dựng, bản đồ tổng hợp đường dây, đường ống kỹ thuật phải được thể hiện trên nền bản đồ nào và theo tỷ lệ nào?</t>
+          <t>Theo quy định về tổ chức Tòa án nhân dân, nhiệm kỳ của Thẩm phán lần đầu và khi được bổ nhiệm lại là bao lâu?</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2015-06-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1. Thành phần bản vẽ bao gồm:</t>
+          <t>THẨM PHÁN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>h) Bản đồ tổng hợp đường dây, đường ống kỹ thuật. Bản vẽ thể hiện trên nên bản đồ quy hoạch tổng mặt bằng sử dụng đất kết hợp bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.</t>
+          <t>Nhiệm kỳ đầu của các Thẩm phán là 05 năm; trường hợp được bổ nhiệm lại hoặc được bổ nhiệm vào ngạch Thẩm phán khác thì nhiệm kỳ tiếp theo là 10 năm.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Điểm h Khoản 1 Điều 10</t>
+          <t>Điều 74</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>04/2022/TT-BXD</t>
+          <t>62/2014/QH13</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159420</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44169</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6189,33 +6159,30 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Câu hỏi không nêu loại đồ án; Điều 10, 12, 27, 29, 36 cùng có mục 'Bản đồ tổng hợp đường dây, đường ống kỹ thuật' với nền bản đồ/tỷ lệ khác nhau</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Điều 12 điểm h: Bản vẽ thể hiện trên nền sơ đồ tổ chức không gian kiến trúc ...</t>
-        </is>
-      </c>
+          <t>Luật Tổ chức TAND 62/2014/QH13 đã bị Luật 34/2024/QH15 thay thế từ 01/01/2025; valid_to vẫn rỗng</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:ec474a1e-2c8a-11f1-a582-751c919294e2:2004-12-07</t>
+          <t>vilextime:T1:provision:da42e420-2c87-11f1-9b3d-cb421e041738:2011-11-26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6225,37 +6192,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Khi cần hướng dẫn thực hiện quyết định thành lập Quỹ Dịch vụ viễn thông công ích Việt Nam, Bộ Bưu chính, Viễn thông phải phối hợp với những cơ quan nào?</t>
+          <t>Trong thời chiến, một công dân có trình độ thạc sĩ làm nghiên cứu khoa học phải đang tham gia loại công trình nào thì được miễn gọi nhập ngũ?</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2004-12-07</t>
+          <t>2011-11-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1. Bộ Bưu chính, Viễn thông: Bộ Bưu chính, Viễn thông chịu trách nhiệm toàn diện về các hoạt động của Quỹ và thực hiện một số nhiệm vụ cụ thể sau:</t>
+          <t>Điều 16. Công dân được miễn gọi nhập ngũ trong lĩnh vực nghiên cứu khoa học</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>đ) Phối hợp với Bộ Tài chính và các Bộ, ngành liên quan hướng dẫn thực hiện quyết định này.</t>
+          <t>4. Công dân có trình độ thạc sỹ hoặc nghiên cứu viên chính trở lên đang tham gia nghiên cứu trong các công trình khoa học cấp quốc gia, quốc tế.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Điểm đ Khoản 1 Điều 10</t>
+          <t>Khoản 4 Điều 16</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>191/2004/QĐ-TTg</t>
+          <t>184/2011/TT-BQP</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18802</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27025</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6269,25 +6236,22 @@
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào QĐ 191/2004/QĐ-TTg nhưng valid_to rỗng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực nghĩa vụ quân sự thời chiến, công dân làm nghiên cứu khoa học cần có trình độ và tham gia loại công trình nào thì được miễn gọi nhập ngũ?»; nhãn cũ khong_dat question_ambiguous: Hỏi 'cần có trình độ và tham gia loại công trình nào'; khoản 3 (tiến sĩ, đề tài cấp bộ trở lên) và khoản 5 (GS, PGS) cũng là trường hợp được miễn). Câu hỏi chốt trình độ thạc sĩ, chỉ khớp khoản 4</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:ee6092ba-eb76-11f0-a704-8938278d801d:2007-05-29</t>
+          <t>vilextime:T1:provision:dfeea17c-e16c-11f0-ab71-f3424eab00a5:2001-02-03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6297,37 +6261,33 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nếu một công ty nhà nước chuyển đổi thành công ty trách nhiệm hữu hạn một thành viên, thì khi kiểm kê nợ phải trả công ty phải lập những tài liệu gì và phân tích các khoản nợ ra sao?</t>
+          <t>Trong lĩnh vực bảo vệ môi trường đối với bãi chôn lấp chất thải rắn, khi kiểm tra chất lượng môi trường thì cần đặc biệt chú ý đến những hạng mục nào?</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2007-05-29</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1. 2 Kiểm kê và đối chiếu các khoản công nợ phải thu, phải trả, các nguồn vốn, quỹ, số dư các tài khoản tại ngân hàng,…đánh giá, phân loại nợ theo quy định hiện hành:</t>
-        </is>
-      </c>
+          <t>2001-02-03</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>b. Đối với nợ phải trả: Phải lập danh sách chủ nợ và xác định từng khoản nợ phải trả. Trong đó phân tích rõ các khoản nợ trong hạn, nợ quá hạn, nợ gốc, nợ lãi, nợ phải trả không còn đối tượng trả, trách nhiệm của cá nhân và tập thể đối với từng khoản nợ quá hạn để kiến nghị giải pháp xử lý.</t>
+          <t>4.2. Trong số các hạng mục phải kiểm tra chất lượng về môi trường cần đặc biệt chú ý kiểm tra các hệ thống chống thấm, hệ thống thu gom và xử lý nước rác, hệ thống thu gom, đánh giá và khử biogas cũng như hệ thống giếng quan trắc nước dưới đất, các trạm quan trắc nước mặt. Công tác kiểm tra phải được tiến hành cả ở hiện trường và trong phòng thí nghiệm, đúng hạng mục và phù hợp với từng thời điểm cần thiết nhằm đảm bảo sao cho những vật liệu và thiết bị sử dụng trong BCL đáp ứng các tiêu chuẩn Việt Nam về môi trường (TCVN).</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1</t>
+          <t>Khoản 4</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>25/2007/TT-BTC</t>
+          <t>01/2001/TTLT/BKHCNMT-BXD</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13699</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23306</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6348,18 +6308,19 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Mục 1.2.b bị ghi thành 'Điểm b Khoản 1' (lead_in '1. 2 Kiểm kê ...')</t>
+          <t>Đáp án là mục 4.2 nhưng citation là 'Khoản 4'</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:f0af9e70-1dea-11f1-be02-15fcb9b1bea7:2021-09-16</t>
+          <t>vilextime:T1:provision:e1d96590-df4a-11f0-b9c1-975d55408b6a:2016-06-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6369,37 +6330,37 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Theo quy định về Quỹ phòng, chống thiên tai, khi kiểm tra, đôn đốc việc thực hiện nghị định thì Bộ Nông nghiệp và Phát triển nông thôn phải phối hợp với những cơ quan nào?</t>
+          <t>Theo quy định về phối hợp trao đổi thông tin bảo đảm an ninh hàng không dân dụng, tình hình an ninh, chính trị của những quốc gia, khu vực nào thuộc nội dung phải trao đổi?</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2016-06-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1. Bộ Nông nghiệp và Phát triển nông thôn có trách nhiệm:</t>
+          <t>Điều 4. Nội dung thông tin trao đổi</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>d) Chủ trì, phối hợp với Ban chỉ đạo quốc gia về phòng, chống thiên tai, Bộ Tài chính và các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ liên quan có trách nhiệm kiểm tra, đôn đốc việc thực hiện Nghị định này.</t>
+          <t>4. Tình hình an ninh, chính trị các nước, khu vực có đường bay đi, đến, bay qua Việt Nam.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 1 Điều 24</t>
+          <t>Khoản 4 Điều 4</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>78/2021/NĐ-CP</t>
+          <t>07/2016/TTTL-BGTVT-BCA-BQP</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=157039</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=105944</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6413,25 +6374,22 @@
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>valid_to_wrong</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 78/2021/NĐ-CP (data/edges.jsonl) nhưng valid_to rỗng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về phối hợp trao đổi thông tin bảo đảm an ninh hàng không dân dụng, thông tin về tình hình nước ngoài nào thuộc nội dung phải trao đổi?»; nhãn cũ khong_dat question_ambiguous: 'Thông tin về tình hình nước ngoài' cũng khớp khoản 3 (tội phạm, khủng bố quốc tế) và khoản 6 (xu hướng ngành hàng không các nước)). Câu hỏi chốt tình hình an ninh, chính trị các nước có đường bay</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:f2798c00-22ab-11f1-b463-8f1119e7a6db:2021-01-02</t>
+          <t>vilextime:T1:provision:e2243f46-df4c-11f0-9861-59e56d9b5b47:2020-02-16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6441,37 +6399,37 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Một công ty đại chúng muốn cho cổ đông dự họp và biểu quyết tại Đại hội đồng cổ đông bằng hình thức trực tuyến thì phải quy định việc này trong văn bản nào?</t>
+          <t>Pháp luật về xác định giá ca máy và thiết bị thi công xây dựng quy định Ủy ban nhân dân cấp tỉnh giao cơ quan nào xác định giá ca máy tại địa phương và căn cứ vào đâu?</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2020-02-16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2. Việc triệu tập, tổ chức họp Đại hội đồng cổ đông tuân thủ các quy định sau đây:</t>
+          <t>Điều 6. Quản lý giá ca máy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>b) Công ty đại chúng quy định tại Quy chế nội bộ về quản trị công ty việc áp dụng công nghệ thông tin hiện đại để cổ đông có thể tham dự và phát biểu ý kiến tại cuộc họp Đại hội đồng cổ đông thông qua họp trực tuyến, bỏ phiếu điện tử hoặc hình thức điện tử khác theo quy định của Luật Doanh nghiệp và Điều lệ công ty;</t>
+          <t>2. Ủy ban nhân dân cấp tỉnh, thành phố trực thuộc trung ương(sau đây gọi tắt là Ủy ban nhân dân cấp tỉnh) giao cho cơ quan chuyên môn về xây dựng căn cứ vào phương pháp xác định giá ca máy theo hướng dẫn tại Thông tư này xác định và trình Ủy ban nhân dân cấp tỉnh công bố trên địa bàn tỉnh, thành phố trực thuộc trung ương theo định kỳ quý/năm hoặc khi có sự thay đổi lớn về giá trên thị trường xây dựng để làm cơ sở xác định chi phí máy thi công để lập và quản lý chi phí đầu tư xây dựng trên địa bàn và gửi về Bộ Xây dựng để theo dõi, quản lý.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 41</t>
+          <t>Khoản 2 Điều 6</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>54/2019/QH14</t>
+          <t>11/2019/TT-BXD</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139885</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140320</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6491,11 +6449,12 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:f8fc582c-eb7a-11f0-9e9f-65637be5a31c:2007-11-13</t>
+          <t>vilextime:T1:provision:ebf45422-df54-11f0-b907-ef5b243581fd#k1#h:2023-01-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6505,37 +6464,37 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Một cơ quan được giao tổ chức thực hiện dự toán ngân sách nhà nước theo nghị quyết của Quốc hội thì phải tiếp tục triển khai giải pháp trọng tâm nào để có nguồn cho cải cách tiền lương và an sinh xã hội?</t>
+          <t>Trong hồ sơ đồ án quy hoạch phân khu đô thị, bản đồ tổng hợp đường dây, đường ống kỹ thuật phải được thể hiện trên nền bản đồ nào và theo tỷ lệ nào?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2007-11-13</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Điều 2. Tán thành các giải pháp thực hiện dự toán ngân sách nhà nước năm 2008 do Chính phủ trình và Ủy ban tài chính - Ngân sách kiến nghị trong Báo cáo thẩm tra và nhấn mạnh những giải pháp trọng tâm dưới đây:</t>
+          <t>1. Thành phần bản vẽ bao gồm:</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>4. Tiếp tục thực hiện đồng bộ các giải pháp tạo nguồn để thực hiện cải cách chính sách tiền lương và chính sách đảm bảo xã hội.</t>
+          <t>h) Bản đồ tổng hợp đường dây, đường ống kỹ thuật. Bản vẽ thể hiện trên nên bản đồ quy hoạch tổng mặt bằng sử dụng đất kết hợp bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 2</t>
+          <t>Điểm h Khoản 1 Điều 10</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>08/2007/QH12</t>
+          <t>04/2022/TT-BXD</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13002</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159420</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6545,33 +6504,26 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>question_leaks</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Câu hỏi chép gần nguyên đáp án ('tiếp tục ... giải pháp ... có nguồn cho cải cách tiền lương'); nghị quyết dự toán một năm</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>4. Tiếp tục thực hiện đồng bộ các giải pháp tạo nguồn để thực hiện cải cách chính sách tiền lương</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về hồ sơ đồ án quy hoạch xây dựng, bản đồ tổng hợp đường dây, đường ống kỹ thuật phải được thể hiện trên nền bản đồ nào và theo tỷ lệ nào?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu loại đồ án; Điều 10, 12, 27, 29, 36 cùng có mục 'Bản đồ tổng hợp đường dây, đường ống kỹ thuật' với nền bản đồ/tỷ lệ khác nhau). Đã nêu đồ án quy hoạch phân khu đô thị (Điều 10)</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:f919ce20-2469-11f1-93a2-314fcdb8318e:2024-07-02</t>
+          <t>vilextime:T1:provision:ec474a1e-2c8a-11f1-a582-751c919294e2:2004-12-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6581,37 +6533,37 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Theo quy định về quản lý chữ ký số của Ngân hàng Nhà nước, khi gửi hồ sơ bằng bản giấy thì tổ chức quản lý thuê bao được lựa chọn những loại bản nào?</t>
+          <t>Khi cần hướng dẫn thực hiện quyết định thành lập Quỹ Dịch vụ viễn thông công ích Việt Nam, Bộ Bưu chính, Viễn thông phải phối hợp với những cơ quan nào?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2004-12-07</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Điều 4. Nội dung chứng thư số</t>
+          <t>1. Bộ Bưu chính, Viễn thông: Bộ Bưu chính, Viễn thông chịu trách nhiệm toàn diện về các hoạt động của Quỹ và thực hiện một số nhiệm vụ cụ thể sau:</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>a) Trường hợp gửi hồ sơ, văn bản, báo cáo bản giấy: Tổ chức quản lý thuê bao có quyền lựa chọn gửi bản gốc hoặc bản sao được cấp từ sổ gốc hoặc bản sao có chứng thực hoặc bản sao kèm xuất trình bản chính để đối chiếu.</t>
+          <t>đ) Phối hợp với Bộ Tài chính và các Bộ, ngành liên quan hướng dẫn thực hiện quyết định này.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Khoản a Điều 4</t>
+          <t>Điểm đ Khoản 1 Điều 10</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>16/2023/TT-NHNN</t>
+          <t>191/2004/QĐ-TTg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164267</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18802</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6627,27 +6579,24 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>citation_path_wrong,lead_in_wrong,group_wrong</t>
+          <t>valid_to_wrong</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Đơn vị là lời văn trích trong văn bản sửa đổi (Điều 4a TT 28/2015/TT-NHNN do TT 16/2023 sửa), không phải điều khoản riêng của 16/2023; citation 'Khoản a Điều 4' và lead_in sai; thực chất là phiên bản mới của một điều khoản đã có</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>"Điều 4a. Cách thức gửi, nhận hồ sơ..."</t>
-        </is>
-      </c>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào QĐ 191/2004/QĐ-TTg nhưng valid_to rỗng</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:fcda0fa4-e14b-11f0-9ac4-238e516e6c2b#k4:2016-01-02</t>
+          <t>vilextime:T1:provision:ee6092ba-eb76-11f0-a704-8938278d801d:2007-05-29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6657,37 +6606,37 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pháp luật về quản lý hoạt động thương mại biên giới quy định việc điều chỉnh linh hoạt hoạt động mua bán hàng hóa qua biên giới theo điều kiện từng địa phương do ai quyết định?</t>
+          <t>Nếu một công ty nhà nước chuyển đổi thành công ty trách nhiệm hữu hạn một thành viên, thì khi kiểm kê nợ phải trả công ty phải lập những tài liệu gì và phân tích các khoản nợ ra sao?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2016-01-02</t>
+          <t>2007-05-29</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Điều 32. Hiệu lực thi hành</t>
+          <t>1. 2 Kiểm kê và đối chiếu các khoản công nợ phải thu, phải trả, các nguồn vốn, quỹ, số dư các tài khoản tại ngân hàng,…đánh giá, phân loại nợ theo quy định hiện hành:</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>4. Trường hợp cần điều hành linh hoạt hoạt động thương mại biên giới phù hợp với điều kiện kinh tế - xã hội của từng địa phương và trong từng thời kỳ, Thủ tướng Chính phủ xem xét quyết định việc điều chỉnh hoạt động mua bán hàng hóa qua biên giới của thương nhân và cư dân biên giới trên cơ sở đề nghị của Bộ Công Thương.</t>
+          <t>b. Đối với nợ phải trả: Phải lập danh sách chủ nợ và xác định từng khoản nợ phải trả. Trong đó phân tích rõ các khoản nợ trong hạn, nợ quá hạn, nợ gốc, nợ lãi, nợ phải trả không còn đối tượng trả, trách nhiệm của cá nhân và tập thể đối với từng khoản nợ quá hạn để kiến nghị giải pháp xử lý.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 32</t>
+          <t>Điểm b Khoản 1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>52/2015/QĐ-TTg</t>
+          <t>25/2007/TT-BTC</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=91876</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13699</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6701,17 +6650,26 @@
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>citation_path_wrong</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Mục 1.2.b bị ghi thành 'Điểm b Khoản 1' (lead_in '1. 2 Kiểm kê ...')</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:fe20558c-e180-11f0-a914-ddbb65539df3:2001-10-04</t>
+          <t>vilextime:T1:provision:f0af9e70-1dea-11f1-be02-15fcb9b1bea7:2021-09-16</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6721,33 +6679,37 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Khi một doanh nghiệp kinh doanh dịch vụ bảo vệ cần xác định thời điểm áp dụng văn bản hướng dẫn quản lý hoạt động này của Bộ Công an, văn bản đó có hiệu lực sau bao lâu kể từ ngày ký?</t>
+          <t>Theo quy định về Quỹ phòng, chống thiên tai, khi kiểm tra, đôn đốc việc thực hiện nghị định thì Bộ Nông nghiệp và Phát triển nông thôn phải phối hợp với những cơ quan nào?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2001-10-04</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1. Bộ Nông nghiệp và Phát triển nông thôn có trách nhiệm:</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>5. Thông tư này có hiệu lực sau 15 ngày, kể từ ngày ký.</t>
+          <t>d) Chủ trì, phối hợp với Ban chỉ đạo quốc gia về phòng, chống thiên tai, Bộ Tài chính và các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ liên quan có trách nhiệm kiểm tra, đôn đốc việc thực hiện Nghị định này.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Khoản 5</t>
+          <t>Điểm d Khoản 1 Điều 24</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>07/2001/TT-BCA (V19)</t>
+          <t>78/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=22671</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=157039</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6761,21 +6723,26 @@
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>valid_to_wrong</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Điều khoản hiệu lực của chính thông tư, không phải quy phạm nội dung — cân nhắc loại khỏi T1</t>
+          <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 78/2021/NĐ-CP (data/edges.jsonl) nhưng valid_to rỗng</t>
         </is>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>vilextime:T1:provision:fe2ac128-eb6e-11f0-b2f9-27b4d1adb5b1:2023-12-02</t>
+          <t>vilextime:T1:provision:f2798c00-22ab-11f1-b463-8f1119e7a6db:2021-01-02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6785,37 +6752,37 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Trường hợp đoạn rẽ từ đường bộ vào đường sắt ngắn hơn 10 mét, biển báo tại đường ngang phải được chọn và đặt như thế nào?</t>
+          <t>Một công ty đại chúng muốn cho cổ đông dự họp và biểu quyết tại Đại hội đồng cổ đông bằng hình thức trực tuyến thì phải quy định việc này trong văn bản nào?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1. Khi chiều dài đoạn rẽ đến đường sắt nhỏ hơn 10 mét (m):</t>
+          <t>2. Việc triệu tập, tổ chức họp Đại hội đồng cổ đông tuân thủ các quy định sau đây:</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>a) Căn cứ góc giao của đường ngang, phải đặt biển "Nơi đường sắt giao vuông góc với đường bộ" hoặc "Nơi đường sắt giao không vuông góc với đường bộ" tại lề hai góc giao giữa đường bộ chạy gần với đoạn rẽ vào đường sắt;</t>
+          <t>b) Công ty đại chúng quy định tại Quy chế nội bộ về quản trị công ty việc áp dụng công nghệ thông tin hiện đại để cổ đông có thể tham dự và phát biểu ý kiến tại cuộc họp Đại hội đồng cổ đông thông qua họp trực tuyến, bỏ phiếu điện tử hoặc hình thức điện tử khác theo quy định của Luật Doanh nghiệp và Điều lệ công ty;</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 1 Điều 25</t>
+          <t>Điểm b Khoản 2 Điều 41</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>29/2023/TT-BGTVT</t>
+          <t>54/2019/QH14</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163781</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139885</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6825,28 +6792,374 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>Hỏi chung 'biển báo phải được chọn và đặt như thế nào' khi đoạn rẽ &lt; 10 m; điểm b cũng quy định biển phải đặt</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>b) Căn cứ loại hình phòng vệ đường ngang phải đặt các biển "Giao nhau với đường sắt có rào chắn"...</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>vilextime:T1:provision:f8fc582c-eb7a-11f0-9e9f-65637be5a31c:2007-11-13</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Một cơ quan được giao tổ chức thực hiện dự toán ngân sách nhà nước theo nghị quyết của Quốc hội thì phải tiếp tục triển khai giải pháp trọng tâm nào để có nguồn cho cải cách tiền lương và an sinh xã hội?</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2007-11-13</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Điều 2. Tán thành các giải pháp thực hiện dự toán ngân sách nhà nước năm 2008 do Chính phủ trình và Ủy ban tài chính - Ngân sách kiến nghị trong Báo cáo thẩm tra và nhấn mạnh những giải pháp trọng tâm dưới đây:</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>4. Tiếp tục thực hiện đồng bộ các giải pháp tạo nguồn để thực hiện cải cách chính sách tiền lương và chính sách đảm bảo xã hội.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Khoản 4 Điều 2</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>08/2007/QH12</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13002</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>question_leaks</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Câu hỏi chép gần nguyên đáp án ('tiếp tục ... giải pháp ... có nguồn cho cải cách tiền lương'); nghị quyết dự toán một năm</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>4. Tiếp tục thực hiện đồng bộ các giải pháp tạo nguồn để thực hiện cải cách chính sách tiền lương</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>loại lineage (question_leaks): Câu hỏi chép gần nguyên đáp án ('tiếp tục ... giải pháp ... có nguồn cho cải cách tiền lương'); nghị quyết dự toán một năm</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>vilextime:T1:provision:f919ce20-2469-11f1-93a2-314fcdb8318e:2024-07-02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Theo quy định về quản lý chữ ký số của Ngân hàng Nhà nước, khi gửi hồ sơ bằng bản giấy thì tổ chức quản lý thuê bao được lựa chọn những loại bản nào?</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Điều 4. Nội dung chứng thư số</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>a) Trường hợp gửi hồ sơ, văn bản, báo cáo bản giấy: Tổ chức quản lý thuê bao có quyền lựa chọn gửi bản gốc hoặc bản sao được cấp từ sổ gốc hoặc bản sao có chứng thực hoặc bản sao kèm xuất trình bản chính để đối chiếu.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Khoản a Điều 4</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>16/2023/TT-NHNN</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164267</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>citation_path_wrong,lead_in_wrong,group_wrong</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Đơn vị là lời văn trích trong văn bản sửa đổi (Điều 4a TT 28/2015/TT-NHNN do TT 16/2023 sửa), không phải điều khoản riêng của 16/2023; citation 'Khoản a Điều 4' và lead_in sai; thực chất là phiên bản mới của một điều khoản đã có</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>"Điều 4a. Cách thức gửi, nhận hồ sơ..."</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>vilextime:T1:provision:fcda0fa4-e14b-11f0-9ac4-238e516e6c2b#k4:2016-01-02</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Pháp luật về quản lý hoạt động thương mại biên giới quy định việc điều chỉnh linh hoạt hoạt động mua bán hàng hóa qua biên giới theo điều kiện từng địa phương do ai quyết định?</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2016-01-02</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Điều 32. Hiệu lực thi hành</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>4. Trường hợp cần điều hành linh hoạt hoạt động thương mại biên giới phù hợp với điều kiện kinh tế - xã hội của từng địa phương và trong từng thời kỳ, Thủ tướng Chính phủ xem xét quyết định việc điều chỉnh hoạt động mua bán hàng hóa qua biên giới của thương nhân và cư dân biên giới trên cơ sở đề nghị của Bộ Công Thương.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Khoản 4 Điều 32</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>52/2015/QĐ-TTg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=91876</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>vilextime:T1:provision:fe20558c-e180-11f0-a914-ddbb65539df3:2001-10-04</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Khi một doanh nghiệp kinh doanh dịch vụ bảo vệ cần xác định thời điểm áp dụng văn bản hướng dẫn quản lý hoạt động này của Bộ Công an, văn bản đó có hiệu lực sau bao lâu kể từ ngày ký?</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2001-10-04</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>5. Thông tư này có hiệu lực sau 15 ngày, kể từ ngày ký.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Khoản 5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>07/2001/TT-BCA (V19)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=22671</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Điều khoản hiệu lực của chính thông tư, không phải quy phạm nội dung — cân nhắc loại khỏi T1</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>vilextime:T1:provision:fe2ac128-eb6e-11f0-b2f9-27b4d1adb5b1:2023-12-02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Khi đoạn rẽ từ đường bộ vào đường sắt ngắn hơn 10 mét, loại biển nào được chọn căn cứ vào góc giao của đường ngang và phải đặt ở vị trí nào?</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1. Khi chiều dài đoạn rẽ đến đường sắt nhỏ hơn 10 mét (m):</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>a) Căn cứ góc giao của đường ngang, phải đặt biển "Nơi đường sắt giao vuông góc với đường bộ" hoặc "Nơi đường sắt giao không vuông góc với đường bộ" tại lề hai góc giao giữa đường bộ chạy gần với đoạn rẽ vào đường sắt;</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 1 Điều 25</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>29/2023/TT-BGTVT</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163781</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đoạn rẽ từ đường bộ vào đường sắt ngắn hơn 10 mét, biển báo tại đường ngang phải được chọn và đặt như thế nào?»; nhãn cũ khong_dat question_ambiguous: Hỏi chung 'biển báo phải được chọn và đặt như thế nào' khi đoạn rẽ &lt; 10 m; điểm b cũng quy định biển phải đặt). Câu hỏi chốt 'căn cứ góc giao' nên chỉ khớp điểm a</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/review/audit_T1.xlsx
+++ b/data/review/audit_T1.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F3F00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,8 +429,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:Y56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="24" max="24"/>
+    <col width="80" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -532,6 +552,16 @@
           <t>audit_note</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trich_van_ban_goc</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trich_van_ban_tac_dong</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -584,9 +614,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19196</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -597,7 +624,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -608,11 +634,25 @@
           <t>NĐ 161/2004/NĐ-CP đã bị NĐ 36/2007/NĐ-CP (xử phạt VPHC lĩnh vực chứng khoán) thay thế; valid_to vẫn rỗng; id cũ vilextime:T1:provision:0874e970-3425-11f1-9e65-619eaa3c24f9:2004-10-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>161/2004/NĐ-CP · hiệu lực 2004-10-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 8. Xử phạt đối với những hành vi vi phạm các quy định về phát hành chứng khoán ra công chúng
+1. Phạt tiền từ 10.000.000 đồng đến 20.000.000 đồng đối với mỗi tổ chức phát hành, tổ chức tư vấn phát hành thực hiện một trong những hành vi vi phạm sau:
+a) Hồ sơ đăng ký phát hành chứng khoán ra công chúng gửi Uỷ ban Chứng khoán Nhà nước có thông tin sai lệch hoặc che dấu sự thật;
+b) Sử dụng các thông tin ngoài bản cáo bạch để thăm dò thị trường trước khi được phép phát hành chứng khoán ra công chúng;
+c) Phân phối chứng khoán ra công chúng trước khi thực hiện việc công bố phát hành;
+d) Phát hành chứng khoán ra công chúng không theo đúng nội dung đăng ký phát hành về chủng loại chứng khoán, thời hạn phát hành và khối lượng tối thiểu theo quy định;
+đ) Thông báo phát hành chứng khoán trên các phương tiện thông tin đại chúng không đúng nội dung, thời hạn và thời gian theo quy định;
+e) Không có tổ chức trung gian tài chính tham gia bảo lãnh phát hành đối với trường hợp phát hành trái phiếu;
+g) Tổ chức bảo lãnh phát hành thực hiện bảo lãnh phát hành tổng giá trị chứng khoán vượt quá tỷ lệ quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -665,9 +705,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13896</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -678,7 +715,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -689,11 +725,17 @@
           <t>Mục 2.9.c bị ghi thành 'Điểm c Khoản 2'; id cũ vilextime:T1:provision:09e3e960-2759-11f1-aa6b-33c42ee76deb:2007-08-08: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>72/2007/TT-BTC · hiệu lực 2007-08-07 → 2017-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -746,9 +788,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183370</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -759,18 +798,38 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực chức danh nghề nghiệp bác sĩ y học dự phòng, nhiệm vụ về truyền thông giáo dục sức khỏe và quản lý sức khỏe cộng đồng gồm những việc gì?»; nhãn cũ khong_dat question_ambiguous: Thông tư có ba Điều cho ba hạng bác sĩ y học dự phòng (Điều 7 hạng I, Điều 8 hạng II, Điều 9 hạng III), mỗi Điều có điểm c về truyền thông giáo dục sức khỏe; câu hỏi không nêu hạng). Đã nêu hạng II; id cũ vilextime:T1:provision:0fdffb50-2d40-11f1-ad9b-6dee35851177:2025-12-19: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>41/2025/TT-BYT · hiệu lực 2025-12-18 → nay · lúc thu thập: Còn hiệu lực
+Điều 8. Bác sĩ y học dự phòng chính (hạng II) - Mã số: V.08.02.05
+1. Nhiệm vụ:
+a) Tổ chức thực hiện nhiệm vụ phòng bệnh, cụ thể:
+- Xây dựng kế hoạch tổ chức thực hiện các hoạt động chuyên môn về phòng bệnh, quản lý chương trình y tế, truyền thông giáo dục sức khỏe, sức khỏe lao động, bệnh nghề nghiệp, tai nạn thương tích;
+- Tổ chức thực hiện hoạt động phòng, chống các bệnh truyền nhiễm: giám sát, phát hiện dịch bệnh, tiêm chủng phòng bệnh, kiểm soát, xử lý và khống chế dịch, bệnh, các tác nhân truyền nhiễm gây dịch nhất là dịch bệnh mới phát sinh;
+- Tổ chức thực hiện hoạt động phòng, chống các bệnh không lây nhiễm: phòng chống các yếu tố nguy cơ; sàng lọc, phát hiện sớm, quản lý, theo dõi người mắc bệnh không lây nhiễm, bệnh mạn tính;
+- Tổ chức triển khai thực hiện việc đánh giá tình trạng sức khỏe, các yếu tố nguy cơ và nhu cầu chăm sóc sức khỏe của cộng đồng;
+- Tổ chức thực hiện các hoạt động sức khỏe môi trường, sức khỏe nghề nghiệp: bảo đảm chất lượng nước sinh hoạt, phòng chống bệnh nghề nghiệp và phòng chống tai nạn, thương tích, quản lý chất thải y tế.
+b) Thực hiện việc khám bệnh, chữa bệnh cấp ban đầu, xử lý cấp cứu, khắc phục hậu quả thiên tai, thảm họa liên quan đến sức khỏe con người theo phạm vi hoạt động chuyên môn được giao;
+c) Tổ chức biên soạn nội dung và lập kế hoạch hướng dẫn công tác thông tin, giáo dục, truyền thông về bảo vệ, chăm sóc và nâng cao sức khỏe; đưa ra các biện pháp quản lý sức khỏe tại cộng đồng;
+d) Tổ chức triển khai các nội dung chăm sóc sức khỏe ban đầu;
+đ) Tham gia phân tích, đánh giá, kết luận những vấn đề chuyên môn về phòng bệnh khi có yêu cầu;
+e) Đào tạo và nghiên cứu khoa học:
+- Tổ chức biên soạn chương trình, tài liệu chuyên môn; xây dựng quy chế, quy trình kỹ thuật chuyên môn phòng bệnh; các giải pháp nhằm nâng cao chất lượng công tác phòng bệnh;
+- Tổ chức đào tạo, bồi dưỡng về lĩnh vực phòng bệnh phù hợp với trình độ và phạm vi chuyên môn đối với viên chức, người học;
+- Chủ trì hoặc tham gia các đề tài, chương trình, dự án nghiên cứu khoa học cấp Nhà nước, cấp bộ, cấp tỉnh;
+- Chủ trì hoặc tham gia nghiên cứu, cung cấp bằng chứng xây dựng chính sách, kế hoạch phát triển về công tác phòng bệnh của ngành, lĩnh vực, địa phương.</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -823,9 +882,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0ae72df0-4247-11f1-9aef-8b444472143a</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -836,18 +892,40 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Hành vi sử dụng biển hiệu sai mẫu hoặc sai nội dung đăng ký hoạt động trong lĩnh vực bổ trợ tư pháp được xác định ra sao về mức xử phạt?»; nhãn cũ khong_dat question_ambiguous: 'Biển hiệu sai mẫu/sai nội dung trong lĩnh vực bổ trợ tư pháp' có ở Điều 9 (tổ chức hành nghề luật sư), 11 (tư vấn pháp luật), 17 (công chứng), 69 (thừa phát lại) với mức phạt khác nhau; câu hỏi không nêu nghề). Hỏi khung phạt tiền của hành vi trong lĩnh vực công chứng: 3–7 triệu theo câu dẫn; tổ chức gấp 02 lần theo khoản 4 Điều 4 NĐ 109/2026</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>109/2026/NĐ-CP · hiệu lực 2026-05-18 → nay · lúc thu thập: Còn hiệu lực
+Điều 17. Hành vi vi phạm quy định về hoạt động của tổ chức hành nghề công chứng
+1. Phạt tiền từ 3.000.000 đồng đến 7.000.000 đồng đối với một trong các hành vi sau:
+a) Không niêm yết hoặc niêm yết không đầy đủ lịch làm việc; thủ tục công chứng; nội quy tiếp người yêu cầu công chứng; phí công chứng, phí, giá dịch vụ theo yêu cầu liên quan đến việc công chứng và chi phí khác tại trụ sở của tổ chức mình;
+b) Đăng báo nội dung đăng ký hoạt động không đúng thời hạn hoặc không đầy đủ nội dung hoặc không đúng số lần theo quy định;
+c) Thực hiện không đúng hoặc không đầy đủ chế độ báo cáo; báo cáo không chính xác về tình hình tổ chức và hoạt động của tổ chức hành nghề công chứng;
+d) Lập, quản lý, sử dụng sổ hoặc sử dụng biểu mẫu trong hoạt động công chứng không đúng quy định;
+đ) Lưu trữ hồ sơ công chứng không đúng quy định;
+e) Sử dụng biển hiệu không đúng mẫu hoặc nội dung biển hiệu không đúng giấy đăng ký hoạt động;
+g) Phân công công chứng viên hướng dẫn tập sự không đúng quy định;
+h) Từ chối tiếp nhận người tập sự hành nghề công chứng do Sở Tư pháp chỉ định mà không có lý do chính đáng;
+i) Từ chối nhận lưu giữ di chúc mà không có lý do chính đáng hoặc từ chối tiếp nhận yêu cầu công bố di chúc khi có yêu cầu hợp lệ từ người thừa kế;
+k) Không duy trì việc đáp ứng điều kiện về trụ sở của tổ chức hành nghề công chứng theo quy định;
+l) Không ghi số văn bản công chứng hoặc không đóng dấu của tổ chức hành nghề công chứng vào văn bản công chứng đã có chữ ký của công chứng viên hoặc không đóng dấu giáp lai giữa các tờ đối với văn bản công chứng có từ 02 tờ trở lên hoặc không giao bản gốc văn bản công chứng cho người yêu cầu công chứng;
+m) Không mua bảo hiểm trách nhiệm nghề nghiệp liên tục cho công chứng viên của tổ chức mình;
+n) Không tạo điều kiện cho công chứng viên của tổ chức mình tham gia bồi dưỡng nghiệp vụ công chứng hằng năm;
+o) Không đề nghị cấp lại thẻ công chứng viên cho công chứng viên trong trường hợp tổ chức hành nghề công chứng thay đổi tên gọi;
+p) Vi phạm quy định về thông báo và gửi bản sao hợp đồng bảo hiểm, hợp đồng thay đổi, gia hạn hợp đồng bảo hiểm trách nhiệm nghề nghiệp của công chứng viên cho Sở Tư pháp khi mua bảo hiểm hoặc thay đổi, gia hạn hợp đồng bảo hiểm;
+q) Không phân công công chứng viên của tổ chức mình thực hiện việc công bố di chúc hoặc phân công trong trường hợp người lập di chúc đã chỉ định công chứng viên khác hiện đang hành nghề tại tổ chức hành nghề công chứng đó là người công bố di chúc;
+r) Không xác nhận và đóng dấu của tổ chức hành nghề công chứng vào bản sao di chúc về việc sao từ hồ sơ gửi giữ di chúc.</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -900,9 +978,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32779</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -913,7 +988,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -924,11 +998,24 @@
           <t>NĐ 176/2013/NĐ-CP đã bị NĐ 117/2020/NĐ-CP thay thế (hiệu lực 15/11/2020), valid_to vẫn rỗng · Mức trong đáp án là mức cho cá nhân; nếu người sử dụng lao động là tổ chức thì gấp 02 lần (khoản 5 quy định chung NĐ 176/2013); id cũ vilextime:T1:provision:2f5ea3c0-2c85-11f1-b760-79130d885196:2014-01-01: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>176/2013/NĐ-CP · hiệu lực 2013-12-31 → nay · lúc thu thập: Còn hiệu lực
+Điều 57. Vi phạm quy định về đóng bảo hiểm y tế
+3. Phạt tiền đối với hành vi không đóng bảo hiểm y tế cho toàn bộ số người lao động có trách nhiệm tham gia bảo hiểm y tế của người sử dụng lao động theo một trong các mức sau đây:
+a) Từ 500.000 đồng đến 1.000.000 đồng, khi vi phạm dưới 10 người lao động;
+b) Từ 1.000.000 đồng đến 5.000.000 đồng, khi vi phạm từ 10 đến dưới 50 người lao động;
+c) Từ 5.000.000 đồng đến 10.000.000 đồng, khi vi phạm từ 50 đến dưới 100 người lao động;
+d) Từ 10.000.000 đồng đến 15.000.000 đồng, khi vi phạm từ 100 đến dưới 500 người lao động;
+đ) Từ 15.000.000 đồng đến 20.000.000 đồng, khi vi phạm từ 500 đến dưới 1.000 người lao động;
+e) Từ 20.000.000 đồng đến 30.000.000 đồng, khi vi phạm từ 1.000 người lao động trở lên.</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -981,9 +1068,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16750</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -994,18 +1078,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:312d0ee8-eb81-11f0-be34-83d33c77be02#k3:2006-04-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>61/2005/QH11 · hiệu lực 2006-04-01 → 2014-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 20. Chỉ định thầu
+3. Trước khi thực hiện chỉ định thầu quy định tại các điểm b, c, d và đ khoản 1 Điều này, dự toán đối với gói thầu đó phải được phê duyệt theo quy định.</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1058,9 +1147,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32730</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1071,18 +1157,24 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:38528280-2c85-11f1-954b-d3e284a740f5:2014-02-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>206/2013/NĐ-CP · hiệu lực 2014-02-01 → 2026-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 21. Quyền, trách nhiệm của Bộ Tài chính
+1. Chủ trì nghiên cứu, xây dựng để báo cáo Chính phủ cơ chế về quản lý nợ của doanh nghiệp; hướng dẫn về các chỉ tiêu giám sát, đánh giá khả năng thanh toán nợ của doanh nghiệp; hướng dẫn chế độ trích lập và sử dụng các khoản dự phòng nợ phải thu khó đòi.
+Phối hợp tham gia với Bộ quản lý ngành, Ủy ban nhân dân cấp tỉnh trong việc giám sát, kiểm tra, đánh giá các khoản nợ của tập đoàn kinh tế nhà nước, tổng công ty nhà nước, công ty trách nhiệm hữu hạn một thành viên do Bộ quản lý ngành, Ủy ban nhân dân cấp tỉnh quyết định thành lập hoặc được giao quản lý.</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1135,9 +1227,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46601</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1148,7 +1237,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -1159,11 +1247,17 @@
           <t>Citation 'Điểm b Khoản 2' thiếu phần/mục cha (path 'Chương I › Khoản 2'); id cũ vilextime:T1:provision:3c58dda6-e177-11f0-aad8-510bc3ddb5e6:2007-08-31: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>07/2007/TTLT-BTM-BTC · hiệu lực 2007-08-30 → 2019-11-05 · lúc thu thập: Hết hiệu lực toàn bộ
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1216,8 +1310,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138874</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>document_ended 2024-07-15 bao_dong_gia</t>
@@ -1233,7 +1325,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -1244,11 +1335,28 @@
           <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 15/2019/TT-BNNPTNT nhưng valid_to rỗng; id cũ vilextime:T1:provision:45d941c0-2c83-11f1-a5f8-7129425f1ab5:2020-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>15/2019/TT-BNNPTNT · hiệu lực 2020-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 5. Dự toán
+1. Chi phí xây dựng:
+a) Chi phí trực tiếp, gồm:
+Chi phí nhân công: chuẩn bị hiện trường, trồng, chăm sóc, kiểm tra, giám sát, bảo vệ rừng và chi phí khác có liên quan;
+Chi phí máy và thiết bị thi công: làm đất, vận chuyển cây con bằng máy; san, ủi mặt bằng, làm đường ranh cản lửa và chi phí khác có liên quan;
+Chi phí vật tư: giống, phân bón, thuốc bảo vệ thực vật và các vật tư khác có liên quan.
+b) Chi phí chung: được tính bằng 5,0% chi phí trực tiếp, gồm:
+Chi phí trang bị bảo hộ, an toàn lao động và bảo vệ môi trường cho người lao động và môi trường xung quanh;
+Chi phí vận chuyển máy móc, thiết bị thi công và lực lượng lao động đến và ra khỏi công trường;
+Chi phí bảo đảm an toàn giao thông phục vụ thi công (nếu có).
+c) Thu nhập chịu thuế tính trước: là lợi nhuận dự tính trong dự toán xây dựng công trình, được tính bằng 5,5% tổng chi phí trực tiếp và chi phí chung;
+d) Thuế giá trị gia tăng thực hiện theo quy định của nhà nước.</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1301,9 +1409,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185823</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1314,18 +1419,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:46db5bf0-31c7-11f1-ac1e-d38b84040a86:2026-02-16: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>341/2025/NĐ-CP · hiệu lực 2026-02-15 → nay · lúc thu thập: Còn hiệu lực
+Điều 36. Hành vi vận chuyển, tàng trữ hàng hóa sao chép lậu
+1. Phạt tiền đối với hành vi vận chuyển hàng hóa sao chép lậu theo quy định như sau:
+a) Từ 1.000.000 đồng đến 3.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được dưới 10.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan dưới 20.000.000 đồng hoặc hàng hóa vi phạm trị giá dưới 20.000.000 đồng;
+b) Từ 3.000.000 đồng đến 5.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 10.000.000 đồng đến dưới 20.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 20.000.000 đồng đến dưới 40.000.000 đồng hoặc hàng hóa vi phạm trị giá từ 20.000.000 đồng đến dưới 40.000.000 đồng;
+c) Từ 5.000.000 đồng đến 10.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 20.000.000 đồng đến dưới 30.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 40.000.000 đồng đến dưới 60.000.000 đồng hoặc hàng hóa vi phạm trị giá từ 40.000.000 đồng đến dưới 60.000.000 đồng;
+d) Từ 10.000.000 đồng đến 20.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 30.000.000 đồng đến dưới 50.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 60.000.000 đồng đến dưới 100.000.000 đồng hoặc hàng hóa vi phạm trị giá từ 60.000.000 đồng đến dưới 100.000.000 đồng;
+đ) Từ 20.000.000 đồng đến 30.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 50.000.000 đồng đến dưới 100.000.000 đồng hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 100.000.000 đồng đến dưới 150.000.000 đồng hoặc hàng hóa vi phạm trị giá từ 100.000.000 đồng đến dưới 150.000.000 đồng;
+e) Từ 30.000.000 đồng đến 50.000.000 đồng trong trường hợp số lợi bất hợp pháp thu được từ 100.000.000 đồng trở lên hoặc gây thiệt hại cho chủ sở hữu quyền tác giả, chủ sở hữu quyền liên quan từ 150.000.000 đồng trở lên hoặc hàng hóa vi phạm trị giá từ 150.000.000 đồng trở lên.</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1378,9 +1494,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18448</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1391,18 +1504,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người bị xử phạt vi phạm hành chính không tự nguyện nộp tiền phạt thì có thể bị áp dụng biện pháp cưỡng chế nào đối với tài sản của mình?»; nhãn cũ khong_dat question_ambiguous: Hỏi biện pháp cưỡng chế 'đối với tài sản'; khoản 1 (khấu trừ tiền từ tài khoản ngân hàng) cũng là biện pháp đối với tài sản). Câu hỏi chốt biện pháp dẫn tới bán đấu giá, chỉ khớp khoản 2; id cũ vilextime:T1:provision:4a1d663e-eb7f-11f0-a965-3115c99302b6#k2:2005-04-09: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>37/2005/NĐ-CP · hiệu lực 2005-04-08 → 2013-12-28 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 2. Các biện pháp cưỡng chế hành chính
+2. Kê biên phần tài sản có giá trị tương ứng với số tiền phạt để bán đấu giá;</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1430,7 +1548,6 @@
           <t>2010-08-12 (giua_khoang); 2026-05-02 (sau_het_hieu_luc)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>1. Vật chứng, ảảnh hoặc biên bản xác nhận vật chứng được đưa ra để xem xét tại phiên tòa.</t>
@@ -1451,9 +1568,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19411</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1464,7 +1578,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -1475,11 +1588,18 @@
           <t>Chấm lại 28/09 trên câu hỏi đã sửa. Câu hỏi nay hỏi đúng việc xem xét vật chứng. Nút không có Điều cha trong cây nên citation "Điều 94" không kiểm được (theo trí nhớ thuộc Điều 212 BLTTHS 2003 — cần kiểm); id cũ vilextime:T1:provision:5003ac4e-eb7e-11f0-a0a3-c9aae40c2eb7:2004-07-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>19/2003/QH11 · hiệu lực 2004-07-01 → 2018-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 94. Huỷ bỏ hoặc thay thế biện pháp ngăn chặn
+1. Khi vụ án bị đình chỉ thì mọi biện pháp ngăn chặn đã áp dụng đều phải được huỷ bỏ.</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1532,9 +1652,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19605</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1545,7 +1662,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -1556,11 +1672,17 @@
           <t>Citation chỉ còn 'Điểm a', path 'Phần 1 › Chương › Mục › Điểm a' mất số hiệu; id cũ vilextime:T1:provision:514503be-eb6f-11f0-8d3d-79ec914317f6:2004-02-21: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>01/2004/TT-BKH · hiệu lực 2004-02-20 → nay · lúc thu thập: Còn hiệu lực
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1613,9 +1735,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=176677</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1626,18 +1745,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:578ff710-29b8-11f1-b193-61b18a6e6e8f:2025-04-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>76/2025/NĐ-CP · hiệu lực 2025-04-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 5. Trình tự rà soát, hoàn thiện thủ tục, điều kiện được tiếp tục sử dụng đất, xác định lại giá đất, thu tiền sử dụng đất, tiền thuê đất đối với 13 dự án tại thành phố Đà Nẵng quy định tại Điều 4 Nghị quyết số 170/2024/QH15
+2. Trình tự rà soát điều kiện được tiếp tục sử dụng đất để thực hiện dự án được thực hiện như sau:
+a) Sở Nông nghiệp và Môi trường chủ trì, phối hợp với các cơ quan có liên quan rà soát các điều kiện quy định tại điểm a khoản 1 và điểm a khoản 2 Điều 4 Nghị quyết số 170/2024/QH15 đối với từng dự án về: sự phù hợp với quy hoạch sử dụng đất hoặc quy hoạch đô thị (quy hoạch chung hoặc quy hoạch phân khu) đã được phê duyệt theo quy định của pháp luật; không vi phạm quy hoạch sử dụng đất quốc phòng, quy hoạch sử dụng đất an ninh, quy hoạch 03 loại rừng (hoặc quy hoạch lâm nghiệp) đã được phê duyệt, điều kiện năng lực thực hiện dự án của nhà đầu tư;
+b) Sở Nông nghiệp và Môi trường tổng hợp kết quả đánh giá điều kiện và lập hồ sơ trình Ủy ban nhân dân thành phố Đà Nẵng xem xét, đánh giá điều kiện đối với từng dự án được tiếp tục sử dụng đất; hồ sơ gồm tờ trình, dự thảo quyết định đánh giá dự án đủ điều kiện được tiếp tục sử dụng đất, ý kiến của các cơ quan liên quan;
+c) Trong thời hạn không quá 05 ngày làm việc kể từ ngày nhận được hồ sơ do Sở Nông nghiệp và Môi trường trình, Ủy ban nhân dân thành phố Đà Nẵng xem xét về các điều kiện và ban hành quyết định đánh giá dự án đủ điều kiện được tiếp tục sử dụng đất gửi Sở Nông nghiệp và Môi trường;
+d) Thời gian hoàn thành các công việc quy định tại khoản này chậm nhất là 06 tháng kể từ ngày Ủy ban nhân dân thành phố Đà Nẵng ban hành quyết định được tiếp tục thực hiện rà soát các điều kiện theo quy định tại điểm d khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1690,9 +1818,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172311</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1703,18 +1828,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:596e6fe0-2c7d-11f1-b48b-4383f69de024:2025-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>68/2024/TT-BQP · hiệu lực 2025-01-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 3. Giải thích từ ngữ
+5. Cơ sở đào tạo lái xe quân sự là các cơ sở đào tạo thuộc phạm vi quản lý của Bộ Quốc phòng có chức năng đào tạo lái xe quân sự.</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1767,9 +1897,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163057</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1780,18 +1907,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:5ad876ec-eb72-11f0-9841-0f234bceec4b:2023-09-16: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>32/2023/TT-BCA · hiệu lực 2023-09-15 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 20. Xử lý vi phạm trong khi tuần tra, kiểm soát
+2. Xử phạt vi phạm hành chính có lập biên bản
+a) Khi phát hiện vi phạm hành chính thuộc trường hợp xử phạt vi phạm hành chính có lập biên bản, cán bộ Cảnh sát giao thông thực hiện lập biên bản vi phạm hành chính theo quy định. Biên bản vi phạm hành chính được lập bằng mẫu in sẵn hoặc lập trên Hệ thống cơ sở dữ liệu xử lý vi phạm hành chính;
+b) Khi lập xong biên bản vi phạm hành chính, cán bộ lập biên bản đọc lại cho những người có tên trong biên bản cùng nghe; hướng dẫn quyền, thời hạn giải trình về vi phạm hành chính đối với hành vi vi phạm hành chính mà cá nhân, tổ chức có quyền giải trình theo quy định tại Điều 61 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020); đề nghị người vi phạm cung cấp số điện thoại liên hệ (nếu có) để nhận thông tin xử phạt thông qua Cổng dịch vụ công Quốc gia, Cổng dịch vụ công Bộ Công an; ký vào biên bản (trường hợp người vi phạm không ký được thì điểm chỉ), trừ trường hợp biên bản được lập theo quy định tại khoản 7 Điều 58 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020). Trường hợp có người chứng kiến, người phiên dịch, người bị thiệt hại hoặc đại diện tổ chức bị thiệt hại thì những người này cùng phải ký vào biên bản; biên bản vi phạm hành chính gồm nhiều trang, thì phải ký vào từng trang biên bản;
+c) Trường hợp người vi phạm không có mặt tại nơi vi phạm hoặc cố tình trốn tránh hoặc vì lý do khách quan mà không ký, điểm chỉ vào biên bản hoặc có mặt nhưng từ chối ký, điểm chỉ vào biên bản hoặc trường hợp không xác định được đối tượng vi phạm thì Tổ trưởng Tổ Cảnh sát giao thông mời đại diện chính quyền cấp xã nơi xảy ra vi phạm hoặc ít nhất 01 người chứng kiến ký vào biên bản xác nhận việc người vi phạm không ký, điểm chỉ vào biên bản; trường hợp không có chữ ký của đại diện chính quyền cấp xã hoặc của người chứng kiến thì cán bộ Cảnh sát giao thông phải ghi rõ lý do vào biên bản. Sử dụng phương tiện, thiết bị kỹ thuật nghiệp vụ ghi nhận vụ việc và phải báo cáo thủ trưởng đơn vị bằng văn bản để làm cơ sở cho người có thẩm quyền xem xét, quyết định xử phạt;
+d) Việc giao biên bản vi phạm hành chính cho người vi phạm thực hiện theo quy định tại Điều 58 Luật Xử lý vi phạm hành chính (sửa đổi, bổ sung năm 2020) và Điều 12 Nghị định số 118/2021/NĐ-CP ngày 23/12/2021 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Xử lý vi phạm hành chính (sau đây viết gọn là Nghị định số 118/2021/NĐ-CP).</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1844,9 +1980,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6776a0a0-543a-11f1-9456-0b6fbb8f8274</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1857,7 +1990,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>citation_path_wrong,group_wrong</t>
@@ -1868,11 +2000,17 @@
           <t>Đơn vị là lời văn trích trong thông tư sửa đổi 121/2025/TT-BTC; citation thiếu Điều ('Điểm b Khoản 2'); thực chất là phiên bản mới của điều khoản thuộc thông tư bị sửa; id cũ vilextime:T1:provision:5e8c584c-543d-11f1-ae49-0120c8b0e422:2026-02-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>121/2025/TT-BTC · hiệu lực 2026-02-01 → nay · lúc thu thập: Hết hiệu lực một phần
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1925,9 +2063,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30386</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1938,7 +2073,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -1949,11 +2083,23 @@
           <t>NĐ 24/2013/NĐ-CP đã bị NĐ 123/2015/NĐ-CP thay thế (hiệu lực 01/01/2016); valid_to vẫn rỗng; id cũ vilextime:T1:provision:5ed1beca-2c86-11f1-841a-7d89578d89e1:2013-05-16: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>24/2013/NĐ-CP · hiệu lực 2013-05-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 17. Thẩm quyền, trình tự, thủ tục ghi vào sổ đăng ký kết hôn việc kết hôn của công dân Việt Nam đã được giải quyết tại cơ quan có thẩm quyền của nước ngoài ở nước ngoài
+2. Hồ sơ ghi vào sổ việc kết hôn được lập thành 01 bộ, gồm các giấy tờ sau:
+a) Tờ khai ghi vào sổ việc kết hôn (theo mẫu quy định);
+b) Bản sao giấy tờ chứng nhận việc kết hôn do cơ quan có thẩm quyền của nước ngoài cấp;
+c) Bản sao một trong các giấy tờ để chứng minh về nhân thân, như Giấy chứng minh nhân dân, Hộ chiếu hoặc giấy tờ hợp lệ thay thế;
+d) Bản sao sổ hộ khẩu hoặc sổ tạm trú của người có yêu cầu.
+Trường hợp công nhận việc kết hôn giữa công dân Việt Nam với người nước ngoài mà trước đó công dân Việt Nam hoặc người nước ngoài đã ly hôn với công dân Việt Nam tại cơ quan có thẩm quyền của nước ngoài thì phải nộp Giấy xác nhận về việc ghi vào sổ hộ tịch việc ly hôn đã tiến hành ở nước ngoài theo quy định của pháp luật Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2006,9 +2152,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111050</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2019,18 +2162,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:624d3820-2dbe-11f1-ad11-45ab3867d967:2016-07-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>60/2016/NĐ-CP · hiệu lực 2016-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 25. Danh mục chế phẩm sinh học trong xử lý chất thải tại Việt Nam
+2. Định kỳ 06 tháng một lần, Tổng cục Môi trường có trách nhiệm rà soát, sửa đổi, bổ sung danh mục chế phẩm sinh học trong xử lý chất thải tại Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2083,9 +2231,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144776</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2096,18 +2241,25 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:67b6aac0-eada-11f0-9fe9-9f5f3d9c1c27#k16#b:2015-03-11: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>85/2014/TT-BGTVT · hiệu lực 2015-03-10 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 4. Các quy định khi cải tạo xe cơ giới
+16. Khối lượng toàn bộ cho phép tham gia giao thông của xe cơ giới sau cải tạo phải đảm bảo:
+a) Đối với xe chở người: Không lớn hơn giá trị nhỏ của khối lượng toàn bộ theo thiết kế tương ứng với số người cho phép chở lớn nhất theo thiết kế của nhà sản xuất và khối lượng toàn bộ cho phép tham gia giao thông theo quy định về tải trọng cầu đường.
+b) Đối với xe tải và xe chuyên dùng: Không lớn hơn giá trị của khối lượng toàn bộ theo thiết kế của nhà sản xuất và khối lượng toàn bộ cho phép tham gia giao thông theo quy định về tải trọng cầu đường.</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2160,9 +2312,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44169</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2173,7 +2322,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -2184,11 +2332,18 @@
           <t>Luật Tổ chức TAND 62/2014/QH13 đã bị Luật Tổ chức TAND 34/2024/QH15 thay thế từ 01/01/2025; valid_to vẫn rỗng; id cũ vilextime:T1:provision:680053d0-2768-11f1-bfbd-efc08bd225d4:2015-06-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>62/2014/QH13 · hiệu lực 2015-06-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 78. Điều động Thẩm phán
+2. Chánh án Tòa án nhân dân tối cao quyết định điều động Thẩm phán từ Tòa án nhân dân này đến làm nhiệm vụ tại Tòa án nhân dân khác không cùng phạm vi thẩm quyền theo lãnh thổ hoặc không cùng một tỉnh, thành phố trực thuộc trung ương.</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2241,9 +2396,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179711</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2254,18 +2406,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cơ sở khám bệnh, chữa bệnh không có đơn giá làm căn cứ thanh toán, quỹ bảo hiểm y tế thanh toán theo đơn giá nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 4, 5, 6 cùng là 'trường hợp không có đơn giá ...' theo tầng; câu hỏi không chỉ ra tầng nào). Câu hỏi nêu tầng 'tỉnh và tỉnh giáp ranh đều không có' (khoản 5) nên chỉ khớp khoản 6; id cũ vilextime:T1:provision:6836992a-2e86-11f1-b466-61cabd0bcac0:2025-08-16: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>188/2025/NĐ-CP · hiệu lực 2025-08-15 → nay · lúc thu thập: Còn hiệu lực
+Điều 49. Thanh toán chi phí mua thuốc, hóa chất, vật tư xét nghiệm, thiết bị y tế cho cơ sử khám bệnh, chữa bệnh là đơn vị sự nghiệp công lập tư bảo đảm chi thường xuyên và chi đầu tư, đơn vị sự nghiệp công lập tự bảo đảm chi thường xuyên và các cơ sở khám bệnh, chữa bệnh tư nhân thuộc trường hợp quy định tại khoản 3 Điều 55 của Luật Đấu thầu năm 2023 được sửa đổi, bổ sung bởi Luật số 90/2025/QH15
+6. Trường hợp không có đơn giá quy định tại khoản 5 Điều này, quỹ bảo hiểm y tế thanh toán theo đơn giá trúng thầu của cơ sở khám bệnh, chữa bệnh của Nhà nước, kết quả mua sắm tập trung trên địa bàn tỉnh khác trên toàn quốc theo nguyên tắc quy định tại các điểm a, b và c khoản 5 Điều này.</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2318,9 +2475,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18116</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2331,18 +2485,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp các đơn vị thuộc Sở Tài chính cần thực hiện quy định pháp luật về thanh tra, Chánh Thanh tra Sở có nhiệm vụ gì đối với thủ trưởng các đơn vị đó?»; nhãn cũ khong_dat question_ambiguous: Khoản 6 cũng là nhiệm vụ của Chánh Thanh tra Sở đối với thủ trưởng đơn vị thuộc Sở về thực hiện pháp luật thanh tra). Câu hỏi chốt 'hướng dẫn, đôn đốc', khác khoản 6; id cũ vilextime:T1:provision:683af2ca-df3c-11f0-b581-0d9a21390744#k4:2005-07-19: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>81/2005/NĐ-CP · hiệu lực 2005-07-18 → 2012-11-25 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Nhiệm vụ, quyền hạn của Chánh Thanh tra Sở
+4. H­ướng dẫn, đôn đốc Thủ tr­ưởng tổ chức, đơn vị thuộc quyền quản lý của Sở Tài chính thực hiện các quy định pháp luật về thanh tra.</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2395,9 +2554,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133210</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2408,18 +2564,26 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về quản lý an toàn trong hoạt động dầu khí quy định chương trình quản lý an toàn phải được thực hiện vào những thời điểm nào của công trình?»; nhãn cũ khong_dat question_ambiguous: Hỏi 'những thời điểm nào' nhưng đáp án chỉ là điểm a; điểm b, c cũng là thời điểm thực hiện). Câu hỏi chốt giai đoạn xây dựng, chỉ khớp điểm a; id cũ vilextime:T1:provision:69823b0a-df52-11f0-ac04-13973f36b963:2018-12-15: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>40/2018/TT-BCT · hiệu lực 2018-12-14 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Thời điểm xây dựng các tài liệu quản lý an toàn
+1. Chương trình quản lý an toàn được thực hiện:
+a) Trước khi thi công, xây dựng, lắp đặt.
+b) Trước khi chạy thử, vận hành.
+c) Trước khi hoán cải, thay đổi công suất, công nghệ, thu dọn công trình khi kết thúc khai thác hoặc kết thúc dự án, thay đổi chính sách an toàn và hệ thống quản lý an toàn.</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2472,9 +2636,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122988</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2485,18 +2646,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:77282ab0-3c74-11f1-b2ff-b7688e5b9a17:2018-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>15/2017/QH14 · hiệu lực 2018-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 126. Trách nhiệm xây dựng Hệ thống thông tin về tài sản công
+2. Bộ Tài chính có trách nhiệm tổ chức xây dựng, quản lý, vận hành, khai thác Hệ thống thông tin về tài sản công thuộc phạm vi quản lý.</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2549,9 +2715,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18566</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2562,18 +2725,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:790c983e-eb89-11f0-bfbc-3b8923ed9a01#k3:2005-07-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>27/2004/QH11 · hiệu lực 2005-07-01 → 2019-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 69. Người giám định
+3. Người giám định từ chối kết luận giám định mà không có lý do chính đáng hoặc kết luận giám định sai sự thật hoặc khi được cơ quan trưng cầu giám định triệu tập mà vắng mặt không có lý do chính đáng thì phải chịu trách nhiệm theo quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2626,9 +2794,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19465</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2639,18 +2804,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:7955ccf0-335c-11f1-85de-b1296396b4f2:2004-09-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>17/2004/PL-UBTVQH11 · hiệu lực 2004-09-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 2. Phạm vi điều chỉnh
+Pháp lệnh này quy định việc xây dựng, tổ chức quản lý, điều hành và sử dụng dự trữ quốc gia.</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2703,9 +2873,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146471</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2716,18 +2883,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:79b8bd90-227e-11f1-8c2a-e9c4dd423d40:2021-02-06: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>147/2020/NĐ-CP · hiệu lực 2021-02-05 → nay · lúc thu thập: Còn hiệu lực
+Điều 38. Vốn nhận ủy thác
+Vốn nhận ủy thác theo quy định tại Điều 32 Nghị định này không thuộc vốn hoạt động của Quỹ đầu tư phát triển địa phương và được hạch toán, quản lý tách bạch với vốn hoạt động của Quỹ.</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2780,9 +2952,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37527</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2793,7 +2962,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -2804,11 +2972,20 @@
           <t>Có cạnh 'Văn bản được thay thế' trỏ vào TT 147/2014/TT-BTC nhưng valid_to rỗng; id cũ vilextime:T1:provision:886734ba-eae9-11f0-bfb6-1b525bfe6ee3:2014-11-26: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>147/2014/TT-BTC · hiệu lực 2014-11-25 → nay · lúc thu thập: Còn hiệu lực
+Điều 13. Thu nhập của Quỹ bảo lãnh tín dụng
+2. Thu về hoạt động tài chính:
+a) Thu lãi tiền gửi tại Kho bạc Nhà nước, ngân hàng thương mại nơi Quỹ bảo lãnh tín dụng mở tài khoản;
+b) Thu lãi đầu tư trái phiếu Chính phủ.</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2861,9 +3038,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14704</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2874,7 +3048,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -2885,11 +3058,17 @@
           <t>Citation 'Điểm d Khoản 2' thiếu Phần/Mục (path 'Phần › Chương › Khoản 2'); id cũ vilextime:T1:provision:89b5eb36-df3b-11f0-be0a-a597416047b7:2007-02-15: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>03/2007/NQ-CP · hiệu lực 2007-02-14 → nay · lúc thu thập: Còn hiệu lực
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2942,9 +3121,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111829</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2955,18 +3131,25 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:89f4e824-df4d-11f0-947a-55d04134c924#k2#b:2016-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>70/2015/TT-BGTVT · hiệu lực 2016-01-01 → 2021-10-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 1. Phạm vi điều chỉnh
+2. Thông tư này không áp dụng đối với:
+a) Xe mô tô, xe gắn máy, máy kéo và các loại xe tương tự;
+b) Xe cơ giới của quân đội, công an sử dụng vào mục đích quốc phòng, an ninh.</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3019,9 +3202,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=113098</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3032,18 +3212,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:8b621ba6-df47-11f0-8be7-01dbfc483b14#k4:2015-12-06: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>97/2015/NĐ-CP · hiệu lực 2015-12-05 → 2020-12-31 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 17. Tiêu chí đánh giá không hoàn thành nhiệm vụ
+4. Vi phạm điều lệ, nội quy, quy chế của tập đoàn, tổng công ty, công ty;</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3096,8 +3281,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119515</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>missed_event 2023-03-01 bao_dong_gia</t>
@@ -3113,18 +3296,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về chế độ làm việc của nhà giáo giáo dục nghề nghiệp quy định cách tính tiền lương dạy thêm giờ như thế nào?»; nhãn cũ khong_dat unanswerable_as_asked: Đáp án chỉ dẫn chiếu 'theo quy định hiện hành', không nêu cách tính mà câu hỏi hỏi). Câu hỏi hỏi căn cứ tính; đáp án chỉ dẫn chiếu quy định hiện hành nhưng trả lời đúng điều được hỏi; id cũ vilextime:T1:provision:8be75e80-2d47-11f1-bbcc-93110808d881:2017-07-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>07/2017/TT-BLĐTBXH · hiệu lực 2017-07-01 → 2026-02-12 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 9. Chế độ dạy thêm giờ
+4. Cách tính trả lương dạy thêm giờ theo quy định hiện hành.</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3177,9 +3365,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=15828</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3190,18 +3375,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:943871ea-df50-11f0-9561-3d5192b5741d:2006-10-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>66/2006/QH11 · hiệu lực 2006-10-01 → 2010-08-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 4.
+3. Cơ quan thẩm tra tiến hành thẩm tra những nội dung chủ yếu sau đây:
+a) Sự cần thiết đầu tư;
+b) Sự phù hợp với quy hoạch phát triển kinh tế - xã hội, quy hoạch phát triển ngành, lĩnh vực; quy hoạch sử dụng đất, tài nguyên; phương án di dân, tái định canh, định cư;
+c) Việc tuân thủ các quy định của pháp luật;
+d) Sự đáp ứng tiêu chí xác định dự án, công trình là dự án, công trình quan trọng quốc gia;
+đ) Những thông số cơ bản của dự án, công trình bao gồm: quy mô; hình thức đầu tư; địa điểm; diện tích đất cần sử dụng; thời gian, tiến độ thực hiện; phương án lựa chọn công nghệ; giải pháp bảo vệ môi trường; nguồn vốn, khả năng thu hồi vốn và trả nợ vốn vay;
+e) Hiệu quả kinh tế - xã hội ở mức báo cáo tiền khả thi.</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3254,9 +3450,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=49828ac0-6e5a-11f1-b670-d3ec94724b75</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3267,7 +3460,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -3278,11 +3470,17 @@
           <t>Citation 'Điểm c Khoản 5' thiếu Điều (path 'Chương V › Mục 2 › Khoản 5'); id cũ vilextime:T1:provision:9e092383-44c5-47d8-94fe-4379606bf0ec:2026-07-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>205/2026/NĐ-CP · hiệu lực 2026-07-01 → nay · lúc thu thập: Còn hiệu lực
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3335,9 +3533,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27889</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3348,7 +3543,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -3359,11 +3553,41 @@
           <t>Mục 4.1 bị ghi thành 'Điểm 4 Khoản 4 Điều 4'</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>188/2012/TT-BTC · hiệu lực 2012-12-28 → nay · lúc thu thập: Còn hiệu lực
+Điều 4. Hồ sơ, thủ tục hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất
+4. Quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất:
+4.1. Chậm nhất trong vòng 90 ngày kể từ ngày kết thúc năm tài chính, các ngân hàng thương mại nhà nước phải gửi hồ sơ đề nghị quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất cho Bộ Tài chính. Đối với các trường hợp hồ sơ không hợp lệ, Bộ Tài chính có trách nhiệm thông báo bằng văn bản cho các ngân hàng thương mại nhà nước trong thời hạn 10 ngày.
+4.2. Hồ sơ đề nghị quyết toán:
+a) Hồ sơ đề nghị quyết toán đối với khoản vay được hỗ trợ lãi suất vay vốn:
+- Báo cáo tổng hợp toàn hệ thống về quyết toán hỗ trợ lãi suất vay vốn đã được kiểm toán bởi Kiểm toán độc lập hoặc Kiểm toán nhà nước (Biểu 1 đính kèm).
+- Báo cáo theo từng tỉnh về quyết toán hỗ trợ lãi suất vay vốn (Biểu 2 đính kèm).
+b) Hồ sơ đề nghị quyết toán đối với khoản vay được cấp bù chênh lệch lãi suất:
+- Báo cáo tổng hợp toàn hệ thống về quyết toán chênh lệch lãi suất cấp bù theo lãi suất tín dụng đầu tư phát triển đã được kiểm toán bởi Kiểm toán độc lập hoặc Kiểm toán nhà nước (Biểu 3 đính kèm).
+- Báo cáo theo từng tỉnh về quyết toán chênh lệch lãi suất cấp bù theo lãi suất tín dụng đầu tư phát triển (Biểu 4 đính kèm).
+4.3. Các ngân hàng thương mại nhà nước tổ chức sao, lưu chứng từ, các báo cáo chi tiết theo từng khoản hỗ trợ lãi suất đảm bảo tính chính xác, minh bạch rõ ràng để tạo điều kiện cho công tác thẩm tra số liệu quyết toán hỗ trợ lãi suất và cấp bù chênh lệch lãi suất quy định tại Điểm 4.4 Khoản 4 Điều này.
+4.4. Thẩm tra số liệu quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất:
+a) Bộ Tài chính tiến hành thẩm tra số liệu quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất sau khi nhận được đầy đủ hồ sơ đề nghị quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất.
+b) Bộ Tài chính thông báo bằng văn bản các chi nhánh của ngân hàng thương mại nhà nước được lựa chọn để thực hiện thẩm tra quyết toán.
+c) Các ngân hàng thương mại nhà nước có trách nhiệm cung cấp các hồ sơ chi tiết theo từng khoản vay, được tổng hợp theo từng chi nhánh được lựa chọn để thực hiện thẩm tra quyết toán như sau:
+- Hợp đồng tín dụng, khế ước hoặc các giấy tờ tương đương để xác định đối tượng khách hàng vay vốn, tình hình thực hiện cho vay, dư nợ, thu nợ.
+- Bảng kê tích số để xác định số tiền hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất.
+- Giấy xác nhận của khách hàng trực tiếp đi vay vốn về việc đã được hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất theo năm trong đó có liệt kê từng lần được hỗ trợ dưới mọi hình thức.
+Các tài liệu nêu trên là bản phôtô có đóng dấu sao y bản chính của các ngân hàng thương mại nhà nước (số lượng 01 bộ) và được người có trách nhiệm ký, ghi rõ họ tên.
+d) Việc thẩm tra số liệu quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất được thực hiện trong thời gian 90 ngày kể từ ngày nhận được đầy đủ hồ sơ quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất của các ngân hàng thương mại nhà nước.
+4.5. Xử lý chênh lệch số liệu quyết toán và số tạm cấp hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất:
+- Trường hợp có sự chênh lệch giữa số báo cáo quyết toán có xác nhận của cơ quan kiểm toán và số thẩm tra quyết toán của Bộ Tài chính, các ngân hàng thương mại nhà nước có trách nhiệm điều chỉnh trên sổ sách kế toán để phản ánh chính xác số quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất.
+- Trường hợp số tạm cấp hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất đã được ngân sách nhà nước chuyển tiền cao hơn số thẩm tra quyết toán thì số chênh lệch sẽ được Bộ Tài chính thu hồi nộp ngân sách nhà nước.
+- Việc xử lý chênh lệch giữa số thẩm tra quyết toán và số tạm cấp hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất được thực hiện trong thời gian 45 ngày kể từ ngày của Biên bản thẩm tra quyết toán.
+- Trường hợp phải kéo dài thời gian xử lý chênh lệch giữa số liệu quyết toán và số thẩm tra quyết toán hỗ trợ lãi suất vay vốn và cấp bù chênh lệch lãi suất và các trường hợp đặc biệt khác sẽ do Bộ trưởng Bộ Tài chính xem xét, quyết định.</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3416,9 +3640,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=129226</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3429,18 +3650,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:a7be8856-df43-11f0-bc93-d9f1eab2568f:2018-07-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>28/2018/TT-BGTVT · hiệu lực 2018-07-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 3. Giải thích từ ngữ
+1. Cung cấp thông tin hỗ trợ cảnh giới tại các điểm giao cắt giữa đường bộ, đường sắt là việc cung cấp thông tin của doanh nghiệp kinh doanh kết cấu hạ tầng đường sắt, chủ sở hữu đường sắt chuyên dùng thuộc phạm vi quản lý cho người cảnh giới để thực hiện nhiệm vụ tại vị trí cần cảnh giới.</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3493,9 +3719,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25420</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3506,18 +3729,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:a82e7fd0-2f43-11f1-845f-b378206c5594:2010-08-11: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>69/2010/NĐ-CP · hiệu lực 2010-08-10 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 12. Thẩm quyền, trình tự, thủ tục công nhận, thu hồi quyết định công nhận Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen
+2. Tổ chức đăng ký công nhận Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen phải nộp ba (03) bộ hồ sơ cho Bộ Khoa học và Công nghệ. Hồ sơ bao gồm:
+a) Đơn đăng ký công nhận Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen theo mẫu của Bộ Khoa học và Công nghệ;
+b) Bản sao các quyết định về chức năng, nhiệm vụ của tổ chức;
+c) Thuyết minh về năng lực của Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen theo mẫu của Bộ Khoa học và Công nghệ;
+d) Tài liệu liên quan chứng minh Phòng thí nghiệm nghiên cứu về sinh vật biến đổi gen đáp ứng các điều kiện quy định tại Điều 11 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3570,9 +3802,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23838</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3583,18 +3812,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:ac625f20-eadf-11f0-bd15-e99c4454aa60#k15:2009-12-23: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>134/2009/QĐ-TTg · hiệu lực 2009-12-22 → 2015-04-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 2. Nhiệm vụ và quyền hạn
+15. Thực hiện công tác cải cách hành chính theo mục tiêu và nội dung chương trình cải cách hành chính nhà nước đã được cấp có thẩm quyền phê duyệt.</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3647,9 +3881,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186231</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3660,18 +3891,25 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:ad505bc0-30b3-11f1-a005-81dac526b4c8:2026-02-17: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>84/2025/TT-NHNN · hiệu lực 2026-02-16 → nay · lúc thu thập: Còn hiệu lực
+Điều 3. Giải thích từ ngữ
+3. Các đơn vị thuộc NHNN bao gồm: các đơn vị NHNN và các đơn vị sự nghiệp thuộc NHNN (không bao gồm các đơn vị trực tiếp nhận, quyết toán kinh phí với Ngân sách Nhà nước), cụ thể:
+a) Các đơn vị NHNN là các đơn vị kế toán phụ thuộc, bao gồm: NHNN Chi nhánh Khu vực; Vụ Tài chính - Kế toán; Sở Giao dịch; Văn phòng; Cục Quản lý ngoại hối; Cục Công nghệ thông tin; Cục Phát hành và Kho quỹ; Chi cục Công nghệ thông tin; Chi cục Phát hành và Kho quỹ; và các đơn vị NHNN có dự án hỗ trợ phát triển chính thức (dự án ODA);
+b) Các đơn vị sự nghiệp thuộc NHNN là các đơn vị kế toán độc lập, trực thuộc NHNN, bao gồm: Trung tâm thông tin tín dụng Quốc gia Việt Nam, Thời báo Ngân hàng, và Ban Quản lý dự án đầu tư xây dựng chuyên ngành.</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3724,9 +3962,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26151</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3737,18 +3972,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:b063dc28-e181-11f0-99cf-1f4f4f29cdc1#k2:2011-03-16: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>01/2011/TT-BXD · hiệu lực 2011-03-15 → 2019-08-15 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 13. Nội dung ĐMC trong quy hoạch phân khu
+2. Đánh giá diễn biến môi trường khu vực, dự báo, so sánh các tác động môi trường của các phương án quy hoạch trên cơ sở mật độ xây dựng, quy hoạch sử dụng đất, bố trí các khu chức năng.</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3801,9 +4041,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152647</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3814,18 +4051,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:b3bcbe30-21be-11f1-af12-01dc2ecd3981:2022-01-08: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>06/2022/NĐ-CP · hiệu lực 2022-01-07 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 29. Trách nhiệm trong quản lý các chất được kiểm soát
+1. Bộ Tài nguyên và Môi trường là cơ quan đầu mối quốc gia thực hiện Công ước Viên và Nghị định thư Montreal, chịu trách nhiệm trước Chính phủ thực hiện quản lý nhà nước về các chất được kiểm soát. Bộ Tài nguyên và Môi trường có trách nhiệm chủ trì, phối hợp với các bộ, ngành liên quan:
+a) Thực hiện quản lý các chất được kiểm soát theo điều ước quốc tế về bảo vệ tầng ô-dôn mà Việt Nam là thành viên; phân bổ, điều chỉnh, bổ sung hạn ngạch sản xuất, nhập khẩu các chất HCFC, HFC theo giai đoạn và hằng năm;
+b) Xây dựng, trình Thủ tướng Chính phủ ban hành Kế hoạch quốc gia về quản lý, loại trừ các chất được kiểm soát; trình cấp có thẩm quyền ban hành, sửa đổi, bổ sung danh mục, hướng dẫn sử dụng các chất được kiểm soát và quy định về điều kiện sản xuất, sử dụng các chất được kiểm soát theo cam kết thực hiện điều ước quốc tế về bảo vệ tầng ô-dôn mà nước Cộng hòa xã hội chủ nghĩa Việt Nam là thành viên;
+c) Công bố, sửa đổi, bổ sung danh mục các mặt hàng cấm xuất khẩu, cấm nhập khẩu; danh mục các mặt hàng được phép xuất khẩu, nhập khẩu theo điều kiện kèm theo mã số hàng hóa thuộc phạm vi quản lý trên cơ sở thống nhất với Bộ Công Thương về danh mục hàng hóa và thống nhất với Bộ Tài chính về mã số hàng hóa;
+d) Xây dựng và vận hành hệ thống dịch vụ công trực tuyến về đăng ký, báo cáo, phân bổ và quản lý hạn ngạch sản xuất, nhập khẩu các chất được kiểm soát; kết nối Cổng thông tin một cửa quốc gia về quản lý các chất được kiểm soát;
+đ) Tổ chức việc thực hiện các nghĩa vụ của quốc gia đối với Nghị định thư Montreal; phối hợp với cơ quan đầu mối của các quốc gia khác trong việc thực hiện các biện pháp tuân thủ Nghị định thư Montreal của Việt Nam;
+e) Thực hiện thanh tra, kiểm tra, giám sát việc đăng ký, báo cáo, sử dụng hạn ngạch; quản lý việc thu gom, tái sử dụng, tái chế và xử lý các chất được kiểm soát;
+g) Tổ chức thực hiện các nội dung được giao theo quy định của Luật Bảo vệ môi trường, Nghị định này và các nhiệm vụ khác liên quan đến quản lý chất được kiểm soát.</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3878,9 +4127,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132219</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3891,7 +4137,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -3902,11 +4147,23 @@
           <t>Có cạnh 'Văn bản được thay thế' trỏ vào NĐ 114/2018/NĐ-CP nhưng valid_to rỗng; id cũ vilextime:T1:provision:b8918060-2d46-11f1-8ed9-293a0f03a912:2018-09-05: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>114/2018/NĐ-CP · hiệu lực 2018-09-04 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 24. Cắm mốc chỉ giới xác định phạm vi bảo vệ đập thủy điện
+4. Phê duyệt phương án cắm mốc chỉ giới
+a) Chủ sở hữu đập, hồ chứa thủy điện nộp 01 bộ hồ sơ trực tiếp hoặc gửi qua đường bưu điện đến Ủy ban nhân dân cấp tỉnh nơi xây dựng đập. Hồ sơ gồm văn bản đề nghị phê duyệt và phương án cắm mốc chỉ giới;
+Trường hợp hồ sơ chưa hợp lệ, trong thời hạn 05 ngày làm việc, kể từ ngày nhận hồ sơ Ủy ban nhân dân cấp tỉnh thông báo bằng văn bản cho chủ sở hữu đập, hồ chứa thủy điện để hoàn chỉnh hồ sơ theo quy định;
+b) Trong thời hạn 25 ngày làm việc, kể từ ngày nhận đủ hồ sơ hợp lệ Ủy ban nhân dân cấp tỉnh có trách nhiệm tổ chức thẩm định;
+c) Trường hợp nội dung phương án cắm mốc chỉ giới phù hợp với quy định của pháp luật hiện hành và đặc điểm nơi xây dựng đập, trong thời hạn 05 ngày làm việc kể từ ngày tổ chức thẩm định, Ủy ban nhân dân cấp tỉnh có trách nhiệm phê duyệt. Trường hợp nội dung phương án cắm mốc chỉ giới không phù hợp với quy định của pháp luật hiện hành hoặc không phù hợp với đặc điểm nơi xây dựng đập, trong thời hạn 05 ngày làm việc kể từ ngày tổ chức thẩm định, Ủy ban nhân dân cấp tỉnh có trách nhiệm ban hành văn bản yêu cầu chủ sở hữu đập, hồ chứa thủy điện điều chỉnh, bổ sung phương án cắm mốc chỉ giới;
+d) Đối với đập có phạm vi bảo vệ thuộc địa bàn một huyện, Ủy ban nhân dân cấp tỉnh xem xét quyết định phân cấp cho Ủy ban nhân dân cấp huyện nơi xây dựng đập phê duyệt.</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3959,9 +4216,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23099</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3972,18 +4226,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:bcd427a2-df46-11f0-9393-9f1aa228ec14#k1#c:2001-10-21: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>71/2001/NĐ-CP · hiệu lực 2001-10-20 → 2006-10-08 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 12. Quỹ phát triển nhà ở
+1. Căn cứ nhu cầu, điều kiện và chương trình phát triển nhà ở của địa phương, Chủ tịch Uỷ ban nhân dân cấp tỉnh có thể quyết định thành lập Quỹ phát triển nhà ở để huy động các nguồn vốn phục vụ đầu tư phát triển nhà ở trên địa bàn theo quy định như sau:
+a) Quỹ phát triển nhà ở được hình thành từ các nguồn: ngân sách nhà nước (tiền bán nhà ở thuộc sở hữu Nhà nước, khấu hao cơ bản trích từ tiền cho thuê nhà ở thuộc sở hữu Nhà nước, tiền sử dụng đất ở và các nguồn ngân sách khác nếu có); tiền huy động, tiền gửi của người có nhu cầu mua nhà ở, tiền hỗ trợ, tiền đóng góp tự nguyện của các tổ chức, cá nhân trong và ngoài nước và các hình thức huy động vốn hợp pháp khác theo quy định của pháp luật;
+b) Qũy phát triển nhà ở hoạt động theo nguyên tắc bảo toàn vốn và bù đắp chi phí theo Điều lệ do Bộ trưởng Bộ Tài chính quy định, sau khi thống nhất với Bộ trưởng Bộ Xây dựng;
+c) Quỹ phát triển nhà ở được sử dụng vào các mục đích sau:
+Cho các doanh nghiệp trong nước quy định tại khoản 1 Điều 3 Nghị định này vay với lãi suất thấp để đầu tư xây dựng các dự án nhà ở được ưu đãi;
+Cho các đối tượng hưởng lương từ ngân sách nhà nước vay với lãi suất thấp để mua nhà ở;
+Cho các doanh nghiệp trong nước vay với điều kiện tín dụng thuận lợi để đầu tư xây dựng các dự án nhà ở.</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4036,9 +4301,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155496</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4049,18 +4311,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:d20598e6-df59-11f0-a9f3-71e4d6f8e635#k7:2021-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>63/2020/TT-BCA · hiệu lực 2021-01-01 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 9. Khám nghiệm hiện trường
+7. Sau khi khám nghiệm hiện trường, cán bộ Cảnh sát giao thông được phân công điều tra, xác minh, giải quyết vụ tai nạn giao thông phải có Báo cáo kết quả khám nghiệm hiện trường vụ tai nạn giao thông đường bộ theo mẫu số 07/TNĐB ban hành theo Thông tư này và đề xuất các biện pháp điều tra, xác minh, giải quyết tiếp theo.</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4113,9 +4380,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44169</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4126,7 +4390,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>valid_to_wrong</t>
@@ -4137,11 +4400,18 @@
           <t>Luật Tổ chức TAND 62/2014/QH13 đã bị Luật 34/2024/QH15 thay thế từ 01/01/2025; valid_to vẫn rỗng; id cũ vilextime:T1:provision:d93e71d8-df44-11f0-8872-818f0d72bc1d:2015-06-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>62/2014/QH13 · hiệu lực 2015-06-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 74. Nhiệm kỳ của Thẩm phán
+Nhiệm kỳ đầu của các Thẩm phán là 05 năm; trường hợp được bổ nhiệm lại hoặc được bổ nhiệm vào ngạch Thẩm phán khác thì nhiệm kỳ tiếp theo là 10 năm.</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4169,7 +4439,6 @@
           <t>2011-07-30 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>4.2. Trong số các hạng mục phải kiểm tra chất lượng về môi trường cần đặc biệt chú ý kiểm tra các hệ thống chống thấm, hệ thống thu gom và xử lý nước rác, hệ thống thu gom, đánh giá và khử biogas cũng như hệ thống giếng quan trắc nước dưới đất, các trạm quan trắc nước mặt. Công tác kiểm tra phải được tiến hành cả ở hiện trường và trong phòng thí nghiệm, đúng hạng mục và phù hợp với từng thời điểm cần thiết nhằm đảm bảo sao cho những vật liệu và thiết bị sử dụng trong BCL đáp ứng các tiêu chuẩn Việt Nam về môi trường (TCVN).</t>
@@ -4190,9 +4459,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23306</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4203,7 +4469,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -4214,11 +4479,17 @@
           <t>Đáp án là mục 4.2 nhưng citation là 'Khoản 4'; id cũ vilextime:T1:provision:dfeea17c-e16c-11f0-ab71-f3424eab00a5:2001-02-03: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>01/2001/TTLT/BKHCNMT-BXD · hiệu lực 2001-02-02 → 2019-08-15 · lúc thu thập: Hết hiệu lực toàn bộ
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4271,9 +4542,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=105944</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4284,18 +4552,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về phối hợp trao đổi thông tin bảo đảm an ninh hàng không dân dụng, thông tin về tình hình nước ngoài nào thuộc nội dung phải trao đổi?»; nhãn cũ khong_dat question_ambiguous: 'Thông tin về tình hình nước ngoài' cũng khớp khoản 3 (tội phạm, khủng bố quốc tế) và khoản 6 (xu hướng ngành hàng không các nước)). Câu hỏi chốt tình hình an ninh, chính trị các nước có đường bay; id cũ vilextime:T1:provision:e1d96590-df4a-11f0-b9c1-975d55408b6a:2016-06-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>07/2016/TTTL-BGTVT-BCA-BQP · hiệu lực 2016-06-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 4. Nội dung thông tin trao đổi
+4. Tình hình an ninh, chính trị các nước, khu vực có đường bay đi, đến, bay qua Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4348,9 +4621,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159420</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4361,18 +4631,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về hồ sơ đồ án quy hoạch xây dựng, bản đồ tổng hợp đường dây, đường ống kỹ thuật phải được thể hiện trên nền bản đồ nào và theo tỷ lệ nào?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu loại đồ án; Điều 10, 12, 27, 29, 36 cùng có mục 'Bản đồ tổng hợp đường dây, đường ống kỹ thuật' với nền bản đồ/tỷ lệ khác nhau). Đã nêu đồ án quy hoạch phân khu đô thị (Điều 10); id cũ vilextime:T1:provision:ebf45422-df54-11f0-b907-ef5b243581fd#k1#h:2023-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>04/2022/TT-BXD · hiệu lực 2023-01-01 → 2025-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 10. Nội dung hồ sơ đồ án quy hoạch phân khu đô thị
+1. Thành phần bản vẽ bao gồm:
+a) Sơ đồ vị trí và giới hạn khu đất: Vị trí, phạm vi ranh giới lập quy hoạch, thể hiện mối quan hệ giữa khu vực lập quy hoạch với các khu vực khác trong đô thị. Bản vẽ hiện trên sơ đồ hướng phát triển không gian và bản đồ quy hoạch sử dụng đất đô thị theo các giai đoạn quy hoạch ở tỷ lệ thích hợp.
+b) Bản đồ hiện trạng sử dụng đất và kiến trúc, cảnh quan: Hiện trạng chức năng sử dụng đất theo quy định tại Phụ lục V của Thông tư này và các chỉ tiêu sử dụng đất; hiện trạng kiến trúc cảnh quan, hệ thống hạ tầng xã hội (giáo dục, y tế, văn hóa, thể dục thể thao, thương mại, cây xanh, nhà ở,...), các khu vực bảo vệ di tích, di sản, danh lam thắng cảnh. Bản vẽ thể hiện trên nền bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+c) Các bản đồ hiện trạng hệ thống hạ tầng kỹ thuật và bảo vệ môi trường: Giao thông, cấp điện và chiếu sáng đô thị, thông tin liên lạc, cấp nước, cao độ nền và thoát nước mưa, thoát nước thải; quản lý chất thải rắn, nghĩa trang và môi trường; công trình hạ tầng kỹ thuật khác. Bản đồ thể hiện trên nền bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+d) Bản đồ quy hoạch tổng mặt bằng sử dụng đất: Xác định quy mô diện tích, dân số và chỉ tiêu sử dụng đất quy hoạch đối với từng ô phố trong khu vực lập quy hoạch theo quy định tại Phụ lục V của Thông tư này; khoảng lùi công trình đối với các trục đường trong khu vực lập quy hoạch; vị trí, quy mô công trình ngầm. Xác định các đơn vị ở; vị trí, quy mô của hệ thống hạ tầng xã hội cấp đô thị trở lên (nếu có) và cấp đơn vị ở trong khu vực. Bản vẽ thể hiện trên nền bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+đ) Sơ đồ tổ chức không gian kiến trúc cảnh quan: Bản vẽ thể hiện trên nền bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+e) Bản đồ quy hoạch hệ thống công trình giao thông và chỉ giới đường đỏ, chỉ giới xây dựng đến cấp đường khu vực đối với bản vẽ tỷ lệ 1/5.000 hoặc đ ường phân khu vực đối với bản vẽ 1/2.000; vị trí, quy mô bến, bãi đỗ xe (trên cao, trên mặt đất và ngầm); tuyến và ga tàu điện ngầm ; hào và tuynel kỹ thuật. Bản vẽ thể hiện trên nền bản đồ quy hoạch tổng mặt bằng sử dụng đất kết hợp bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+g) Các bản đồ quy hoạch hệ thống công trình hạ tầng kỹ thuật theo từng chuyên ngành: Chuẩn bị kỹ thuật, cấp nước, cấp năng lượng và chiếu sáng, thoát nước thải và xử lý chất thải rắn, hạ tầng viễn thông thụ động và công trình hạ tầng kỹ thuật khác. Thể hiện trên nền bản đồ quy hoạch tổng mặt bằng sử dụng đất kết hợp bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+h) Bản đồ tổng hợp đường dây, đường ống kỹ thuật. Bản vẽ thể hiện trên nên bản đồ quy hoạch tổng mặt bằng sử dụng đất kết hợp bản đồ địa hình tỷ lệ 1/2.000 hoặc 1/5.000.
+i) Bản vẽ xác định các khu vực xây dựng công trình ngầm : Các công trình công cộng ngầm , các công trình cao tầng có xây dựng tầng hầm (nếu có). Bản vẽ thể hiện theo tỷ lệ thích hợp trên nền bản đồ quy hoạch tổng mặt bằng sử dụng đất , bản đồ tổng hợp đường dây, đường ống kỹ thuật kết hợp bản đồ địa hình.
+k) Các bản vẽ thiết kế đô thị: Thể hiện theo quy định tại Thông tư số 06/2013/TT-BXD .</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4425,9 +4710,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13699</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4438,7 +4720,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>citation_path_wrong</t>
@@ -4449,11 +4730,17 @@
           <t>Mục 1.2.b bị ghi thành 'Điểm b Khoản 1' (lead_in '1. 2 Kiểm kê ...'); id cũ vilextime:T1:provision:ee6092ba-eb76-11f0-a704-8938278d801d:2007-05-29: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>25/2007/TT-BTC · hiệu lực 2007-05-28 → 2010-05-05 · lúc thu thập: Hết hiệu lực toàn bộ
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4506,9 +4793,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139885</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4519,18 +4803,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:f2798c00-22ab-11f1-b463-8f1119e7a6db:2021-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>54/2019/QH14 · hiệu lực 2021-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 41. Nội dung quản trị công ty áp dụng đối với công ty đại chúng
+2. Việc triệu tập, tổ chức họp Đại hội đồng cổ đông tuân thủ các quy định sau đây:
+a) Hội đồng quản trị, Ban kiểm soát, người triệu tập họp Đại hội đồng cổ đông phải tuân thủ đầy đủ trình tự, thủ tục về triệu tập họp Đại hội đồng cổ đông theo quy định của Luật Doanh nghiệp, Điều lệ công ty và Quy chế nội bộ về quản trị công ty; bố trí địa điểm, thời gian hợp lý để các cổ đông tham dự họp Đại hội đồng cổ đông;
+b) Công ty đại chúng quy định tại Quy chế nội bộ về quản trị công ty việc áp dụng công nghệ thông tin hiện đại để cổ đông có thể tham dự và phát biểu ý kiến tại cuộc họp Đại hội đồng cổ đông thông qua họp trực tuyến, bỏ phiếu điện tử hoặc hình thức điện tử khác theo quy định của Luật Doanh nghiệp và Điều lệ công ty;
+c) Công ty đại chúng phải mời đại diện tổ chức kiểm toán được chấp thuận thực hiện kiểm toán Báo cáo tài chính năm của công ty dự họp Đại hội đồng cổ đông thường niên trong trường hợp Báo cáo kiểm toán báo cáo tài chính năm của công ty có các khoản ngoại trừ trọng yếu;
+d) Tuân thủ các quy định khác của pháp luật và Điều lệ công ty.</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4583,9 +4876,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164267</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4596,7 +4886,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
           <t>citation_path_wrong,lead_in_wrong,group_wrong</t>
@@ -4612,10 +4901,57 @@
           <t>"Điều 4a. Cách thức gửi, nhận hồ sơ..."</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>16/2023/TT-NHNN · hiệu lực 2024-07-01 → 2026-03-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 4. Nội dung chứng thư số
+1. Tên tổ chức cung cấp dịch vụ chữ ký số.
+2. Tên của thuê bao.
+3. Số hiệu (Serial Number) của chứng thư số.
+4. Thời hạn có hiệu lực của chứng thư số.
+5. Khóa công khai của thuê bao.
+6. Chữ ký số của tổ chức cung cấp dịch vụ chữ ký số.
+7. Các hạn chế về mục đích, phạm vi sử dụng của chứng thư số.
+8. Các hạn chế về trách nhiệm pháp lý của tổ chức cung cấp dịch vụ chữ ký số.
+9. Thuật toán mật mã.
+10. Các nội dung cần thiết khác theo quy định của Bộ Thông tin và Truyền thông."
+5. Sửa đổi, bổ sung Điều 4a Thông tư 28/2015/TT-NHNN (đã được sửa đổi, bổ sung bởi khoản 4 Điều 1 Thông tư 10/2020/TT-NHNN) như sau:
+"Điều 4a. Cách thức gửi, nhận hồ sơ, văn bản, báo cáo liên quan đến dịch vụ chứng thực chữ ký số và kết quả xử lý
+1. Tổ chức quản lý thuê bao gửi hồ sơ, văn bản, báo cáo liên quan đến chứng thư số và dịch vụ chứng thực chữ ký số đến Ngân hàng Nhà nước (Cục Công nghệ thông tin) thông qua một trong các phương thức sau:
+a) Phương thức điện tử qua Hệ thống dịch vụ công;
+b) Văn bản giấy nộp trực tiếp tại Bộ phận Một cửa hoặc gửi qua dịch vụ bưu chính
+c) Văn bản điện tử gửi qua hệ thống Quản lý văn bản và điều hành của Ngân hàng Nhà nước (áp dụng đối với các đơn vị thuộc Ngân hàng Nhà nước). Ngân hàng Nhà nước (Cục Công nghệ thông tin) chỉ tiếp nhận, xử lý văn bản giấy và văn bản điện tử gửi qua hệ thống Quản lý văn bản và điều hành của Ngân hàng Nhà nước trong các trường hợp sau đây:
+- Hệ thống dịch vụ công gặp sự cố không thể hoạt động được;
+- Tổ chức quản lý thuê bao chưa được cấp chứng thư số có nghiệp vụ dịch vụ công hoặc chứng thư số hết hiệu lực hoặc thiết bị lưu khóa bí mật của thuê bao bị hỏng.
+2. Gửi hồ sơ, văn bản, báo cáo liên quan đến chứng thư số và dịch vụ chứng thực chữ ký số Ngân hàng Nhà nước
+a) Trường hợp gửi hồ sơ, văn bản, báo cáo bản giấy: Tổ chức quản lý thuê bao có quyền lựa chọn gửi bản gốc hoặc bản sao được cấp từ sổ gốc hoặc bản sao có chứng thực hoặc bản sao kèm xuất trình bản chính để đối chiếu.
+b) Trường hợp gửi hồ sơ, văn bản, báo cáo điện tử: Các hồ sơ, văn bản, báo cáo (trừ các văn bản, báo cáo là các Phụ lục của Thông tư này đã được chuyển đổi thành các biểu mẫu điện tử trên Hệ thống dịch vụ công) gửi qua Hệ thống dịch vụ công, tổ chức quản lý thuê bao gửi bản điện tử được số hóa từ bản gốc (tập tin định dạng PDF) và được người có thẩm quyền của tổ chức quản lý thuê bao ký số sử dụng chứng thư số của CA-NHNN.
+3. Cục Công nghệ thông tin gửi thông báo kết quả xử lý, lý do từ chối trong trường hợp hồ sơ không được chấp thuận đến tổ chức quản lý thuê bao bằng phương thức điện tử qua Hệ thống dịch vụ công. Trường hợp Hệ thống dịch vụ công gặp sự cố, thông báo kết quả được gửi đến tổ chức quản lý thuê bao qua dịch vụ bưu chính hoặc địa chỉ thư điện tử của thuê bao và cá nhân hoặc bộ phận đầu mối phụ trách quản lý chứng thư số của tổ chức quản lý thuê bao."
+6. Sửa đổi, bổ sung Điều 4b Thông tư 28/2015/TT-NHNN (đã được sửa đổi, bổ sung bởi khoản 5 Điều 1 Thông tư 10/2020/TT-NHNN) như sau:
+"Điều 4b. Thiết bị lưu khóa bí mật của thuê bao
+1. Cục Công nghệ thông tin có trách nhiệm hướng dẫn về chủng loại, thông số kỹ thuật thiết bị lưu khóa bí mật của thuê bao phù hợp với hệ thống chứng thực chữ ký số Ngân hàng Nhà nước và tình hình phát triển công nghệ.
+2. Cục Công nghệ thông tin cung cấp thiết bị lưu khóa bí mật cho các đơn vị hành chính thuộc Ngân hàng Nhà nước. Các đơn vị sự nghiệp thuộc Ngân hàng Nhà nước và các tổ chức quản lý thuê bao khác tự trang bị thiết bị lưu khóa bí mật theo đúng hướng dẫn của Cục Công nghệ thông tin.
+3. Việc gửi, nhận thiết bị lưu khóa bí mật giữa Cục Công nghệ thông tin và các đơn vị hành chính thuộc Ngân hàng Nhà nước được thực hiện bằng phương thức trực tiếp hoặc thông qua dịch vụ bưu chính."
+7. Sửa đổi, bổ sung Điều 5 Thông tư 28/2015/TT-NHNN (đã được sửa đổi, bổ sung bởi khoản 6 Điều 1 Thông tư 10/2020/TT-NHNN) như sau:
+"Điều 5. Cấp, bổ sung nghiệp vụ chứng thư số
+1. Khi có nhu cầu cấp chứng thư số hoặc bổ sung nghiệp vụ, tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ bao gồm:
+a) Cấp, bổ sung nghiệp vụ chứng thư số cho cá nhân là người có thẩm quyền: - Giấy đề nghị cấp, bổ sung nghiệp vụ chứng thư số cho cá nhân theo Phụ lục 01 ban hành kèm theo Thông tư này; - Quyết định bổ nhiệm của người có thẩm quyền khi đề nghị cấp mới chứng thư số (đối với cơ quan nhà nước).
+b) Cấp, bổ sung nghiệp vụ chứng thư số cho cá nhân là người được người có thẩm quyền ủy quyền:
+- Giấy đề nghị cấp, bổ sung nghiệp vụ chứng thư số cho cá nhân theo Phụ lục 01 ban hành kèm theo Thông tư này;
+- Quyết định bổ nhiệm của người có thẩm quyền khi đề nghị cấp mới chứng thư số (đối với cơ quan nhà nước);
+- Văn bản ủy quyền của người có thẩm quyền cho cá nhân được cấp chứng thư số hoặc bổ sung nghiệp vụ chứng thư số, nêu rõ người được ủy quyền được phép đại diện cho tổ chức ký duyệt hồ sơ, văn bản, tài liệu, báo cáo, giao dịch trên hệ thống thông tin tương ứng với nghiệp vụ của chứng thư số đề nghị cấp. Người được ủy quyền không được ủy quyền lại cho người khác thực hiện
+c) Cấp, bổ sung nghiệp vụ chứng thư số cho tổ chức:
+Giấy đề nghị cấp, bổ sung nghiệp vụ chứng thư số cho tổ chức theo Phụ lục 02 ban hành kèm theo Thông tư này.
+2. Trường hợp chứng thư số đã được cấp và còn hiệu lực, được tổ chức quản lý thuê bao đề nghị bổ sung nghiệp vụ chứng thư số, Cục Công nghệ thông tin thực hiện bổ sung nghiệp vụ cho chứng thư số hiện có của thuê bao.
+3. Trường hợp cấp chứng thư số sau khi chứng thư số cũ hết hiệu lực hoặc chứng thư số đã bị thu hồi, thuê bao có nhu cầu tiếp tục sử dụng thì thực hiện thủ tục cấp mới chứng thư số theo quy định tại khoản 1 Điều này.
+4. Thời hạn giải quyết và kết quả thực hiện Trong thời hạn 03 ngày làm việc kể từ ngày nhận được hồ sơ đề nghị cấp chứng thư số hợp lệ, Cục Công nghệ thông tin thực hiện cấp chứng thư số hoặc bổ sung nghiệp vụ chứng thư số cho thuê bao, gửi thông báo cấp chứng thư số và mã kích hoạt chứng thư số đến địa c</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4668,9 +5004,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=91876</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4681,18 +5014,23 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>id cũ vilextime:T1:provision:fcda0fa4-e14b-11f0-9ac4-238e516e6c2b#k4:2016-01-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>52/2015/QĐ-TTg · hiệu lực 2016-01-01 → 2018-01-23 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 32. Hiệu lực thi hành
+4. Trường hợp cần điều hành linh hoạt hoạt động thương mại biên giới phù hợp với điều kiện kinh tế - xã hội của từng địa phương và trong từng thời kỳ, Thủ tướng Chính phủ xem xét quyết định việc điều chỉnh hoạt động mua bán hàng hóa qua biên giới của thương nhân và cư dân biên giới trên cơ sở đề nghị của Bộ Công Thương.</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4720,7 +5058,6 @@
           <t>2001-11-28 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>5. Thông tư này có hiệu lực sau 15 ngày, kể từ ngày ký.</t>
@@ -4741,9 +5078,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=22671</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4754,18 +5088,22 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Điều khoản hiệu lực của chính thông tư, không phải quy phạm nội dung — cân nhắc loại khỏi T1; id cũ vilextime:T1:provision:fe20558c-e180-11f0-a914-ddbb65539df3:2001-10-04: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>07/2001/TT-BCA (V19) · hiệu lực 2001-10-03 → 2009-08-28 · lúc thu thập: Hết hiệu lực toàn bộ
+(không cắt được đoạn)</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4818,9 +5156,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163781</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4831,18 +5166,25 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đoạn rẽ từ đường bộ vào đường sắt ngắn hơn 10 mét, biển báo tại đường ngang phải được chọn và đặt như thế nào?»; nhãn cũ khong_dat question_ambiguous: Hỏi chung 'biển báo phải được chọn và đặt như thế nào' khi đoạn rẽ &lt; 10 m; điểm b cũng quy định biển phải đặt). Câu hỏi chốt 'căn cứ góc giao' nên chỉ khớp điểm a; id cũ vilextime:T1:provision:fe2ac128-eb6e-11f0-b2f9-27b4d1adb5b1:2023-12-02: spread_as_of (07/10) đổi as_of, cùng phiên bản và câu hỏi; nối lại 11/10</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>29/2023/TT-BGTVT · hiệu lực 2023-12-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 25. Yêu cầu đối với việc đặt biển báo hiệu trong trường hợp đường bộ liền kề và có đoạn rẽ vào đường sắt
+1. Khi chiều dài đoạn rẽ đến đường sắt nhỏ hơn 10 mét (m):
+a) Căn cứ góc giao của đường ngang, phải đặt biển "Nơi đường sắt giao vuông góc với đường bộ" hoặc "Nơi đường sắt giao không vuông góc với đường bộ" tại lề hai góc giao giữa đường bộ chạy gần với đoạn rẽ vào đường sắt;
+b) Căn cứ loại hình phòng vệ đường ngang phải đặt các biển "Giao nhau với đường sắt có rào chắn" hoặc "Giao nhau với đường sắt không có rào chắn" trên lề bên phải đường bộ chạy gần đường sắt. Khoảng cách các biển đến đoạn rẽ từ 40 mét (m) đến 240 mét (m).</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
